--- a/data/exports/validation_study/packets/week-2/packet-4.xlsx
+++ b/data/exports/validation_study/packets/week-2/packet-4.xlsx
@@ -544,7 +544,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2. 'techniques' sheet - the 17 attacks, mechanisms and defenses we recorded from your papers.</t>
+          <t>2. 'techniques' sheet - the 16 attacks, mechanisms and defenses we recorded from your papers.</t>
         </is>
       </c>
     </row>
@@ -2284,11 +2284,11 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Trojan's Whisper: Stealthy Manipulation of OpenClaw through Injected Bootstrapped Guidance</t>
+          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Trojan's Whisper - Stealthy Manipulation of OpenClaw through Injected Bootstrapped Guidance.pdf</t>
+          <t>data/papers/Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks.pdf</t>
         </is>
       </c>
       <c r="G2" s="5" t="n"/>
@@ -2312,15 +2312,15 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Human-Interpretable Adversarial Prompt Attack on Large Language Models with Situational Context</t>
+          <t>FlashMem: Distilling Intrinsic Latent Memory via Computation Reuse</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>ACL</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Human-Interpretable Adversarial Prompt Attack on Large Language Models with Situational Context.pdf</t>
+          <t>data/papers/FlashMem - Distilling Intrinsic Latent Memory via Computation Reuse.pdf</t>
         </is>
       </c>
       <c r="G3" s="5" t="n"/>
@@ -2340,15 +2340,15 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
+          <t>Poisoning Retrieval Corpora by Injecting Adversarial Passages</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>ACL</t>
+          <t>EMNLP</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Caution for the Environment - Multimodal Agents are Susceptible to Environmental Distractions.pdf</t>
+          <t>data/papers/Poisoning Retrieval Corpora by Injecting Adversarial Passages.pdf</t>
         </is>
       </c>
       <c r="G4" s="5" t="n"/>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Enterprise Secure AI Execution Engine: A Zero-Trust Security Gateway for Enterprise LLM Systems</t>
+          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
@@ -2376,15 +2376,15 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>International Congress on Information and Communication Technology</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Enterprise Secure AI Execution Engine - A Zero-Trust Security Gateway for Enterprise LLM Systems.pdf</t>
+          <t>data/papers/Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution.pdf</t>
         </is>
       </c>
       <c r="G5" s="5" t="n"/>
@@ -2396,23 +2396,23 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Tug-of-War between Knowledge: Exploring and Resolving Knowledge Conflicts in Retrieval-Augmented Language Models</t>
+          <t>Tug-of-War within A Decade: Conflict Resolution in Vulnerability Analysis via Teacher-Guided Retrieval-Augmented Generations</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>International Conference on Language Resources and Evaluation</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Tug-of-War between Knowledge - Exploring and Resolving Knowledge Conflicts in Retrieval-Augmented Language Models.pdf</t>
+          <t>data/papers/Tug-of-War within A Decade - Conflict Resolution in Vulnerability Analysis via Teacher-Guided Retrieval-Augmented Generations.pdf</t>
         </is>
       </c>
       <c r="G6" s="5" t="n"/>
@@ -2424,23 +2424,19 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>CodeDelegator: Mitigating Context Pollution via Role Separation in Code-as-Action Agents</t>
+          <t>Context-Aware RL for Agentic and Multimodal LLMs</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v>2026</v>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
+      <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>data/papers/CodeDelegator - Mitigating Context Pollution via Role Separation in Code-as-Action Agents.pdf</t>
+          <t>data/papers/Context-Aware RL for Agentic and Multimodal LLMs.pdf</t>
         </is>
       </c>
       <c r="G7" s="5" t="n"/>
@@ -2452,19 +2448,23 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Compile, Then Page: Executable SOP Programs and a Capability-Gated Runtime for Procedural LLM Agents</t>
+          <t>Hybrid Real-time Framework for Detecting Adaptive Prompt Injection Attacks in Large Language Models</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v>2026</v>
       </c>
-      <c r="D8" s="2" t="n"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Computing Theories and Applications</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Compile, Then Page - Executable SOP Programs and a Capability-Gated Runtime for Procedural LLM Agents.pdf</t>
+          <t>data/papers/Hybrid Real-time Framework for Detecting Adaptive Prompt Injection Attacks in Large Language Models.pdf</t>
         </is>
       </c>
       <c r="G8" s="5" t="n"/>
@@ -2476,23 +2476,19 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Breaking ReAct Agents: Foot-in-the-Door Attack Will Get You In</t>
+          <t>DRIP: Defending Prompt Injection via Token-wise Representation Editing and Residual Instruction Fusion</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>NAACL</t>
-        </is>
-      </c>
+        <v>2025</v>
+      </c>
+      <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Breaking ReAct Agents - Foot-in-the-Door Attack Will Get You In.pdf</t>
+          <t>data/papers/DRIP - Defending Prompt Injection via Token-wise Representation Editing and Residual Instruction Fusion.pdf</t>
         </is>
       </c>
       <c r="G9" s="5" t="n"/>
@@ -2504,23 +2500,23 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Defending Against Prompt Injection with DataFilter</t>
+          <t>MCPTox: A Benchmark for Tool Poisoning on Real-World MCP Servers</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>AAAI</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Defending Against Prompt Injection with DataFilter.pdf</t>
+          <t>data/papers/MCPTox - A Benchmark for Tool Poisoning on Real-World MCP Servers.pdf</t>
         </is>
       </c>
       <c r="G10" s="5" t="n"/>
@@ -2532,15 +2528,15 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>HAGE: Harnessing Agentic Memory via RL-Driven Weighted Graph Evolution</t>
+          <t>Corpus Poisoning via Approximate Greedy Gradient Descent</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>ACL</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
@@ -2548,7 +2544,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>data/papers/HAGE - Harnessing Agentic Memory via RL-Driven Weighted Graph Evolution.pdf</t>
+          <t>data/papers/Corpus Poisoning via Approximate Greedy Gradient Descent.pdf</t>
         </is>
       </c>
       <c r="G11" s="5" t="n"/>
@@ -2560,11 +2556,11 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>LUMINA: Long-horizon Understanding for Multi-turn Interactive Agents</t>
+          <t>The Task Shield: Enforcing Task Alignment to Defend Against Indirect Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
@@ -2572,11 +2568,11 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>data/papers/LUMINA - Long-horizon Understanding for Multi-turn Interactive Agents.pdf</t>
+          <t>data/papers/The Task Shield - Enforcing Task Alignment to Defend Against Indirect Prompt Injection in LLM Agents.pdf</t>
         </is>
       </c>
       <c r="G12" s="5" t="n"/>
@@ -2588,7 +2584,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>AgentProg: Empowering Long-Horizon GUI Agents with Program-guided Context Management</t>
+          <t>PIShield: Detecting Prompt Injection Attacks via Intrinsic LLM Features</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
@@ -2596,7 +2592,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>SIGMOBILE</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
@@ -2604,7 +2600,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>data/papers/AgentProg - Empowering Long-Horizon GUI Agents with Program-guided Context Management.pdf</t>
+          <t>data/papers/PIShield - Detecting Prompt Injection Attacks via Intrinsic LLM Features.pdf</t>
         </is>
       </c>
       <c r="G13" s="5" t="n"/>
@@ -2616,11 +2612,11 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>ICON: Indirect Prompt Injection Defense for Agents based on Inference-Time Correction</t>
+          <t>Rethinking All Evidence: Enhancing Trustworthy Retrieval-Augmented Generation via Conflict-Driven Summarization</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
@@ -2632,7 +2628,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>data/papers/ICON - Indirect Prompt Injection Defense for Agents based on Inference-Time Correction.pdf</t>
+          <t>data/papers/Rethinking All Evidence - Enhancing Trustworthy Retrieval-Augmented Generation via Conflict-Driven Summarization.pdf</t>
         </is>
       </c>
       <c r="G14" s="5" t="n"/>
@@ -2644,15 +2640,15 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Research on Security Enhancement Methods for Adversarial Robust Large Language Model Intelligent Agents for Medical Decision-Making Tasks</t>
+          <t>PISanitizer: Preventing Prompt Injection to Long-Context LLMs via Prompt Sanitization</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2026 7th International Seminar on Artificial Intelligence, Networking and Information Technology (AINIT)</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
@@ -2660,7 +2656,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Research on Security Enhancement Methods for Adversarial Robust Large Language Model Intelligent Agents for Medical Decision-Making Tasks.pdf</t>
+          <t>data/papers/PISanitizer - Preventing Prompt Injection to Long-Context LLMs via Prompt Sanitization.pdf</t>
         </is>
       </c>
       <c r="G15" s="5" t="n"/>
@@ -2672,7 +2668,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>ESLD (External Surrogate Latent Defense): A Latent-Space Architecture for Faster, Stronger Prompt-Injection Defense</t>
+          <t>CASCADE: A Cascaded Hybrid Defense Architecture for Prompt Injection Detection in MCP-Based Systems</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -2688,7 +2684,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>data/papers/ESLD (External Surrogate Latent Defense) - A Latent-Space Architecture for Faster, Stronger Prompt-Injection Defense.pdf</t>
+          <t>data/papers/CASCADE - A Cascaded Hybrid Defense Architecture for Prompt Injection Detection in MCP-Based Systems.pdf</t>
         </is>
       </c>
       <c r="G16" s="5" t="n"/>
@@ -2772,7 +2768,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Trojan's Whisper: Stealthy Manipulation of OpenClaw through Injected Bootstrapped Guidance</t>
+          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -2795,7 +2791,7 @@
       <c r="H2" s="5" t="n"/>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>77bd60b2f06f814a3f6ef85ec0c11b0176b0ceb1</t>
+          <t>66c8e83ed0fc215dc8be0e44715a692ef27f005b</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2801,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Trojan's Whisper: Stealthy Manipulation of OpenClaw through Injected Bootstrapped Guidance</t>
+          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -2828,7 +2824,7 @@
       <c r="H3" s="5" t="n"/>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>77bd60b2f06f814a3f6ef85ec0c11b0176b0ceb1</t>
+          <t>66c8e83ed0fc215dc8be0e44715a692ef27f005b</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2834,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Trojan's Whisper: Stealthy Manipulation of OpenClaw through Injected Bootstrapped Guidance</t>
+          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -2861,7 +2857,7 @@
       <c r="H4" s="5" t="n"/>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>77bd60b2f06f814a3f6ef85ec0c11b0176b0ceb1</t>
+          <t>66c8e83ed0fc215dc8be0e44715a692ef27f005b</t>
         </is>
       </c>
     </row>
@@ -2871,7 +2867,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Trojan's Whisper: Stealthy Manipulation of OpenClaw through Injected Bootstrapped Guidance</t>
+          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -2894,7 +2890,7 @@
       <c r="H5" s="5" t="n"/>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>77bd60b2f06f814a3f6ef85ec0c11b0176b0ceb1</t>
+          <t>66c8e83ed0fc215dc8be0e44715a692ef27f005b</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2900,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Trojan's Whisper: Stealthy Manipulation of OpenClaw through Injected Bootstrapped Guidance</t>
+          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -2919,7 +2915,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>tool-output</t>
         </is>
       </c>
       <c r="F6" s="5" t="n"/>
@@ -2927,7 +2923,7 @@
       <c r="H6" s="5" t="n"/>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>77bd60b2f06f814a3f6ef85ec0c11b0176b0ceb1</t>
+          <t>66c8e83ed0fc215dc8be0e44715a692ef27f005b</t>
         </is>
       </c>
     </row>
@@ -2937,7 +2933,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Trojan's Whisper: Stealthy Manipulation of OpenClaw through Injected Bootstrapped Guidance</t>
+          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -2952,7 +2948,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>persistence-backdoor</t>
+          <t>goal-hijack</t>
         </is>
       </c>
       <c r="F7" s="5" t="n"/>
@@ -2960,7 +2956,7 @@
       <c r="H7" s="5" t="n"/>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>77bd60b2f06f814a3f6ef85ec0c11b0176b0ceb1</t>
+          <t>66c8e83ed0fc215dc8be0e44715a692ef27f005b</t>
         </is>
       </c>
     </row>
@@ -2970,7 +2966,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Trojan's Whisper: Stealthy Manipulation of OpenClaw through Injected Bootstrapped Guidance</t>
+          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -2993,7 +2989,7 @@
       <c r="H8" s="5" t="n"/>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>77bd60b2f06f814a3f6ef85ec0c11b0176b0ceb1</t>
+          <t>66c8e83ed0fc215dc8be0e44715a692ef27f005b</t>
         </is>
       </c>
     </row>
@@ -3003,7 +2999,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Trojan's Whisper: Stealthy Manipulation of OpenClaw through Injected Bootstrapped Guidance</t>
+          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -3018,7 +3014,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F9" s="5" t="n"/>
@@ -3026,7 +3022,7 @@
       <c r="H9" s="5" t="n"/>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>77bd60b2f06f814a3f6ef85ec0c11b0176b0ceb1</t>
+          <t>66c8e83ed0fc215dc8be0e44715a692ef27f005b</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3032,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Trojan's Whisper: Stealthy Manipulation of OpenClaw through Injected Bootstrapped Guidance</t>
+          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -3059,7 +3055,7 @@
       <c r="H10" s="5" t="n"/>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>77bd60b2f06f814a3f6ef85ec0c11b0176b0ceb1</t>
+          <t>66c8e83ed0fc215dc8be0e44715a692ef27f005b</t>
         </is>
       </c>
     </row>
@@ -3069,7 +3065,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Trojan's Whisper: Stealthy Manipulation of OpenClaw through Injected Bootstrapped Guidance</t>
+          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -3084,7 +3080,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>cross-session-dormant</t>
+          <t>one-shot</t>
         </is>
       </c>
       <c r="F11" s="5" t="n"/>
@@ -3092,7 +3088,7 @@
       <c r="H11" s="5" t="n"/>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>77bd60b2f06f814a3f6ef85ec0c11b0176b0ceb1</t>
+          <t>66c8e83ed0fc215dc8be0e44715a692ef27f005b</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3098,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Trojan's Whisper: Stealthy Manipulation of OpenClaw through Injected Bootstrapped Guidance</t>
+          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -3125,7 +3121,7 @@
       <c r="H12" s="5" t="n"/>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>77bd60b2f06f814a3f6ef85ec0c11b0176b0ceb1</t>
+          <t>66c8e83ed0fc215dc8be0e44715a692ef27f005b</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3131,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Trojan's Whisper: Stealthy Manipulation of OpenClaw through Injected Bootstrapped Guidance</t>
+          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -3150,7 +3146,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>No public code, dataset, or artifact release is stated. The authors instead describe responsible disclosure: they conducted all experiments in a fully synthetic environment (referred to as the DevSecBench/ORE-Bench benchmark, containing no real user data or credentials) and privately provided their adversarial skill implementations and evaluation framework directly to the OpenClaw development team rather than releasing them publicly, explicitly to reduce misuse risk.</t>
+          <t>No explicit code/dataset release URL is given in the extracted text. The paper states adaptive-attack prompt templates and payload examples are provided 'at Appendix E' and 'Appendix D' within the paper itself, but no external GitHub/HuggingFace repository link is mentioned for the evaluation harness, adapted payloads, or per-framework configurations.</t>
         </is>
       </c>
       <c r="F13" s="5" t="n"/>
@@ -3158,7 +3154,7 @@
       <c r="H13" s="5" t="n"/>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>77bd60b2f06f814a3f6ef85ec0c11b0176b0ceb1</t>
+          <t>66c8e83ed0fc215dc8be0e44715a692ef27f005b</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3164,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Trojan's Whisper: Stealthy Manipulation of OpenClaw through Injected Bootstrapped Guidance</t>
+          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -3183,7 +3179,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Six state-of-the-art LLM backends usable by OpenClaw agents are evaluated: DeepSeek V3.2, Kimi K2.5, Gemini 3.1 Pro, Claude Opus 4.6, GPT-5.3 Codex, and Qwen3 Max. A Claude-based hybrid classifier is additionally used as one of the four evaluated skill-detection/scanning defenses.</t>
+          <t>Ten representative IPI-centric defense frameworks are evaluated: LlamaFirewall (Detection), Tool Filter (Prompt Engineering), Meta SecAlign (Fine-tuning, using its public LoRA adapter for Llama-3.1-8B-Instruct), IsolateGPT, ACE, and CaMeL (System Design: plan-then-execute, code-then-execute, and Dual-LLM architectures respectively), Task Shield and MELON (Runtime Checking), and Progent (Policy Enforcing, with a Progent-LLM variant for automated policy generation). For all non-fine-tuning frameworks, GPT-4o (2024-11-20) is used as the backend LLM (temperature 0); DeepSeek-V3 is used in a supplementary generalization check (Appendix F). Undefended baselines Llama3.1-8B and SecAlign are also reported for comparison.</t>
         </is>
       </c>
       <c r="F14" s="5" t="n"/>
@@ -3191,7 +3187,7 @@
       <c r="H14" s="5" t="n"/>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>77bd60b2f06f814a3f6ef85ec0c11b0176b0ceb1</t>
+          <t>66c8e83ed0fc215dc8be0e44715a692ef27f005b</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3197,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Trojan's Whisper: Stealthy Manipulation of OpenClaw through Injected Bootstrapped Guidance</t>
+          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -3216,7 +3212,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>The paper constructs ORE-Bench (OpenClaw Realistic Environment Benchmark), a realistic simulated developer workspace built around a fictional user persona ('Alex Wang') containing synthetic sensitive data such as SSH keys, cloud/service credentials, and version control metadata (.git directories), a Docker Compose homelab stack, and an experimental RAG system, designed to mirror the complexity of real developer workstations while using only synthetic data. Against this environment, the authors construct 26 malicious OpenClaw skills spanning 13 attack categories (grouped into 10 high-risk, 8 medium-risk, and 8 low-risk skills) and test them with natural user prompts (reported as 52 prompts in the Conclusion and Abstract, and 78 prompts in the Introduction, an inconsistency present in the paper itself) across the six evaluated LLM backends.</t>
+          <t>Three existing static agent-IPI benchmarks are used: AgentDojo (4 scenarios per attack method, 74 tools, 629 test cases), InjecAgent (6 scenarios per attack method, 62 tools, 1,054 test cases), and Agent Security Bench/ASB (10 scenarios per attack method, 420 tools, 2,040 test cases). Utility is measured via AgentDojo's dynamic benchmark without implanted attack payloads. The paper's own contribution is a set of 949 adapted/adjusted IPI payloads (generated via an LLM-driven payload-adjustment-and-refinement pipeline) used to construct the three novel adaptive attacks.</t>
         </is>
       </c>
       <c r="F15" s="5" t="n"/>
@@ -3224,7 +3220,7 @@
       <c r="H15" s="5" t="n"/>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>77bd60b2f06f814a3f6ef85ec0c11b0176b0ceb1</t>
+          <t>66c8e83ed0fc215dc8be0e44715a692ef27f005b</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3230,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Trojan's Whisper: Stealthy Manipulation of OpenClaw through Injected Bootstrapped Guidance</t>
+          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -3249,7 +3245,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Across the six LLM backends and natural user prompts, guidance injection attacks achieve success rates ranging from 16.0% to 64.2% (per the Abstract; the Introduction separately reports success rates up to 89% under a different prompt count, an internal inconsistency in the paper), with the majority of malicious actions executed autonomously without requiring user confirmation. Model susceptibility varies substantially: DeepSeek V3.2 is the most vulnerable, showing high success rates across five of six attack categories; Kimi K2.5 is second-most vulnerable, particularly for information gathering and data leakage; Gemini 3.1 Pro is the most resistant overall (though still selectively vulnerable to data leakage and supply chain attacks); and Claude Opus 4.6 shows strong resistance except for supply chain attacks. Critically, 94% of the 26 malicious skills evade detection across four representative defenses: a rule-based Static Pattern Scan flagged only 1/10 high-risk skills (10%) and 0% of medium/low-risk skills; the open-source LLM-Guard library (ten input scanners) flagged 0% of all 26 skills; the authors' own two-stage hybrid classifier (scanner filtering plus Claude-based semantic assessment) flagged only 1/10 high-risk skills (10%) with zero false positives on medium/low-risk skills; and SkillScan, a commercial third-party skill-vetting platform used by the OpenClaw marketplace, assigned only modest average risk scores to the malicious skills (19.75/100 for high-risk, 14.70 for medium-risk, 14.88 for low-risk) compared to a score of 100 for an official skill with overt system modifications, indicating current commercial vetting fails to recognize malicious intent embedded in narrative guidance despite being able to detect overt threats.</t>
+          <t>Across the three static benchmarks (Table 2), most SoTA defense frameworks reduce ASR below 10% in the majority of scenarios (e.g., Progent and IsolateGPT near 0% average ASR; MELON 2.67%, Task Shield 0.43%), but undefended baselines are far more vulnerable (Llama3.1-8B 45.91% average ASR, GPT-4o 23.69%, SecAlign 11.77%). However, all ten frameworks are shown to be bypassable: the three novel adaptive attacks substantially increase ASR against targeted frameworks. Semantic-Masquerading IPI (adapting payloads to use functionally similar/differently-parameterized tools) more than doubles ASR against IsolateGPT, Tool Filter, CaMeL, and LlamaFirewall, with IsolateGPT and LlamaFirewall approaching a fourfold increase. Cascading IPI (an if-then-else payload structure with judge/filter items targeting auxiliary judge-LLM components) achieves 5.37% ASR against Task Shield (2.6x its 2.07% baseline) and 4.53% against MELON (4.8x its 0.95% baseline). Isolation-Breach IPI achieves the first documented zero-day-style bypass of IsolateGPT's architectural planner/executor separation by exploiting an overlooked information channel (error-message propagation/context feedback loops) to inject malicious intent directly into the trusted planner's context, causing the downstream isolation mechanism to become irrelevant once the planner itself is compromised.</t>
         </is>
       </c>
       <c r="F16" s="5" t="n"/>
@@ -3257,7 +3253,7 @@
       <c r="H16" s="5" t="n"/>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>77bd60b2f06f814a3f6ef85ec0c11b0176b0ceb1</t>
+          <t>66c8e83ed0fc215dc8be0e44715a692ef27f005b</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3263,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Trojan's Whisper: Stealthy Manipulation of OpenClaw through Injected Bootstrapped Guidance</t>
+          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -3282,7 +3278,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>The paper evaluates four detection/defense baselines against its 26 adversarial skills rather than comparing against alternative attack methods: a Static Pattern Scan (a rule-based scanner searching for explicit malicious patterns like credential-file access or sudoers modification, tuned to minimize false positives), the open-source LLM-Guard library (ten input scanners including PromptInjection, Secrets, Gibberish, InvisibleText, Sentiment, Toxicity, BanSubstrings, BanTopics, Code, and Regex, flagging at confidence &gt;=0.7), a custom two-stage Hybrid Classifier (low-confidence scanner-output filtering followed by Claude-based semantic assessment of whether signals form a complete malicious behavior chain, flagging at confidence &gt;0.75), and SkillScan, a commercial third-party skill-vetting platform actually used by the OpenClaw marketplace (outputting a proprietary 0-100 risk score via static and dynamic analysis).</t>
+          <t>For the benchmark evaluation, each of the ten defense frameworks is compared against undefended baseline agents (plain GPT-4o, plain Llama3.1-8B, and SecAlign as a fine-tuning-only baseline) across the same three benchmarks. For the adaptive attacks, each novel attack is compared against the corresponding template-based baseline attack already used by the benchmark (e.g., the AgentDojo 'Important' attack template serves as the direct-payload baseline for both the Semantic-Masquerading and Cascading IPI comparisons).</t>
         </is>
       </c>
       <c r="F17" s="5" t="n"/>
@@ -3290,7 +3286,7 @@
       <c r="H17" s="5" t="n"/>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>77bd60b2f06f814a3f6ef85ec0c11b0176b0ceb1</t>
+          <t>66c8e83ed0fc215dc8be0e44715a692ef27f005b</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3296,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Trojan's Whisper: Stealthy Manipulation of OpenClaw through Injected Bootstrapped Guidance</t>
+          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -3315,7 +3311,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>The threat model targets OpenClaw's skill ecosystem, specifically its agent:bootstrap lifecycle hook, which allows third-party skills to inject 'bootstrap guidance' files into the agent's foundational reasoning context before any user interaction occurs. The attacker is a malicious or compromised skill author who publishes a skill to the public ClawHub marketplace containing carefully crafted operational narratives that subtly redefine what constitutes 'routine' or 'best-practice' behavior (e.g., framing .git directory deletion as standard disposable-artifact cleanup, or framing MITM proxy setup as standard debugging practice), rather than embedding explicit malicious commands. When a legitimate user later issues an ambiguous or high-level request (e.g., 'free up disk space' or 'help me debug my trading bot'), the agent -- operating under its corrupted understanding of best practices, and resolving request ambiguity via in-context learning that recombines salient patterns from its context, including the injected guidance -- autonomously operationalizes the narrative and executes destructive, privilege-escalating, or data-exfiltrating actions while genuinely believing it is being helpful. This attack is enabled by three architectural properties the paper identifies as distinguishing OpenClaw from other coding agents: broad access to the user's private environment (configuration directories, credential stores, tool settings) beyond a single project workspace; exposure to untrusted external content (web searches, repositories, skill marketplaces, documentation) that can influence the agent's reasoning context; and autonomous execution capability, where the agent resolves request ambiguity by inferring actions rather than always requesting clarification.</t>
+          <t>The threat model assumes the adversary has no prior knowledge of the agent's architecture A or backend LLM, and can only manipulate static resources within the environment E; specifically, when the agent invokes a tool, E returns a malicious response embedded via a static injection template controlled by the adversary. All information and resources accessible to the agent are treated as trusted except for tool return results (agent memory, tool descriptions/schemas, the SDK, and OS are assumed trustworthy). The attack succeeds if the agent's final tool-call execution sequence matches the adversary's intended sequence. This SoK focuses exclusively on Indirect Prompt Injection (IPI) against LLM agents with function-calling/tool-use capabilities (distinct from IPI against passive QA LLMs), where injected content typically arrives via tool return results and the attacker's goal is to hijack tool-calling behavior to threaten user assets or privacy.</t>
         </is>
       </c>
       <c r="F18" s="5" t="n"/>
@@ -3323,7 +3319,7 @@
       <c r="H18" s="5" t="n"/>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>77bd60b2f06f814a3f6ef85ec0c11b0176b0ceb1</t>
+          <t>66c8e83ed0fc215dc8be0e44715a692ef27f005b</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3329,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Trojan's Whisper: Stealthy Manipulation of OpenClaw through Injected Bootstrapped Guidance</t>
+          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -3348,7 +3344,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>The paper has an explicit 'Limitations' section (8.3) with four stated points. First, the ORE-Bench environment, while realistic, cannot capture the full diversity of real-world developer setups, and variations in directory structures, installed tools, and user behavior may affect attack success rates. Second, only six LLM backends were evaluated, and newer models with enhanced safety training may exhibit different susceptibility. Third, the attacks are specific to OpenClaw's bootstrap hook mechanism, and other agent frameworks may have different architectures that either mitigate or amplify the risk. Fourth, the study focused specifically on guidance injection via skill hooks, leaving other injection channels (e.g., through web searches or documentation ingestion) unexplored. A separate 'Future Work' section (8.4) identifies developing robust defenses against adversarial natural language (potentially via formal methods for defining safe agent behavior), exploring attack transferability across different agent platforms and LLMs, and establishing broader community benchmarks/disclosure norms as open directions.</t>
+          <t>The paper has no section explicitly titled 'Limitations.' The closest analog appears in the discussion immediately preceding the Conclusion, following the Isolation-Breach IPI attack: the authors state that 'architectural separation alone is insufficient when high-level planners remain semantically coupled to untrusted data' and argue future defenses must move beyond ad-hoc isolation toward rigorous formal reasoning (e.g., mathematically enforced non-interference properties ensuring tainted inputs cannot influence privileged control flows through any channel, including error logs or side-effects) to provide provable security guarantees -- framing the current generation of defenses, including those evaluated in this SoK, as fundamentally lacking such formal guarantees. The Conclusion similarly states that 'future agent security must evolve beyond static benchmarks' to address the six identified root-cause architectural vulnerabilities.</t>
         </is>
       </c>
       <c r="F19" s="5" t="n"/>
@@ -3356,7 +3352,7 @@
       <c r="H19" s="5" t="n"/>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>77bd60b2f06f814a3f6ef85ec0c11b0176b0ceb1</t>
+          <t>66c8e83ed0fc215dc8be0e44715a692ef27f005b</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3362,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Trojan's Whisper: Stealthy Manipulation of OpenClaw through Injected Bootstrapped Guidance</t>
+          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -3381,7 +3377,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>This paper identifies and systematically characterizes 'Guidance Injection,' a novel attack vector against OpenClaw, an autonomous coding agent platform with an extensible skill ecosystem. Unlike traditional prompt injection, which relies on explicit malicious instructions that are typically detectable via static analysis or obvious behavioral anomalies, guidance injection exploits OpenClaw's agent:bootstrap lifecycle hook, through which third-party skills can inject 'bootstrap guidance' files into the agent's foundational reasoning context before any user interaction takes place. Because LLM-based agents exhibit a primacy effect (early context disproportionately influences subsequent outputs) and resolve ambiguous user instructions via in-context learning that recombines salient contextual patterns, an attacker who controls this early bootstrap context can reshape what the agent considers 'normal' or 'best-practice' behavior without ever issuing an overtly malicious command -- the attack succeeds precisely because the agent appears to be functioning normally, genuinely believing it is following legitimate operational guidelines, which makes detection substantially harder than conventional command-injection-style attacks. To study this systematically, the authors construct ORE-Bench, a realistic simulated developer workspace (complete with synthetic credentials, a Docker Compose homelab stack, and version control metadata) and build 26 malicious OpenClaw skills spanning 13 attack categories across three risk tiers: high-risk skills (H1-H10) use authoritative language framing unauthorized operations as routine maintenance; medium-risk skills (M1-M8) use narrative techniques that encourage the agent to infer dangerous recommendations without any explicit malicious command; and low-risk skills (L1-L8) inject marketing/branding content to demonstrate output-level manipulation susceptibility. These skills are tested against six frontier LLM backends under natural, ambiguous user prompts (e.g., requests to clean disk space or debug a trading bot), measuring both attack success rate (whether the agent autonomously performs the intended harmful action, often without explicit user confirmation) and stealth (evasion of both pre-installation marketplace scanners and post-deployment runtime monitoring), finding that because malicious intent is encoded in narrative operational guidance rather than executable code or explicit commands, both rule-based pattern scanners and LLM-based semantic detectors -- including a commercial platform actively used by the real OpenClaw marketplace -- systematically fail to recognize the threat, motivating the paper's proposed architectural mitigations centered on capability isolation, runtime policy enforcement, and transparent guidance provenance rather than content-filtering-based defenses.</t>
+          <t>This paper is the first Systematization of Knowledge (SoK) on IPI-centric LLM agent defense frameworks, providing a five-dimensional taxonomy (Technical Paradigm: detection, prompt engineering, fine-tuning, system design, runtime checking, policy enforcing; Intervention Stage: pre-/intra-/post-inference; Model Access: white-/black-box; Explainability: deterministic/probabilistic; Automation Level: full-/semi-automation), a comprehensive three-axis empirical evaluation (security via Attack Success Rate, utility via task success rate/false positive rate, and overhead via wall-clock time/token usage) of ten representative frameworks across three existing static benchmarks (AgentDojo, InjecAgent, ASB) with standardized model configurations, and a defense-failure root-cause analysis. From analyzing why representative frameworks fail under evaluation, the authors identify six recurring root causes of defense circumvention: imprecise access control over tool selection, imprecise access control over tool parameters, incomplete isolation of malicious information (e.g., porous planner/executor separation in system-design frameworks), judgment errors in checking/detecting auxiliary LLMs, inadequate coverage of static security policies, and poor generalization of fine-tuned defense LLMs. Building on this taxonomy of failure modes, the paper designs and demonstrates three novel logic-driven (not gradient-optimization-based) adaptive attacks, each targeting a specific root cause: Semantic-Masquerading IPI uses an LLM-driven pipeline to adapt injection payloads to use functionally similar or differently-parameterized tools that evade tool-selection/parameter access-control checks (validated via an 'Attack Success Judging' LLM since the adapted payloads break AgentDojo's static state-based ground truth); Cascading IPI structures the injected payload into head/body/end components with an if-then-else logic targeting auxiliary judge-LLM components used by runtime-checking frameworks (Task Shield, MELON), using 'judge' payload items to force a fake-benign auditor response and 'filter' items to force verbatim repetition that bypasses extraction/filtering; and Isolation-Breach IPI exploits overlooked information-flow channels (error messages, context feedback loops) to inject malicious intent directly into a system-design framework's architecturally 'trusted' planner component, demonstrated as a novel bypass of IsolateGPT.</t>
         </is>
       </c>
       <c r="F20" s="5" t="n"/>
@@ -3389,7 +3385,7 @@
       <c r="H20" s="5" t="n"/>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>77bd60b2f06f814a3f6ef85ec0c11b0176b0ceb1</t>
+          <t>66c8e83ed0fc215dc8be0e44715a692ef27f005b</t>
         </is>
       </c>
     </row>
@@ -3399,7 +3395,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Human-Interpretable Adversarial Prompt Attack on Large Language Models with Situational Context</t>
+          <t>FlashMem: Distilling Intrinsic Latent Memory via Computation Reuse</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -3422,7 +3418,7 @@
       <c r="H21" s="5" t="n"/>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>7cf2dd505b53e690ce0ff1fd15cc55f127841819</t>
+          <t>4e368119b5b8e809062d9da09b24941c705f9236</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3428,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Human-Interpretable Adversarial Prompt Attack on Large Language Models with Situational Context</t>
+          <t>FlashMem: Distilling Intrinsic Latent Memory via Computation Reuse</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -3447,7 +3443,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>ML/AI</t>
         </is>
       </c>
       <c r="F22" s="5" t="n"/>
@@ -3455,7 +3451,7 @@
       <c r="H22" s="5" t="n"/>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>7cf2dd505b53e690ce0ff1fd15cc55f127841819</t>
+          <t>4e368119b5b8e809062d9da09b24941c705f9236</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3461,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Human-Interpretable Adversarial Prompt Attack on Large Language Models with Situational Context</t>
+          <t>FlashMem: Distilling Intrinsic Latent Memory via Computation Reuse</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -3488,7 +3484,7 @@
       <c r="H23" s="5" t="n"/>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>7cf2dd505b53e690ce0ff1fd15cc55f127841819</t>
+          <t>4e368119b5b8e809062d9da09b24941c705f9236</t>
         </is>
       </c>
     </row>
@@ -3498,7 +3494,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Human-Interpretable Adversarial Prompt Attack on Large Language Models with Situational Context</t>
+          <t>FlashMem: Distilling Intrinsic Latent Memory via Computation Reuse</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -3513,7 +3509,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>attack</t>
+          <t>defense</t>
         </is>
       </c>
       <c r="F24" s="5" t="n"/>
@@ -3521,7 +3517,7 @@
       <c r="H24" s="5" t="n"/>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>7cf2dd505b53e690ce0ff1fd15cc55f127841819</t>
+          <t>4e368119b5b8e809062d9da09b24941c705f9236</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3527,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Human-Interpretable Adversarial Prompt Attack on Large Language Models with Situational Context</t>
+          <t>FlashMem: Distilling Intrinsic Latent Memory via Computation Reuse</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -3546,7 +3542,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>memory</t>
         </is>
       </c>
       <c r="F25" s="5" t="n"/>
@@ -3554,7 +3550,7 @@
       <c r="H25" s="5" t="n"/>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>7cf2dd505b53e690ce0ff1fd15cc55f127841819</t>
+          <t>4e368119b5b8e809062d9da09b24941c705f9236</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3560,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Human-Interpretable Adversarial Prompt Attack on Large Language Models with Situational Context</t>
+          <t>FlashMem: Distilling Intrinsic Latent Memory via Computation Reuse</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -3579,7 +3575,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>reasoning-corruption</t>
         </is>
       </c>
       <c r="F26" s="5" t="n"/>
@@ -3587,7 +3583,7 @@
       <c r="H26" s="5" t="n"/>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>7cf2dd505b53e690ce0ff1fd15cc55f127841819</t>
+          <t>4e368119b5b8e809062d9da09b24941c705f9236</t>
         </is>
       </c>
     </row>
@@ -3597,7 +3593,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Human-Interpretable Adversarial Prompt Attack on Large Language Models with Situational Context</t>
+          <t>FlashMem: Distilling Intrinsic Latent Memory via Computation Reuse</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -3612,7 +3608,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F27" s="5" t="n"/>
@@ -3620,7 +3616,7 @@
       <c r="H27" s="5" t="n"/>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>7cf2dd505b53e690ce0ff1fd15cc55f127841819</t>
+          <t>4e368119b5b8e809062d9da09b24941c705f9236</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3626,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Human-Interpretable Adversarial Prompt Attack on Large Language Models with Situational Context</t>
+          <t>FlashMem: Distilling Intrinsic Latent Memory via Computation Reuse</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -3653,7 +3649,7 @@
       <c r="H28" s="5" t="n"/>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>7cf2dd505b53e690ce0ff1fd15cc55f127841819</t>
+          <t>4e368119b5b8e809062d9da09b24941c705f9236</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3659,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Human-Interpretable Adversarial Prompt Attack on Large Language Models with Situational Context</t>
+          <t>FlashMem: Distilling Intrinsic Latent Memory via Computation Reuse</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -3686,7 +3682,7 @@
       <c r="H29" s="5" t="n"/>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>7cf2dd505b53e690ce0ff1fd15cc55f127841819</t>
+          <t>4e368119b5b8e809062d9da09b24941c705f9236</t>
         </is>
       </c>
     </row>
@@ -3696,7 +3692,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Human-Interpretable Adversarial Prompt Attack on Large Language Models with Situational Context</t>
+          <t>FlashMem: Distilling Intrinsic Latent Memory via Computation Reuse</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -3711,7 +3707,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>one-shot</t>
+          <t>session-persistent</t>
         </is>
       </c>
       <c r="F30" s="5" t="n"/>
@@ -3719,7 +3715,7 @@
       <c r="H30" s="5" t="n"/>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>7cf2dd505b53e690ce0ff1fd15cc55f127841819</t>
+          <t>4e368119b5b8e809062d9da09b24941c705f9236</t>
         </is>
       </c>
     </row>
@@ -3729,7 +3725,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Human-Interpretable Adversarial Prompt Attack on Large Language Models with Situational Context</t>
+          <t>FlashMem: Distilling Intrinsic Latent Memory via Computation Reuse</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -3744,7 +3740,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F31" s="5" t="n"/>
@@ -3752,7 +3748,7 @@
       <c r="H31" s="5" t="n"/>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>7cf2dd505b53e690ce0ff1fd15cc55f127841819</t>
+          <t>4e368119b5b8e809062d9da09b24941c705f9236</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3758,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Human-Interpretable Adversarial Prompt Attack on Large Language Models with Situational Context</t>
+          <t>FlashMem: Distilling Intrinsic Latent Memory via Computation Reuse</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -3777,7 +3773,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>N - no code or prompt release stated; built on the public PromptBench codebase and the public IMDB top-1000 Kaggle dataset (CC0)</t>
+          <t>No code, model, or dataset release URL (e.g., GitHub) is found in the extracted text.</t>
         </is>
       </c>
       <c r="F32" s="5" t="n"/>
@@ -3785,7 +3781,7 @@
       <c r="H32" s="5" t="n"/>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>7cf2dd505b53e690ce0ff1fd15cc55f127841819</t>
+          <t>4e368119b5b8e809062d9da09b24941c705f9236</t>
         </is>
       </c>
     </row>
@@ -3795,7 +3791,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Human-Interpretable Adversarial Prompt Attack on Large Language Models with Situational Context</t>
+          <t>FlashMem: Distilling Intrinsic Latent Memory via Computation Reuse</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3810,7 +3806,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>4-bit quantized Llama-2-7B-chat (suffix generation target); gpt-3.5-turbo-0125; gpt-4; phi-1.5; gemma-7b; Meta-Llama-3-8B. GPT-4 Judge used as the harmfulness scorer; gpt-4-0125-preview used to paraphrase prompts.</t>
+          <t>Instruct-tuned backbones from Qwen (Qwen 2.5-1.5B-Instruct, Qwen 3-4B-Instruct) and Llama (Llama 3.1-8B-Instruct, Llama 3.2-3B-Instruct), with a lightweight FlashMem Consolidator trained via SFT for each backbone while keeping the backbone frozen. Appendix experiments extend to larger Qwen3-14B and Qwen3-32B backbones and additional baselines (SoftCoT, LatentSeek, MemOS).</t>
         </is>
       </c>
       <c r="F33" s="5" t="n"/>
@@ -3818,7 +3814,7 @@
       <c r="H33" s="5" t="n"/>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>7cf2dd505b53e690ce0ff1fd15cc55f127841819</t>
+          <t>4e368119b5b8e809062d9da09b24941c705f9236</t>
         </is>
       </c>
     </row>
@@ -3828,7 +3824,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Human-Interpretable Adversarial Prompt Attack on Large Language Models with Situational Context</t>
+          <t>FlashMem: Distilling Intrinsic Latent Memory via Computation Reuse</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3843,7 +3839,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>IMDB top-1000 movies dataset (Kaggle, CC0), filtered to the crime genre, using Series_Title / Genre / Overview fields as situational context; only two crime movies are actually used in the reported attacks. Framework built on the PromptBench codebase. 22 successful prompt-response pairs collected as few-shot demonstrations.</t>
+          <t>Evaluated on six benchmarks spanning three task types: mathematical/scientific reasoning (GSM8K, MATH, GPQA), code generation (KodCode), and long-context summarization (BookSum, GovReport). Appendix evaluations additionally use LongBench v2 and RULER-64k (NIAH / multi-hop tracing) for long-context robustness testing.</t>
         </is>
       </c>
       <c r="F34" s="5" t="n"/>
@@ -3851,7 +3847,7 @@
       <c r="H34" s="5" t="n"/>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>7cf2dd505b53e690ce0ff1fd15cc55f127841819</t>
+          <t>4e368119b5b8e809062d9da09b24941c705f9236</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3857,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Human-Interpretable Adversarial Prompt Attack on Large Language Models with Situational Context</t>
+          <t>FlashMem: Distilling Intrinsic Latent Memory via Computation Reuse</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3876,7 +3872,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Converting a gradient-optimized nonsensical suffix into a fluent English phrase and wrapping the malicious request in a movie overview transfers across models: gpt-3.5-turbo-0125, gemma-7b and Meta-Llama-3-8B produce maximum-harmfulness (GPT-4 Judge score 5) responses from a single demonstration, phi-1.5 needs 2, and gpt-4 needs up to 10 demonstrations and tops out at score 4 - which the authors attribute to output-length limits rather than real robustness. The whole pipeline needs no gradient access at attack time.</t>
+          <t>FlashMem matches or exceeds the heavy-weight segregated latent-memory baseline MemGen across most tasks while reducing inference latency by up to 5x. On Qwen 2.5 1.5B, FlashMem reaches 70.09% GSM8K accuracy (vs. MemGen 70.54%, Vanilla 65.12%) and 50.16% on MATH, exceeding MemGen (46.55%); on Llama 3.2 3B, FlashMem surpasses MemGen on the challenging MATH dataset (48.05% vs. 45.17%), suggesting the shared-KV design better preserves mathematical priors in smaller parametric spaces. On the larger Qwen3-14B/32B backbones (Appendix), FlashMem remains close to or exceeds MemGen (e.g., Qwen3-14B: FlashMem 92.18 vs. MemGen 92.24 on one reasoning metric, and FlashMem 68.72 vs. MemGen 67.81 on another). Efficiency benchmarking (Table 3) shows FlashMem maintains a peak VRAM profile nearly identical to the Vanilla baseline (31.44 GB vs. 31.21 GB), whereas MemGen incurs substantially higher overhead, since FlashMem eliminates redundant re-encoding by attending directly to the backbone's frozen KV cache rather than using an independent encoder. An ablation on Consolidator depth (Table 4) shows performance saturates quickly, with a single-layer consolidator already achieving strong results. An entropy-reduction analysis (Table 5) shows FlashMem's Cognitive Monitor-triggered memory consolidation produces a measurable reduction in attention entropy (model uncertainty) at trigger points compared to the Vanilla baseline, which shows sustained or rising entropy at the same moments of confusion.</t>
         </is>
       </c>
       <c r="F35" s="5" t="n"/>
@@ -3884,7 +3880,7 @@
       <c r="H35" s="5" t="n"/>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>7cf2dd505b53e690ce0ff1fd15cc55f127841819</t>
+          <t>4e368119b5b8e809062d9da09b24941c705f9236</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3890,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Human-Interpretable Adversarial Prompt Attack on Large Language Models with Situational Context</t>
+          <t>FlashMem: Distilling Intrinsic Latent Memory via Computation Reuse</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3909,7 +3905,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>None - no defense or attack baseline is run head-to-head; the work is positioned qualitatively against gradient-based nonsensical suffix attacks (Zou et al., Andriushchenko et al.) and many-shot jailbreaking (Anil et al.), whose suffix it reuses as a starting point</t>
+          <t>Compared against three paradigms: (1) direct generation baselines Vanilla and CoT-SC (self-consistency chain-of-thought); (2) KV-cache compression baseline SnapKV; and (3) generative latent memory baseline MemGen (the primary heavy-weight comparator, using independent/segregated encoder modules). Appendix experiments add further latent-memory baselines SoftCoT, LatentSeek, and MemOS, plus matched SFT controls trained on the same trajectories.</t>
         </is>
       </c>
       <c r="F36" s="5" t="n"/>
@@ -3917,7 +3913,7 @@
       <c r="H36" s="5" t="n"/>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>7cf2dd505b53e690ce0ff1fd15cc55f127841819</t>
+          <t>4e368119b5b8e809062d9da09b24941c705f9236</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3923,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Human-Interpretable Adversarial Prompt Attack on Large Language Models with Situational Context</t>
+          <t>FlashMem: Distilling Intrinsic Latent Memory via Computation Reuse</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3942,7 +3938,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>An attacker with only black-box API access and no gradient access at attack time, who can craft the full user prompt. One-time white-box access to a small open model (4-bit Llama-2-7B) is used to seed the initial adversarial suffix; from there GPT-3.5 rewrites it into fluent text and the attack transfers to proprietary models. The attacker's aim is to make the prompt look innocuous to human or entropy-based review.</t>
+          <t>N/A - non-adversarial. The incidental failure mode of interest is the architectural statelessness of LLMs: because LLMs map inputs to outputs based on static frozen parameters without retaining persistent internal state, agents are forced to discard rich intermediate reasoning representations after every inference step and redundantly reprocess historical context to maintain long-horizon coherence, creating both an information-preservation problem and a computational-efficiency bottleneck (existing latent-memory solutions compound this via architectural segregation -- auxiliary encoders decoupled from the reasoning backbone -- causing duplicate forward passes and disjoint memory buffers).</t>
         </is>
       </c>
       <c r="F37" s="5" t="n"/>
@@ -3950,7 +3946,7 @@
       <c r="H37" s="5" t="n"/>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>7cf2dd505b53e690ce0ff1fd15cc55f127841819</t>
+          <t>4e368119b5b8e809062d9da09b24941c705f9236</t>
         </is>
       </c>
     </row>
@@ -3960,7 +3956,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Human-Interpretable Adversarial Prompt Attack on Large Language Models with Situational Context</t>
+          <t>FlashMem: Distilling Intrinsic Latent Memory via Computation Reuse</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3975,7 +3971,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Authors state the human-interpretable adversarial insertion is rigid - changing its wording destroys the attack - and that the success rate is still inadequate against newer models such as Claude 3. They also note gemma-7b and Llama-3-8B do not reliably follow instructions, and that proprietary API models change over time so a response obtained today may not reproduce tomorrow.</t>
+          <t>The paper has an explicit 'Limitations' section stating two limitations: (1) the current framework is optimized for textual and code-based tasks and has not yet been extended to multimodal settings; given the increasing prominence of Vision-Language Models (VLMs), adapting FlashMem's Shared-KV paradigm to handle multi-sensory inputs and visual tokens is identified as a promising future direction; (2) while the paper validates FlashMem's effectiveness on representative open-source models (Qwen and Llama families up to 32B), exploration of this intrinsic memory mechanism on ultra-large-scale foundation models is left unaddressed (the text is truncated at this point but frames scale as an open validation gap).</t>
         </is>
       </c>
       <c r="F38" s="5" t="n"/>
@@ -3983,7 +3979,7 @@
       <c r="H38" s="5" t="n"/>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>7cf2dd505b53e690ce0ff1fd15cc55f127841819</t>
+          <t>4e368119b5b8e809062d9da09b24941c705f9236</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3989,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Human-Interpretable Adversarial Prompt Attack on Large Language Models with Situational Context</t>
+          <t>FlashMem: Distilling Intrinsic Latent Memory via Computation Reuse</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -4008,7 +4004,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Proposes a gradient-free way to turn a nonsensical adversarial suffix into a fluent, human-readable jailbreak prompt by combining it with situational context harvested from movie plot overviews. Generates the initial suffix with an existing random-search method on a quantized Llama-2-7B, has GPT-3.5-turbo rewrite it into a meaningful English sentence, then assembles a template of malicious prompt + adversarial insertion + IMDB crime-movie overview. Extends the attack to other models by collecting full prompt-response pairs that scored 5 on a GPT-4 harmfulness judge and replaying them as few-shot chain-of-thought demonstrations. Reports the minimum number of demonstrations needed per model across six open and proprietary LLMs. The evaluation is small-scale - two movies, one suffix, five target models, no attack-success-rate statistics or defense baselines.</t>
+          <t>This paper proposes FlashMem, a framework for distilling intrinsic latent memory directly from an LLM agent's transient reasoning states via computation reuse, addressing architectural segregation and computational redundancy in prior generative latent-memory approaches (e.g., MemGen, SoftCoT), which rely on independent auxiliary encoders or adapters decoupled from the reasoning backbone, forcing duplicate forward passes and disjoint memory buffers. FlashMem instead uses the backbone's last hidden state as a compact, empirically effective summary of the interaction history (motivated by prior findings that final-layer representations preserve rich trajectory information), projecting it via a two-layer MLP into an initial latent embedding that seeds a lightweight 'Memory Consolidator' -- a stacked-decoder module using a projection-free cross-attention mechanism that discards trainable Key/Value projection matrices entirely and instead attends directly to the frozen backbone's accumulated KV cache (only the Query projection is learned), minimizing parameter count, VRAM usage, and eliminating redundant re-parameterization/re-encoding of context. The resulting synthesized memory embeddings are soft-injected into the backbone's input stream (fed through the backbone to generate corresponding KV pairs appended to the active cache) to guide subsequent reasoning, rather than being concatenated as raw tokens. A complementary parameter-free 'Cognitive Monitor,' grounded in the correlation between attention entropy and model uncertainty, adaptively triggers memory consolidation only when the agent exhibits high epistemic uncertainty/internal confusion, avoiding wasteful computation from consolidating on every step. The Consolidator is trained via supervised fine-tuning per backbone while the backbone itself remains frozen, and weight inheritance techniques are used to address the semantic-alignment challenge of training a lightweight module to collaborate with a frozen, massive backbone.</t>
         </is>
       </c>
       <c r="F39" s="5" t="n"/>
@@ -4016,7 +4012,7 @@
       <c r="H39" s="5" t="n"/>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>7cf2dd505b53e690ce0ff1fd15cc55f127841819</t>
+          <t>4e368119b5b8e809062d9da09b24941c705f9236</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4022,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
+          <t>Poisoning Retrieval Corpora by Injecting Adversarial Passages</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -4049,7 +4045,7 @@
       <c r="H40" s="5" t="n"/>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>ee745d4c5e9ff890731866f54b6b333bb3a4eb57</t>
+          <t>e3a49a110801fd961db887f8af1239cc79b55a5b</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4055,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
+          <t>Poisoning Retrieval Corpora by Injecting Adversarial Passages</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -4074,7 +4070,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="F41" s="5" t="n"/>
@@ -4082,7 +4078,7 @@
       <c r="H41" s="5" t="n"/>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>ee745d4c5e9ff890731866f54b6b333bb3a4eb57</t>
+          <t>e3a49a110801fd961db887f8af1239cc79b55a5b</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4088,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
+          <t>Poisoning Retrieval Corpora by Injecting Adversarial Passages</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -4115,7 +4111,7 @@
       <c r="H42" s="5" t="n"/>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>ee745d4c5e9ff890731866f54b6b333bb3a4eb57</t>
+          <t>e3a49a110801fd961db887f8af1239cc79b55a5b</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4121,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
+          <t>Poisoning Retrieval Corpora by Injecting Adversarial Passages</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -4140,7 +4136,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>defense</t>
+          <t>attack</t>
         </is>
       </c>
       <c r="F43" s="5" t="n"/>
@@ -4148,7 +4144,7 @@
       <c r="H43" s="5" t="n"/>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>ee745d4c5e9ff890731866f54b6b333bb3a4eb57</t>
+          <t>e3a49a110801fd961db887f8af1239cc79b55a5b</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4154,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
+          <t>Poisoning Retrieval Corpora by Injecting Adversarial Passages</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -4173,7 +4169,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>cross-modal</t>
+          <t>RAG</t>
         </is>
       </c>
       <c r="F44" s="5" t="n"/>
@@ -4181,7 +4177,7 @@
       <c r="H44" s="5" t="n"/>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>ee745d4c5e9ff890731866f54b6b333bb3a4eb57</t>
+          <t>e3a49a110801fd961db887f8af1239cc79b55a5b</t>
         </is>
       </c>
     </row>
@@ -4191,7 +4187,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
+          <t>Poisoning Retrieval Corpora by Injecting Adversarial Passages</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -4206,7 +4202,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>silent-corruption</t>
         </is>
       </c>
       <c r="F45" s="5" t="n"/>
@@ -4214,7 +4210,7 @@
       <c r="H45" s="5" t="n"/>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>ee745d4c5e9ff890731866f54b6b333bb3a4eb57</t>
+          <t>e3a49a110801fd961db887f8af1239cc79b55a5b</t>
         </is>
       </c>
     </row>
@@ -4224,7 +4220,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
+          <t>Poisoning Retrieval Corpora by Injecting Adversarial Passages</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4247,7 +4243,7 @@
       <c r="H46" s="5" t="n"/>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>ee745d4c5e9ff890731866f54b6b333bb3a4eb57</t>
+          <t>e3a49a110801fd961db887f8af1239cc79b55a5b</t>
         </is>
       </c>
     </row>
@@ -4257,7 +4253,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
+          <t>Poisoning Retrieval Corpora by Injecting Adversarial Passages</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4272,7 +4268,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F47" s="5" t="n"/>
@@ -4280,7 +4276,7 @@
       <c r="H47" s="5" t="n"/>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>ee745d4c5e9ff890731866f54b6b333bb3a4eb57</t>
+          <t>e3a49a110801fd961db887f8af1239cc79b55a5b</t>
         </is>
       </c>
     </row>
@@ -4290,7 +4286,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
+          <t>Poisoning Retrieval Corpora by Injecting Adversarial Passages</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4313,7 +4309,7 @@
       <c r="H48" s="5" t="n"/>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>ee745d4c5e9ff890731866f54b6b333bb3a4eb57</t>
+          <t>e3a49a110801fd961db887f8af1239cc79b55a5b</t>
         </is>
       </c>
     </row>
@@ -4323,7 +4319,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
+          <t>Poisoning Retrieval Corpora by Injecting Adversarial Passages</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4338,7 +4334,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>one-shot</t>
+          <t>cross-session-dormant</t>
         </is>
       </c>
       <c r="F49" s="5" t="n"/>
@@ -4346,7 +4342,7 @@
       <c r="H49" s="5" t="n"/>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>ee745d4c5e9ff890731866f54b6b333bb3a4eb57</t>
+          <t>e3a49a110801fd961db887f8af1239cc79b55a5b</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4352,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
+          <t>Poisoning Retrieval Corpora by Injecting Adversarial Passages</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4379,7 +4375,7 @@
       <c r="H50" s="5" t="n"/>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>ee745d4c5e9ff890731866f54b6b333bb3a4eb57</t>
+          <t>e3a49a110801fd961db887f8af1239cc79b55a5b</t>
         </is>
       </c>
     </row>
@@ -4389,7 +4385,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
+          <t>Poisoning Retrieval Corpora by Injecting Adversarial Passages</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4404,7 +4400,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Code is publicly released at https://github.com/xbmxb/EnvDistraction, including the simulated distraction dataset (1198 samples across four subsets: Pop-up box, Search, Recommendation, Chat), the data construction pipeline (Algorithm 1), and the three working-pattern evaluation prompts/harness used across ten MLLM agents.</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F51" s="5" t="n"/>
@@ -4412,7 +4408,7 @@
       <c r="H51" s="5" t="n"/>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>ee745d4c5e9ff890731866f54b6b333bb3a4eb57</t>
+          <t>e3a49a110801fd961db887f8af1239cc79b55a5b</t>
         </is>
       </c>
     </row>
@@ -4422,7 +4418,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
+          <t>Poisoning Retrieval Corpora by Injecting Adversarial Passages</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4437,7 +4433,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Ten MLLMs: generalist black-box agents GPT-4v, GPT-4o, GLM-4v, Qwen-VL-plus, and Claude-Sonnet-3.5; open-source generalist MLLMs Qwen-VL-chat-7B, MiniCPM-Llama3-V2.5, and LLaVa-v1.6-34B; and specialist GUI agents CogAgent-chat and SeeClick. For the faithfulness-improvement experiment, Llama-3.1-8B-Instruct is fine-tuned with LoRA via DPO.</t>
+          <t>Dense retrievers: Contriever (pre-trained/unsupervised), Contriever-ms (fine-tuned on MS MARCO), DPR-nq (trained on NQ), DPR-mul (trained on multiple datasets), ANCE; multi-vector retriever ColBERT (v1, pre-trained on MS MARCO); sparse retriever BM25 (robustness check)</t>
         </is>
       </c>
       <c r="F52" s="5" t="n"/>
@@ -4445,7 +4441,7 @@
       <c r="H52" s="5" t="n"/>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>ee745d4c5e9ff890731866f54b6b333bb3a4eb57</t>
+          <t>e3a49a110801fd961db887f8af1239cc79b55a5b</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4451,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
+          <t>Poisoning Retrieval Corpora by Injecting Adversarial Passages</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4470,7 +4466,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>A self-constructed simulated dataset of 1198 GUI screenshots across four distraction scenarios: Pop-up box (662 samples: 208+220+234 across 3 layout templates), Search (250 samples, built on real Google Search API results with GPT-4-generated fake results inserted), Recommendation (176 samples, using a BM25 retriever over Amazon Reviews with a GPT-4-fabricated fake product inserted), and Chat (110 samples, built on Discord chat rooms with dialogue-based distractions). A DPO training pseudo-dataset sampled from Alpaca is also used for the faithfulness-improvement experiment.</t>
+          <t>Natural Questions (NQ) and MS MARCO as primary training/test sets; transfer evaluated on 7 unseen BEIR benchmark domains: HotpotQA, FiQA (finance), Quora, FEVER, TREC-COVID (bio-medical), ArguAna, SCIDOCS</t>
         </is>
       </c>
       <c r="F53" s="5" t="n"/>
@@ -4478,7 +4474,7 @@
       <c r="H53" s="5" t="n"/>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>ee745d4c5e9ff890731866f54b6b333bb3a4eb57</t>
+          <t>e3a49a110801fd961db887f8af1239cc79b55a5b</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4484,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
+          <t>Poisoning Retrieval Corpora by Injecting Adversarial Passages</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4503,7 +4499,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Every evaluated MLLM is measurably susceptible to environmental distraction: the strongest generalist model, GPT-4o, still produces distracted actions (Accdist) in 9.09% of direct-prompt cases overall, and the best specialist agent SeeClick is distracted 6.84% of the time, while weaker models like Qwen-VL-plus are distracted up to 76.92% under CoT prompting on the Pop-up box subset. Providing explicit action annotations to reduce perception burden often worsens faithfulness rather than helping -- e.g., GPT-4v's Accdist rises from 6.57% (direct prompt) to 16.26% (action annotation) on Pop-up box, and SeeClick's distraction rate jumps from 2.17% to 12.42%. Under active adversarial environment injection (rewriting pop-up buttons), GPT-4o's Accdist rises from 5.00% baseline to 33.33-40.00% (attack success rate 6/8 goal cases) and GLM-4v's rises from 60.45% to as high as 70.83% (ASR 8/8). A DPO-based faithfulness fine-tuning of Llama-3.1-8B-Instruct improves Chat-subset Accgold from 31.8% (baseline) to 40.9%, but yields only modest gains on Pop-up box (37.0% to 37.3%).</t>
+          <t>As few as 1-10 adversarial passages fool the unsupervised Contriever model on &gt;75-90% of queries on NQ/MS MARCO; supervised retrievers (DPR, ANCE) are harder to attack but success rate still exceeds 50% with up to 500 injected passages (&lt;0.02% of the corpus). Adversarial passages generated on NQ/MS MARCO transfer effectively to 7 unseen out-of-domain corpora (e.g. 94.1% success rate on FiQA, a financial QA domain), showing the attack generalizes beyond the training distribution and is not simply due to train/test query overlap. The attack also works against the multi-vector retriever ColBERT (20.1% success with 50 x 250-token passages) though it is more robust to single-token perturbations; a targeted-misinformation case study shows harmful content can be embedded in the passages while maintaining attack effectiveness (11.7-59.6% success with 1-10 passages); sparse BM25 retrieval is essentially immune (0% attack success, no transfer from dense-retriever attacks) and passage-embedding-norm clipping is shown to reduce attack success by 99.4% at a small (6%) cost to normal retrieval accuracy.</t>
         </is>
       </c>
       <c r="F54" s="5" t="n"/>
@@ -4511,7 +4507,7 @@
       <c r="H54" s="5" t="n"/>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>ee745d4c5e9ff890731866f54b6b333bb3a4eb57</t>
+          <t>e3a49a110801fd961db887f8af1239cc79b55a5b</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4517,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
+          <t>Poisoning Retrieval Corpora by Injecting Adversarial Passages</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4536,7 +4532,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>The paper's own three working patterns (Direct prompt, CoT prompt, Action annotation) function as internal ablations/baselines against each other, isolating the effect of perception level on faithfulness. The DPO faithfulness-improvement method is compared against an untrained baseline model and a preference-aware prompting variant. No external prior defense system is used as a baseline since this is largely a novel-phenomenon measurement paper rather than a defense paper.</t>
+          <t>Comparison across five dense retriever architectures (Contriever, Contriever-ms, DPR-nq, DPR-mul, ANCE) and one multi-vector retriever (ColBERT) as targets; BM25 (sparse) as a robustness/non-transferability check; ablations over number of adversarial passages (1/10/50/500), passage length (10/20/50/100 tokens), and passage initialization (natural text vs. random [MASK] tokens)</t>
         </is>
       </c>
       <c r="F55" s="5" t="n"/>
@@ -4544,7 +4540,7 @@
       <c r="H55" s="5" t="n"/>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>ee745d4c5e9ff890731866f54b6b333bb3a4eb57</t>
+          <t>e3a49a110801fd961db887f8af1239cc79b55a5b</t>
         </is>
       </c>
     </row>
@@ -4554,7 +4550,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
+          <t>Poisoning Retrieval Corpora by Injecting Adversarial Passages</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4569,7 +4565,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Primarily non-adversarial: the paper's core setting is 'benign but risky' -- user and agent are both benign and non-malicious, and the environment, while not adversarial, naturally contains irrelevant or misleading content (ads, pop-ups, fake search/recommendation results, chat logs) that can unintentionally distract the GUI agent from the user's true goal. Section 5.1 additionally introduces an explicit adversarial extension (environment injection), where an attacker who can eavesdrop on the user's goal and modify the GUI environment (e.g., man-in-the-middle rewriting of HTML pop-up button text/labels) actively crafts distractions to mislead the agent into taking an unintended action, without altering the user's or agent's own behavior.</t>
+          <t>A malicious user with no special system access can inject a small number of adversarial passages (generated via a HotFlip-style gradient-based discrete-token optimization against a set of training queries) into an open, editable retrieval corpus (e.g. Wikipedia, Reddit, or other open-access platforms), with the goal of having dense retrieval models return these passages among top-k results for a broad set of unseen queries, including out-of-domain queries the attacker never explicitly optimized for - a form of black-hat SEO / retrieval corpus poisoning that can be used to spread misinformation or degrade user experience.</t>
         </is>
       </c>
       <c r="F56" s="5" t="n"/>
@@ -4577,7 +4573,7 @@
       <c r="H56" s="5" t="n"/>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>ee745d4c5e9ff890731866f54b6b333bb3a4eb57</t>
+          <t>e3a49a110801fd961db887f8af1239cc79b55a5b</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4583,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
+          <t>Poisoning Retrieval Corpora by Injecting Adversarial Passages</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4602,7 +4598,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>The paper has an explicit 'Limitations' section with three points: (i) the work does not itself develop or fully validate faithfulness-improvement solutions beyond a preliminary DPO experiment, leaving further exploration of faithfulness-aligned pre-training, contextual/instruction correlation modeling, action-consequence prediction, and human-feedback incorporation to future work; (ii) although the dataset simulates realistic distractions using an LLM-driven pipeline, it does not cover all possible vulnerable scenarios, and future work could build a more comprehensive distraction set via crowd-sourced annotation of real-world websites; (iii) the study quantifies unfaithfulness only via objective action-type accuracy and does not investigate the severity or downstream consequences of distracted actions, which is left for future work.</t>
+          <t>The attack is computationally expensive - for each group of queries, the optimization must be run independently on a single GPU to generate one adversarial passage, and the authors explicitly note more efficient methods for generating multiple passages are needed as future work; the study is scoped specifically to corpus poisoning (injecting new passages) and does not investigate other attack surfaces such as maliciously manipulating user queries; adversarial passages are highly unnatural text (detectable via language-model likelihood filtering, e.g. GPT-2 scoring) and have anomalously high embedding L2-norms (detectable/defensible via norm clipping), so the specific attack as presented is not stealthy against these two simple defenses, though the authors caution a stronger attacker could incorporate natural-language priors to evade likelihood-based detection.</t>
         </is>
       </c>
       <c r="F57" s="5" t="n"/>
@@ -4610,7 +4606,7 @@
       <c r="H57" s="5" t="n"/>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>ee745d4c5e9ff890731866f54b6b333bb3a4eb57</t>
+          <t>e3a49a110801fd961db887f8af1239cc79b55a5b</t>
         </is>
       </c>
     </row>
@@ -4620,7 +4616,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
+          <t>Poisoning Retrieval Corpora by Injecting Adversarial Passages</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4635,7 +4631,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>This paper studies whether multimodal GUI agents remain faithful to user goals when operating in benign but content-rich environments that contain irrelevant distractions (ads, pop-ups, fake search/recommendation results, misleading chat messages) -- explicitly distinguishing this from adversarial prompt injection or jailbreak settings, since both the user and the agent are assumed benign. The authors build a 1198-sample simulated dataset across four scenario subsets (Pop-up box, Search, Recommendation, Chat) via an LLM-driven construction pipeline that inserts distracting but non-malicious content into realistic GUI screenshots, then evaluate 10 MLLM-based GUI agents (5 generalist API models, 3 open-source generalist models, 2 specialist GUI agents) under three working patterns offering progressively more explicit perception support (raw image only, chain-of-thought over the image, and explicit action-space annotations). They find universal susceptibility to distraction across all models and patterns, that stronger perceptual/action-space information does not reliably reduce distraction and can even increase it, and that faithfulness and helpfulness are correlated rather than in tension for the strongest models. The paper further demonstrates an adversarial 'environment injection' attack -- rewriting pop-up button semantics to be ambiguous or emotionally persuasive -- that substantially raises distraction rates (up to 8/8 attack success against GLM-4v), and proposes a preliminary faithfulness-improvement method using a special input token plus DPO fine-tuning (on Llama-3.1-8B-Instruct) to teach the model to prioritize the user's goal channel over environmental feedback, yielding modest to substantial gains depending on the scenario.</t>
+          <t>Introduces a corpus poisoning attack against dense retrieval systems, in which a malicious user generates a small number of adversarial passages (via gradient-based discrete-token optimization, adapted from HotFlip, that maximizes similarity to a training set of queries) and injects them into a retrieval corpus to mislead dense retrievers into returning them among top-k results - a stronger, broad-query-generalizing threat model than prior single-query adversarial-passage attacks. The attack is evaluated on five dense retrieval architectures (unsupervised Contriever, supervised Contriever-ms/DPR-nq/DPR-mul/ANCE) and shown to be highly effective, especially against unsupervised retrievers (&gt;75% success with a single passage), and to transfer surprisingly well to seven unseen out-of-domain retrieval corpora and tasks from the BEIR benchmark despite being optimized only on NQ or MS MARCO training queries; the attack also partially generalizes to the multi-vector ColBERT retriever, and a case study shows the injected passages can carry targeted misinformation while remaining effective. The paper further shows sparse BM25 retrieval is immune to the attack (and that dense-retriever adversarial passages do not transfer to it), and evaluates two candidate defenses - language-model likelihood filtering and passage-embedding-norm clipping - finding norm clipping substantially reduces attack success with minor cost to normal retrieval performance.</t>
         </is>
       </c>
       <c r="F58" s="5" t="n"/>
@@ -4643,7 +4639,7 @@
       <c r="H58" s="5" t="n"/>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>ee745d4c5e9ff890731866f54b6b333bb3a4eb57</t>
+          <t>e3a49a110801fd961db887f8af1239cc79b55a5b</t>
         </is>
       </c>
     </row>
@@ -4653,7 +4649,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Enterprise Secure AI Execution Engine: A Zero-Trust Security Gateway for Enterprise LLM Systems</t>
+          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4676,7 +4672,7 @@
       <c r="H59" s="5" t="n"/>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>1ce4b21dda6721f1c94b63ab1b93144a87a9b0ad</t>
+          <t>arxiv:2606.25514</t>
         </is>
       </c>
     </row>
@@ -4686,7 +4682,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Enterprise Secure AI Execution Engine: A Zero-Trust Security Gateway for Enterprise LLM Systems</t>
+          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4701,7 +4697,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>ML/AI</t>
         </is>
       </c>
       <c r="F60" s="5" t="n"/>
@@ -4709,7 +4705,7 @@
       <c r="H60" s="5" t="n"/>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>1ce4b21dda6721f1c94b63ab1b93144a87a9b0ad</t>
+          <t>arxiv:2606.25514</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4715,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Enterprise Secure AI Execution Engine: A Zero-Trust Security Gateway for Enterprise LLM Systems</t>
+          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4742,7 +4738,7 @@
       <c r="H61" s="5" t="n"/>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>1ce4b21dda6721f1c94b63ab1b93144a87a9b0ad</t>
+          <t>arxiv:2606.25514</t>
         </is>
       </c>
     </row>
@@ -4752,7 +4748,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Enterprise Secure AI Execution Engine: A Zero-Trust Security Gateway for Enterprise LLM Systems</t>
+          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4767,7 +4763,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>defense</t>
+          <t>both</t>
         </is>
       </c>
       <c r="F62" s="5" t="n"/>
@@ -4775,7 +4771,7 @@
       <c r="H62" s="5" t="n"/>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>1ce4b21dda6721f1c94b63ab1b93144a87a9b0ad</t>
+          <t>arxiv:2606.25514</t>
         </is>
       </c>
     </row>
@@ -4785,7 +4781,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Enterprise Secure AI Execution Engine: A Zero-Trust Security Gateway for Enterprise LLM Systems</t>
+          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -4800,7 +4796,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>tool-output</t>
         </is>
       </c>
       <c r="F63" s="5" t="n"/>
@@ -4808,7 +4804,7 @@
       <c r="H63" s="5" t="n"/>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>1ce4b21dda6721f1c94b63ab1b93144a87a9b0ad</t>
+          <t>arxiv:2606.25514</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4814,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Enterprise Secure AI Execution Engine: A Zero-Trust Security Gateway for Enterprise LLM Systems</t>
+          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -4833,7 +4829,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>data-exfiltration</t>
+          <t>silent-corruption</t>
         </is>
       </c>
       <c r="F64" s="5" t="n"/>
@@ -4841,7 +4837,7 @@
       <c r="H64" s="5" t="n"/>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>1ce4b21dda6721f1c94b63ab1b93144a87a9b0ad</t>
+          <t>arxiv:2606.25514</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4847,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Enterprise Secure AI Execution Engine: A Zero-Trust Security Gateway for Enterprise LLM Systems</t>
+          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -4866,7 +4862,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F65" s="5" t="n"/>
@@ -4874,7 +4870,7 @@
       <c r="H65" s="5" t="n"/>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>1ce4b21dda6721f1c94b63ab1b93144a87a9b0ad</t>
+          <t>arxiv:2606.25514</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4880,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Enterprise Secure AI Execution Engine: A Zero-Trust Security Gateway for Enterprise LLM Systems</t>
+          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -4899,7 +4895,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F66" s="5" t="n"/>
@@ -4907,7 +4903,7 @@
       <c r="H66" s="5" t="n"/>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>1ce4b21dda6721f1c94b63ab1b93144a87a9b0ad</t>
+          <t>arxiv:2606.25514</t>
         </is>
       </c>
     </row>
@@ -4917,7 +4913,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Enterprise Secure AI Execution Engine: A Zero-Trust Security Gateway for Enterprise LLM Systems</t>
+          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -4932,7 +4928,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>ingestion</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F67" s="5" t="n"/>
@@ -4940,7 +4936,7 @@
       <c r="H67" s="5" t="n"/>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>1ce4b21dda6721f1c94b63ab1b93144a87a9b0ad</t>
+          <t>arxiv:2606.25514</t>
         </is>
       </c>
     </row>
@@ -4950,7 +4946,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Enterprise Secure AI Execution Engine: A Zero-Trust Security Gateway for Enterprise LLM Systems</t>
+          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -4965,7 +4961,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>one-shot</t>
+          <t>session-persistent</t>
         </is>
       </c>
       <c r="F68" s="5" t="n"/>
@@ -4973,7 +4969,7 @@
       <c r="H68" s="5" t="n"/>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>1ce4b21dda6721f1c94b63ab1b93144a87a9b0ad</t>
+          <t>arxiv:2606.25514</t>
         </is>
       </c>
     </row>
@@ -4983,7 +4979,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Enterprise Secure AI Execution Engine: A Zero-Trust Security Gateway for Enterprise LLM Systems</t>
+          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -4998,7 +4994,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F69" s="5" t="n"/>
@@ -5006,7 +5002,7 @@
       <c r="H69" s="5" t="n"/>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>1ce4b21dda6721f1c94b63ab1b93144a87a9b0ad</t>
+          <t>arxiv:2606.25514</t>
         </is>
       </c>
     </row>
@@ -5016,7 +5012,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Enterprise Secure AI Execution Engine: A Zero-Trust Security Gateway for Enterprise LLM Systems</t>
+          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5031,7 +5027,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Code/artifact released: 'Artifact, 2026. URL https://github.com/Intelligent-CAT-Lab/icat-agent' cited as reference [7] and referenced directly in the Concluding Remarks ('Our artifact is available at [7]').</t>
         </is>
       </c>
       <c r="F70" s="5" t="n"/>
@@ -5039,7 +5035,7 @@
       <c r="H70" s="5" t="n"/>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>1ce4b21dda6721f1c94b63ab1b93144a87a9b0ad</t>
+          <t>arxiv:2606.25514</t>
         </is>
       </c>
     </row>
@@ -5049,7 +5045,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Enterprise Secure AI Execution Engine: A Zero-Trust Security Gateway for Enterprise LLM Systems</t>
+          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5064,7 +5060,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>None - security gateway pipeline (RBAC, deterministic tokenization, adversarial prompt detection) tested upstream of an unspecified LLM; compared against a baseline unsecured LLM deployment, no specific downstream LLM identified</t>
+          <t>On SWE-bench Verified: MiniMax M2.5 (strong frontier model) and GPT-5-mini (mid-tier model). On SWE-bench Pro: GPT-5.4-xhigh (best-performing leaderboard model) and Claude Sonnet 4.5 (mid-tier model). All baselines are run with the same underlying models as icat-agent for controlled comparison.</t>
         </is>
       </c>
       <c r="F71" s="5" t="n"/>
@@ -5072,7 +5068,7 @@
       <c r="H71" s="5" t="n"/>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>1ce4b21dda6721f1c94b63ab1b93144a87a9b0ad</t>
+          <t>arxiv:2606.25514</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5078,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Enterprise Secure AI Execution Engine: A Zero-Trust Security Gateway for Enterprise LLM Systems</t>
+          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5097,7 +5093,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>300-prompt adversarial subset derived from the HackAPrompt benchmark, spanning 5 attack categories (Credential Extraction, Role Escalation Attempts, Encoded Payload Injection, SQL-like Data Extraction, Internal Document Access Requests; 60 prompts each), tested under 3 RBAC roles (Admin, Employee, Intern)</t>
+          <t>SWE-bench Verified (500 human-validated real-world GitHub issue instances, the most widely adopted agentic issue-resolution benchmark) and SWE-bench Pro (long-horizon, multi-language software engineering problems, designed for more complex repairs than Verified). Evaluated across difficulty levels (easy/medium/hard for Verified based on human-fixing-time labels; grouped by number of golden-patch-modified files for Pro), across four programming languages (Python, TypeScript, JavaScript, Go) for Pro, and across issue-description quality groups (high vs. low quality, determined by icat-agent's own rubric-based checker).</t>
         </is>
       </c>
       <c r="F72" s="5" t="n"/>
@@ -5105,7 +5101,7 @@
       <c r="H72" s="5" t="n"/>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>1ce4b21dda6721f1c94b63ab1b93144a87a9b0ad</t>
+          <t>arxiv:2606.25514</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5111,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Enterprise Secure AI Execution Engine: A Zero-Trust Security Gateway for Enterprise LLM Systems</t>
+          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5130,7 +5126,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>The proposed Secure AI Execution Engine achieves 98.7% block accuracy and 99.3% tokenization accuracy with a 1.3% false-allow rate, versus 82%/75%/12% for an unsecured baseline LLM deployment, at a modest latency cost (18ms vs. 12ms).</t>
+          <t>icat-agent consistently outperforms baseline scaffolds across all settings. On SWE-bench Verified, it resolves 79.4% (MiniMax M2.5) and 64.6% (GPT-5-mini) of issues, improving over mini-SWE-agent by 3.6 and 8.4 percentage points respectively. On SWE-bench Pro, it resolves 62.2% with Claude Sonnet 4.5 (+18.5pp over SWE-agent) and 67.4% with GPT-5.4-xhigh (+8.3pp over mini-SWE-agent, +6.3pp over Claude Code) -- the 67.4% result surpasses the previously best-reported SWE-bench Pro result (59.10%, mini-SWE-agent+GPT-5.4-xhigh) by 8.3 points. Gains are larger on SWE-bench Pro (more challenging, less contaminated) than Verified, larger on non-Python languages (TypeScript +23.4pp, JavaScript +50.0pp over SWE-agent with Claude Sonnet 4.5), larger on low-quality/ambiguous issue descriptions (e.g., low-quality resolution improving from 44.9% to 61.4% with Claude Sonnet 4.5, and 57.5% to 73.3% with GPT-5.4-xhigh), and larger on harder/more complex multi-file problems (16.1-23.6% improvement over SWE-agent, 5.3-7.2% over Claude Code across difficulty groups). icat-agent is also more cost-effective, reducing average cost by $1.18/instance versus the multi-agent Claude Code baseline while achieving higher resolution rates. Component ablations show: the Issue Quality Checker improves cost-efficiency without hurting repair quality (forcing exploration on all instances increased cost by 18-24% while resolution rate stayed flat or dropped slightly); the Explorer agent achieves strong file-level localization (87.6-88.7% recall on Verified, 74.7-80.6% precision/63.9-64.4% recall on Pro); and a controlled comparison isolating communication design (icat-agent's event-based message passing vs. a Claude-Code-SDK-based orchestrator using shared context, both with identical specialized agent roles) shows icat-agent still wins 67.4% vs. 61.1% under identical GPT-5.4-xhigh, indicating gains come from the communication protocol itself, not merely agent specialization. The reproduction-test-generation component (Validator) produces genuine fail-to-pass reproduction tests in 74.6-80.5% of Verified instances and 74.8-78.3% of Pro instances.</t>
         </is>
       </c>
       <c r="F73" s="5" t="n"/>
@@ -5138,7 +5134,7 @@
       <c r="H73" s="5" t="n"/>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>1ce4b21dda6721f1c94b63ab1b93144a87a9b0ad</t>
+          <t>arxiv:2606.25514</t>
         </is>
       </c>
     </row>
@@ -5148,7 +5144,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Enterprise Secure AI Execution Engine: A Zero-Trust Security Gateway for Enterprise LLM Systems</t>
+          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5163,7 +5159,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Baseline LLM deployment with no security enforcement layer (direct prompt processing, minimal content filtering)</t>
+          <t>SWE-Agent and mini-SWE-Agent (widely used single-agent scaffolds on the SWE-bench leaderboards), and Claude Code (used via the Claude Code SDK to construct an orchestrator/sub-agent multi-agent scaffold with specialized sub-agents for exploration, patch editing, and validation -- representing a common shared-context multi-agent design pattern, used as the strongest widely-used multi-agent baseline).</t>
         </is>
       </c>
       <c r="F74" s="5" t="n"/>
@@ -5171,7 +5167,7 @@
       <c r="H74" s="5" t="n"/>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>1ce4b21dda6721f1c94b63ab1b93144a87a9b0ad</t>
+          <t>arxiv:2606.25514</t>
         </is>
       </c>
     </row>
@@ -5181,7 +5177,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Enterprise Secure AI Execution Engine: A Zero-Trust Security Gateway for Enterprise LLM Systems</t>
+          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5196,7 +5192,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Attackers submit arbitrary prompts (prompt injection, encoded payloads, multi-step reasoning attacks) without access to internal system settings or model configuration, attempting credential theft, role escalation, or confidential-document extraction from an enterprise LLM deployment across Admin/Employee/Intern access levels.</t>
+          <t>N/A - non-adversarial in the traditional security sense, though the paper explicitly names and formally distinguishes two context-integrity failure modes it calls 'context poisoning': (1) test overfitting, where the same agent that generates a patch also writes a weak or incomplete reproduction test, then generates a patch that satisfies that flawed test rather than fixing the actual underlying bug; and (2) patch overfitting, where the agent postpones test generation until after patching, writing tests that happen to pass on the already-generated (possibly incorrect) patch rather than genuinely validating whether the patch resolves the issue. Both arise specifically because monolithic single-agent scaffolds share one growing context across localization, patching, and validation, so the same contaminated reasoning trace that produced a flawed patch also produces the 'independent' check that approves it -- the paper's proposed decentralized, event-based multi-agent architecture is explicitly designed to structurally prevent this self-referential context contamination by giving the Validator agent an isolated context that never sees the Patch Editor's internal reasoning.</t>
         </is>
       </c>
       <c r="F75" s="5" t="n"/>
@@ -5204,7 +5200,7 @@
       <c r="H75" s="5" t="n"/>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>1ce4b21dda6721f1c94b63ab1b93144a87a9b0ad</t>
+          <t>arxiv:2606.25514</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5210,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Enterprise Secure AI Execution Engine: A Zero-Trust Security Gateway for Enterprise LLM Systems</t>
+          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5229,7 +5225,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Authors note the default-deny security policy reduces usability for ambiguous legitimate requests, the pipeline's effectiveness depends on the accuracy of its sensitive-data/adversarial-pattern detection models, and the system currently lacks adaptive/behavioral anomaly detection for multi-stage exfiltration (flagged as future work).</t>
+          <t>Explicit 'Threats to Validity' section covering three standard software-engineering-research validity dimensions. External validity: icat-agent is evaluated only on software engineering benchmarks that may not fully represent industrial-scale systems with much larger codebases, so observed performance may not fully generalize to large-scale production repositories; mitigated partially by evaluating on two benchmarks covering a broad range of real-world bug complexity and multiple model backbones. Internal validity: errors in reproduction-test generation or exploration-based localization can propagate downstream to the Patch Editor and affect patch quality; the event-driven communication design mitigates but does not eliminate this by restricting inter-agent interaction to structured message payloads rather than shared internal context. Construct validity: measuring effectiveness solely via issue-resolution rate (whether a patch passes the benchmark's golden tests) under-approximates true correctness, since golden tests can reject a patch that actually resolves the issue but doesn't match the reference solution's exact structure, and localization metrics treat golden-patch files as the only correct fix location even though valid alternative locations may exist -- the authors argue this bias likely underestimates icat-agent's absolute performance but applies equally to all compared methods, preserving the validity of relative comparisons.</t>
         </is>
       </c>
       <c r="F76" s="5" t="n"/>
@@ -5237,7 +5233,7 @@
       <c r="H76" s="5" t="n"/>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>1ce4b21dda6721f1c94b63ab1b93144a87a9b0ad</t>
+          <t>arxiv:2606.25514</t>
         </is>
       </c>
     </row>
@@ -5247,7 +5243,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Enterprise Secure AI Execution Engine: A Zero-Trust Security Gateway for Enterprise LLM Systems</t>
+          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -5262,7 +5258,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Introduces the Enterprise Secure AI Execution Engine, a Zero-Trust AI Security Gateway that enforces input sanitization, Role-Based Access Control (RBAC), adversarial prompt detection, and deterministic tokenization of sensitive entities before prompts reach an enterprise LLM. Evaluates the gateway on a 300-prompt adversarial subset derived from the HackAPrompt benchmark across five attack categories under three RBAC roles. Reports 98.7% block accuracy and 99.3% tokenization accuracy versus 82%/75% for an unprotected baseline LLM deployment, with only a modest latency increase. Identifies usability trade-offs from default-deny policies and dependence on detection-model accuracy as open limitations.</t>
+          <t>icat-agent is a decentralized, multi-agent scaffold for resolving real-world software issues (bug localization, reproduction, patching, and validation) that directly targets context degradation and context poisoning as failure modes of dominant monolithic single-agent scaffolds (e.g., SWE-agent), which maintain a single shared, growing context across the entire trajectory. The paper identifies two specific context-poisoning failure patterns that arise from this shared-context design: test overfitting (the same agent writes both a weak reproduction test and a patch tailored to satisfy that weak test rather than the actual bug) and patch overfitting (tests are generated after patching and thus biased to validate the already-produced patch rather than independently checking correctness) -- both consequences of validation not being genuinely independent from patch generation when both share one contaminated context. icat-agent's core architectural response is to replace shared context with synchronous, event-based message passing between specialized agents (an Issue Quality Checker/router, an Explorer for repository investigation, a Patch Editor, and an independent Validator), exposing only structured outcomes between agents rather than raw internal reasoning traces, so that validation genuinely operates on an isolated context uncontaminated by the patch-generation agent's potentially flawed reasoning. A rubric-based Issue Quality Checker further adapts the workflow dynamically: well-specified, high-quality issue descriptions bypass exploration and proceed directly to parallel patch generation and independent validation, while ambiguous or low-quality issue descriptions first trigger the Explorer agent to gather missing repository context before repair begins -- avoiding both unnecessary exploration cost on clear issues and under-informed patching on unclear ones. Evaluated on SWE-bench Verified and SWE-bench Pro across multiple model backbones (MiniMax M2.5, GPT-5-mini, Claude Sonnet 4.5, GPT-5.4-xhigh) against SWE-agent, mini-SWE-agent, and a Claude-Code-SDK-based shared-context multi-agent orchestrator baseline, icat-agent consistently and substantially improves issue-resolution rates across all difficulty levels, programming languages, and issue-quality groups (with the largest gains concentrated on harder, lower-quality, and non-Python instances, consistent with the paper's mechanistic story), while also being more cost-effective than the comparable multi-agent Claude Code baseline -- with the isolated communication-design ablation confirming that the improvement stems specifically from the event-based, context-isolated communication protocol rather than merely from having specialized agent roles.</t>
         </is>
       </c>
       <c r="F77" s="5" t="n"/>
@@ -5270,7 +5266,7 @@
       <c r="H77" s="5" t="n"/>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>1ce4b21dda6721f1c94b63ab1b93144a87a9b0ad</t>
+          <t>arxiv:2606.25514</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5276,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Tug-of-War between Knowledge: Exploring and Resolving Knowledge Conflicts in Retrieval-Augmented Language Models</t>
+          <t>Tug-of-War within A Decade: Conflict Resolution in Vulnerability Analysis via Teacher-Guided Retrieval-Augmented Generations</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -5303,7 +5299,7 @@
       <c r="H78" s="5" t="n"/>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>812b87876b22260fe046af447c5f40a4ce2906ea</t>
+          <t>a2de6faaa98252c163c088613a04ad2dceb284a4</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5309,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Tug-of-War between Knowledge: Exploring and Resolving Knowledge Conflicts in Retrieval-Augmented Language Models</t>
+          <t>Tug-of-War within A Decade: Conflict Resolution in Vulnerability Analysis via Teacher-Guided Retrieval-Augmented Generations</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -5336,7 +5332,7 @@
       <c r="H79" s="5" t="n"/>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>812b87876b22260fe046af447c5f40a4ce2906ea</t>
+          <t>a2de6faaa98252c163c088613a04ad2dceb284a4</t>
         </is>
       </c>
     </row>
@@ -5346,7 +5342,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Tug-of-War between Knowledge: Exploring and Resolving Knowledge Conflicts in Retrieval-Augmented Language Models</t>
+          <t>Tug-of-War within A Decade: Conflict Resolution in Vulnerability Analysis via Teacher-Guided Retrieval-Augmented Generations</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -5369,7 +5365,7 @@
       <c r="H80" s="5" t="n"/>
       <c r="I80" s="5" t="inlineStr">
         <is>
-          <t>812b87876b22260fe046af447c5f40a4ce2906ea</t>
+          <t>a2de6faaa98252c163c088613a04ad2dceb284a4</t>
         </is>
       </c>
     </row>
@@ -5379,7 +5375,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Tug-of-War between Knowledge: Exploring and Resolving Knowledge Conflicts in Retrieval-Augmented Language Models</t>
+          <t>Tug-of-War within A Decade: Conflict Resolution in Vulnerability Analysis via Teacher-Guided Retrieval-Augmented Generations</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -5394,7 +5390,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>defense</t>
         </is>
       </c>
       <c r="F81" s="5" t="n"/>
@@ -5402,7 +5398,7 @@
       <c r="H81" s="5" t="n"/>
       <c r="I81" s="5" t="inlineStr">
         <is>
-          <t>812b87876b22260fe046af447c5f40a4ce2906ea</t>
+          <t>a2de6faaa98252c163c088613a04ad2dceb284a4</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5408,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Tug-of-War between Knowledge: Exploring and Resolving Knowledge Conflicts in Retrieval-Augmented Language Models</t>
+          <t>Tug-of-War within A Decade: Conflict Resolution in Vulnerability Analysis via Teacher-Guided Retrieval-Augmented Generations</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5435,7 +5431,7 @@
       <c r="H82" s="5" t="n"/>
       <c r="I82" s="5" t="inlineStr">
         <is>
-          <t>812b87876b22260fe046af447c5f40a4ce2906ea</t>
+          <t>a2de6faaa98252c163c088613a04ad2dceb284a4</t>
         </is>
       </c>
     </row>
@@ -5445,7 +5441,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Tug-of-War between Knowledge: Exploring and Resolving Knowledge Conflicts in Retrieval-Augmented Language Models</t>
+          <t>Tug-of-War within A Decade: Conflict Resolution in Vulnerability Analysis via Teacher-Guided Retrieval-Augmented Generations</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -5468,7 +5464,7 @@
       <c r="H83" s="5" t="n"/>
       <c r="I83" s="5" t="inlineStr">
         <is>
-          <t>812b87876b22260fe046af447c5f40a4ce2906ea</t>
+          <t>a2de6faaa98252c163c088613a04ad2dceb284a4</t>
         </is>
       </c>
     </row>
@@ -5478,7 +5474,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Tug-of-War between Knowledge: Exploring and Resolving Knowledge Conflicts in Retrieval-Augmented Language Models</t>
+          <t>Tug-of-War within A Decade: Conflict Resolution in Vulnerability Analysis via Teacher-Guided Retrieval-Augmented Generations</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -5501,7 +5497,7 @@
       <c r="H84" s="5" t="n"/>
       <c r="I84" s="5" t="inlineStr">
         <is>
-          <t>812b87876b22260fe046af447c5f40a4ce2906ea</t>
+          <t>a2de6faaa98252c163c088613a04ad2dceb284a4</t>
         </is>
       </c>
     </row>
@@ -5511,7 +5507,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Tug-of-War between Knowledge: Exploring and Resolving Knowledge Conflicts in Retrieval-Augmented Language Models</t>
+          <t>Tug-of-War within A Decade: Conflict Resolution in Vulnerability Analysis via Teacher-Guided Retrieval-Augmented Generations</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -5534,7 +5530,7 @@
       <c r="H85" s="5" t="n"/>
       <c r="I85" s="5" t="inlineStr">
         <is>
-          <t>812b87876b22260fe046af447c5f40a4ce2906ea</t>
+          <t>a2de6faaa98252c163c088613a04ad2dceb284a4</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5540,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Tug-of-War between Knowledge: Exploring and Resolving Knowledge Conflicts in Retrieval-Augmented Language Models</t>
+          <t>Tug-of-War within A Decade: Conflict Resolution in Vulnerability Analysis via Teacher-Guided Retrieval-Augmented Generations</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -5567,7 +5563,7 @@
       <c r="H86" s="5" t="n"/>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>812b87876b22260fe046af447c5f40a4ce2906ea</t>
+          <t>a2de6faaa98252c163c088613a04ad2dceb284a4</t>
         </is>
       </c>
     </row>
@@ -5577,7 +5573,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Tug-of-War between Knowledge: Exploring and Resolving Knowledge Conflicts in Retrieval-Augmented Language Models</t>
+          <t>Tug-of-War within A Decade: Conflict Resolution in Vulnerability Analysis via Teacher-Guided Retrieval-Augmented Generations</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -5600,7 +5596,7 @@
       <c r="H87" s="5" t="n"/>
       <c r="I87" s="5" t="inlineStr">
         <is>
-          <t>812b87876b22260fe046af447c5f40a4ce2906ea</t>
+          <t>a2de6faaa98252c163c088613a04ad2dceb284a4</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5606,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Tug-of-War between Knowledge: Exploring and Resolving Knowledge Conflicts in Retrieval-Augmented Language Models</t>
+          <t>Tug-of-War within A Decade: Conflict Resolution in Vulnerability Analysis via Teacher-Guided Retrieval-Augmented Generations</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -5633,7 +5629,7 @@
       <c r="H88" s="5" t="n"/>
       <c r="I88" s="5" t="inlineStr">
         <is>
-          <t>812b87876b22260fe046af447c5f40a4ce2906ea</t>
+          <t>a2de6faaa98252c163c088613a04ad2dceb284a4</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5639,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Tug-of-War between Knowledge: Exploring and Resolving Knowledge Conflicts in Retrieval-Augmented Language Models</t>
+          <t>Tug-of-War within A Decade: Conflict Resolution in Vulnerability Analysis via Teacher-Guided Retrieval-Augmented Generations</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -5658,7 +5654,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>No code/dataset release URL is stated in the sections reviewed. The Acknowledgments section notes funding information was 'temporarily hidden due to anonymous submission,' and the paper describes constructing a CVE dataset via the NVD API and the CVE official GitHub dataset for internal use, but no public repository link is given for the framework or curated dataset.</t>
         </is>
       </c>
       <c r="F89" s="5" t="n"/>
@@ -5666,7 +5662,7 @@
       <c r="H89" s="5" t="n"/>
       <c r="I89" s="5" t="inlineStr">
         <is>
-          <t>812b87876b22260fe046af447c5f40a4ce2906ea</t>
+          <t>a2de6faaa98252c163c088613a04ad2dceb284a4</t>
         </is>
       </c>
     </row>
@@ -5676,7 +5672,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Tug-of-War between Knowledge: Exploring and Resolving Knowledge Conflicts in Retrieval-Augmented Language Models</t>
+          <t>Tug-of-War within A Decade: Conflict Resolution in Vulnerability Analysis via Teacher-Guided Retrieval-Augmented Generations</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5691,7 +5687,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>FLAN-T5-XL (3B), FLAN-T5-XXL (11B), FLAN-UL2 (20B), Baichuan2 7B, Baichuan2 13B, LLaMA2 7B, LLaMA2 13B; ChatGPT (gpt-3.5-turbo, API-access)</t>
+          <t>Seven LLMs across closed- and open-source categories: GPT-4o-mini, Claude-3.5-Haiku-20241022, and Gemini-2.0-Flash-Exp (closed-source, No Prompt / Prompt Only conditions), plus Llama-3-70B and Mistral-Medium (open-source, No Prompt / Prompt Only conditions). For the DPO-tuned and full CRVA-TGRAG conditions, GPT-4o-mini, DPO-Llama3-8B, and DPO-Mistral-8B are used.</t>
         </is>
       </c>
       <c r="F90" s="5" t="n"/>
@@ -5699,7 +5695,7 @@
       <c r="H90" s="5" t="n"/>
       <c r="I90" s="5" t="inlineStr">
         <is>
-          <t>812b87876b22260fe046af447c5f40a4ce2906ea</t>
+          <t>a2de6faaa98252c163c088613a04ad2dceb284a4</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5705,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Tug-of-War between Knowledge: Exploring and Resolving Knowledge Conflicts in Retrieval-Augmented Language Models</t>
+          <t>Tug-of-War within A Decade: Conflict Resolution in Vulnerability Analysis via Teacher-Guided Retrieval-Augmented Generations</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -5724,7 +5720,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Natural Questions (NQ), TriviaQA, PopQA (entity-centric, long-tail popularity distribution), MuSiQue (multi-hop, 2-4 hop questions); reconstructed conflict-specific variants NQ-Conf/TriviaQA-Conf (truthful vs. irrelevant vs. misleading evidence conflicts) and NQ-Inco/TriviaQA-Inco (questions where the model's internal memory answers incorrectly), all using Wikipedia as the external source</t>
+          <t>A custom-constructed CVE (Common Vulnerabilities and Exposures) dataset built from the NVD (National Vulnerability Database) API and the official CVE GitHub dataset, organizing pre- and post-update knowledge for each CVE number and labeling differences between versions to isolate genuine knowledge conflicts. Nine CVE documents were used for the document-chunking visualization/validation experiments. No standard external QA benchmark is used; evaluation metrics include Faithfulness (Faith), Context Recall (CR), Context Precision (CP), Answer Relevance (AR), Answer Correctness (AC), Answer Similarity (AS), BLEU, and ROUGE-L (F/P/R).</t>
         </is>
       </c>
       <c r="F91" s="5" t="n"/>
@@ -5732,7 +5728,7 @@
       <c r="H91" s="5" t="n"/>
       <c r="I91" s="5" t="inlineStr">
         <is>
-          <t>812b87876b22260fe046af447c5f40a4ce2906ea</t>
+          <t>a2de6faaa98252c163c088613a04ad2dceb284a4</t>
         </is>
       </c>
     </row>
@@ -5742,7 +5738,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Tug-of-War between Knowledge: Exploring and Resolving Knowledge Conflicts in Retrieval-Augmented Language Models</t>
+          <t>Tug-of-War within A Decade: Conflict Resolution in Vulnerability Analysis via Teacher-Guided Retrieval-Augmented Generations</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -5757,7 +5753,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Retrieval-Augmented Language Models (RALMs) readily change their internal beliefs to trust conflicting external evidence, even when their internal memory was actually correct (recall against conflicting references far exceeds recall against internal-memory predictions). As model size and capability increase, models gain greater confidence in their internal memory, but this manifests as a Dunning-Kruger-like effect: more capable models (e.g. ChatGPT) tend to lack confidence in their correct internal memory while stubbornly persisting in their incorrect internal memory more than half the time, even when given correct conflicting evidence. RALMs exhibit an availability bias toward common knowledge on PopQA - for long-tail (rarely-known) facts they rely mostly on external sources, but as entity popularity increases they increasingly trust their internal memory instead. RALMs generally struggle to discern truthful from misleading evidence (K-Precision for misleading evidence is often higher than for truthful evidence) and are readily distracted by irrelevant evidence, following a 'majority rule' whereby they trust whichever type of evidence appears more frequently in context - notably, providing more external evidence is not always better, since excessively long context can cause the model to lose focus and answer less accurately. RALMs also exhibit confirmation bias, being more inclined to select evidence consistent with their own internal memory regardless of its correctness. In multi-hop reasoning (MuSiQue), increasing the number of conflicting hops progressively hinders the model's ability to reason to the correct answer, with even ChatGPT performing poorly as conflicting hops accumulate. The proposed Conflict-Disentangle Contrastive Decoding (CD²) method, without updating model parameters, achieves a 2.05% and 2.70% Recall improvement on NQ-Inco and TriviaQA-Inco respectively (memory-vs-external conflicts) by amplifying the difference between expert (external-source-conditioned) and internal-memory-only logits, and achieves a 29.83% and 23.06% Recall improvement over an in-context baseline on NQ-Conf and TriviaQA-Conf respectively (truthful-vs-misleading conflicts) via fact-aware instruction tuning of separate expert/amateur logits, while substantially decreasing the model's K-Precision for misleading evidence.</t>
+          <t>CRVA-TGRAG (the full two-stage method, combining optimized RAG retrieval with teacher-guided DPO fine-tuning) substantially outperforms all baselines across all evaluation metrics (Table 1). With DPO-Mistral-8B, the full method achieves Faith=0.76, CR=0.46, CP=0.46, AR=0.93, AC=0.88, AS=0.95, versus Naive RAG with GPT-4o-mini at Faith=0.70, CR=0.01, CP=0.02, AR=0.01, AC=0.28, AS=0.78 -- a roughly 45x improvement in Context Recall and over 3x in Answer Relevance. Non-RAG baselines (No Prompt, Prompt Only) score nearly zero on Faith/CR/CP (marked '-', not computed since no retrieval occurs) and show inconsistent AR scores ranging from 0.01 (Claude-3.5-Haiku, Prompt Only) to 0.92 (DPO-Mistral-8B, DPO+Prompt) with AC generally low (0.24-0.36), indicating base LLMs struggle to resolve CVE knowledge conflicts from parametric knowledge alone regardless of prompting strategy. An ablation isolating the RAG-only stage (CRVA-TGRAG No DPO) versus DPO-only (DPO+Prompt) shows DPO alone substantially improves AR (up to 0.92) but leaves AC and AS close to non-DPO baselines, while the RAG-only stage substantially improves Faith/CR/CP over Naive RAG (0.49/0.46/0.45 vs. 0.70(lower is not necessarily better here)/0.01/0.02), confirming that combining both stages is necessary for the full performance gain, since neither component alone achieves comparably high scores across all six metrics simultaneously.</t>
         </is>
       </c>
       <c r="F92" s="5" t="n"/>
@@ -5765,7 +5761,7 @@
       <c r="H92" s="5" t="n"/>
       <c r="I92" s="5" t="inlineStr">
         <is>
-          <t>812b87876b22260fe046af447c5f40a4ce2906ea</t>
+          <t>a2de6faaa98252c163c088613a04ad2dceb284a4</t>
         </is>
       </c>
     </row>
@@ -5775,7 +5771,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Tug-of-War between Knowledge: Exploring and Resolving Knowledge Conflicts in Retrieval-Augmented Language Models</t>
+          <t>Tug-of-War within A Decade: Conflict Resolution in Vulnerability Analysis via Teacher-Guided Retrieval-Augmented Generations</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -5790,7 +5786,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Closed-book (no external evidence provided) vs. In-context (external evidence provided, standard prompting) vs. Finetune_Orig (fine-tuned on the original, non-conflict training set) vs. Finetune_Conf (fine-tuned on a conflict-enhanced training set) vs. the proposed CD² method, compared on NQ-Conf/TriviaQA-Conf (truthful-misleading evidence conflicts); In-context vs. CD² at varying contrastive-decoding strength (alpha=0.3/0.5/0.7) compared on NQ-Inco/TriviaQA-Inco (internal-memory-vs-external-source conflicts)</t>
+          <t>Six method variants compared across the seven LLMs: No Prompt (direct query to the latest LLM with no retrieval or special prompting), Prompt Only (prompt engineering plus Chain-of-Thought, no RAG), DPO+Prompt (teacher-guided preference-tuned models without RAG), Naive RAG (basic RAG scheme, no optimization or DPO), CRVA-TGRAG (No DPO) (optimized retrieval stage only, without preference tuning), and the full CRVA-TGRAG (Ours) combining both stages.</t>
         </is>
       </c>
       <c r="F93" s="5" t="n"/>
@@ -5798,7 +5794,7 @@
       <c r="H93" s="5" t="n"/>
       <c r="I93" s="5" t="inlineStr">
         <is>
-          <t>812b87876b22260fe046af447c5f40a4ce2906ea</t>
+          <t>a2de6faaa98252c163c088613a04ad2dceb284a4</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5804,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Tug-of-War between Knowledge: Exploring and Resolving Knowledge Conflicts in Retrieval-Augmented Language Models</t>
+          <t>Tug-of-War within A Decade: Conflict Resolution in Vulnerability Analysis via Teacher-Guided Retrieval-Augmented Generations</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -5823,7 +5819,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>N/A - non-adversarial; studies incidental knowledge conflicts arising in RALMs from naturally-occurring misinformation, divergent perspectives, evolving/outdated knowledge, and entity-substitution-based counterfactual evidence (synthetically generated via ChatGPT purely as a controlled experimental construction, not as an adversarial threat), rather than framing external content as coming from a malicious attacker with a specific manipulation goal</t>
+          <t>N/A - non-adversarial. This is a cybersecurity-knowledge-retrieval reliability paper, not a paper studying adversarial attacks on the LLM itself, though its domain (CVE/vulnerability analysis) is cybersecurity-adjacent. The incidental failure mode of interest is naturally occurring knowledge conflict and staleness: over 200,000 CVEs were discovered in the past decade and more than 30,000 have since been changed or updated, but LLMs' internal/parametric knowledge and static training data go stale, causing knowledge discrepancies between an LLM's internal memory and updated ground truth, leading to factually incorrect fabrications and hallucinated vulnerability analysis outputs (illustrated in Figure 1 with truthful, irrelevant, and misleading candidate answers to a 'which vulnerability is the latest' query).</t>
         </is>
       </c>
       <c r="F94" s="5" t="n"/>
@@ -5831,7 +5827,7 @@
       <c r="H94" s="5" t="n"/>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>812b87876b22260fe046af447c5f40a4ce2906ea</t>
+          <t>a2de6faaa98252c163c088613a04ad2dceb284a4</t>
         </is>
       </c>
     </row>
@@ -5841,7 +5837,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Tug-of-War between Knowledge: Exploring and Resolving Knowledge Conflicts in Retrieval-Augmented Language Models</t>
+          <t>Tug-of-War within A Decade: Conflict Resolution in Vulnerability Analysis via Teacher-Guided Retrieval-Augmented Generations</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -5856,7 +5852,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>The explicit Limitations section states: (1) the paper mainly investigates knowledge conflicts in RALMs from two perspectives - model performance and confidence score - and identifies exploring the model's internal mechanisms (e.g. analyzing whether knowledge conflicts inhibit or stimulate the activation values of specific neurons) as future work not covered here; (2) the paper's proposed method for resolving knowledge conflicts (CD²) works by calibrating the open-source model's own output logits via contrastive decoding, and how to mitigate knowledge conflicts in black-box LLMs that do not expose output logits (and thus cannot use this technique) remains an open, unstudied problem.</t>
+          <t>Explicit 'Limitation' section (Section 6, distinct from the Conclusion) identifying issues specifically with a proposed but not fully realized future direction (Agentic RAG with online retrieval) rather than the current method itself: online retrieval via general search engines (Google, Bing) or designated databases (NVD, CNNVD) could further alleviate knowledge conflicts, but the authors flag two problems this approach would face: (1) search engines may be influenced or induced by malicious SEO, potentially retrieving irrelevant or outdated content; (2) content obtained from comprehensive searches or online databases may still suffer from timeliness issues, resulting in retrieval of inaccurate information -- both of which could themselves reintroduce knowledge conflicts in the final LLM output. The Agentic RAG direction with internet search integration is framed as a promising but unimplemented direction for future work rather than a limitation of the current CRVA-TGRAG method's reported results.</t>
         </is>
       </c>
       <c r="F95" s="5" t="n"/>
@@ -5864,7 +5860,7 @@
       <c r="H95" s="5" t="n"/>
       <c r="I95" s="5" t="inlineStr">
         <is>
-          <t>812b87876b22260fe046af447c5f40a4ce2906ea</t>
+          <t>a2de6faaa98252c163c088613a04ad2dceb284a4</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5870,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Tug-of-War between Knowledge: Exploring and Resolving Knowledge Conflicts in Retrieval-Augmented Language Models</t>
+          <t>Tug-of-War within A Decade: Conflict Resolution in Vulnerability Analysis via Teacher-Guided Retrieval-Augmented Generations</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -5889,7 +5885,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Introduces a comprehensive evaluation framework for exploring how Retrieval-Augmented Language Models (RALMs) behave when their internal parametric memory conflicts with retrieved external evidence, and when retrieved external sources themselves conflict with each other (truthful vs. irrelevant vs. misleading). The framework reconstructs four QA datasets (NQ, TriviaQA, PopQA, MuSiQue) to probe conflicts from open-domain (single evidence), entity-centric (popularity-varying), and multi-hop (multiple evidence pieces) perspectives, evaluates eight LLMs of varying scale and capability (seven open-source, one API-access), and measures three dimensions: correctness (EM/F1/Recall), faithfulness (whether and which type of external evidence the model relies on, via K-Precision), and memorization (how strongly the model sticks to its internal memory, via a Memorization Ratio metric). Investigating conflicts between internal memory and external sources, the paper finds RALMs readily override even correct internal beliefs when given conflicting external evidence, that more capable models paradoxically show a Dunning-Kruger-like pattern of low confidence in correct internal memory but stubborn persistence in incorrect internal memory, and that models exhibit an availability bias favoring commonly-known (high-popularity) knowledge over reliance on external sources. Investigating conflicts among truthful, irrelevant, and misleading external evidence, the paper finds RALMs often cannot reliably distinguish truthful from misleading evidence, are distracted by irrelevant evidence, follow a majority-rule heuristic trusting whichever evidence type is more numerous (with excessively long context sometimes causing accuracy to degrade rather than improve), exhibit confirmation bias favoring evidence consistent with their own internal memory, and become progressively less accurate as the number of conflicting reasoning hops increases in multi-hop QA. To address these failure modes, the paper proposes Conflict-Disentangle Contrastive Decoding (CD²), which uses contrastive decoding to amplify the logit difference between an 'expert' signal (conditioned on external sources, or specifically fine-tuned to generate truthful answers) and an 'amateur'/no-external-source signal (either the model's raw internal-memory-only logits, or a separately fine-tuned model deliberately trained to generate misleading answers), thereby better calibrating the model's confidence and improving its ability to correctly resolve both types of knowledge conflict without requiring any change to the underlying model's parameters, achieving measurable Recall improvements over in-context and fine-tuning baselines across both conflict settings.</t>
+          <t>CRVA-TGRAG (Conflict Resolution in Vulnerability Analysis via Teacher-Guided Retrieval-Augmented Generation) is a two-stage framework addressing knowledge conflict and staleness when LLMs analyze CVE (Common Vulnerabilities and Exposures) information, where an LLM's static parametric/training-time knowledge can be truthful, irrelevant, or actively misleading relative to updated ground-truth vulnerability records. Stage I improves document retrieval accuracy through Parent Document Segmentation combined with semantic-similarity-based chunking (splitting documents at points where embedding-distance between adjacent sentences exceeds a configurable percentile threshold, tuned across 85th/90th/95th percentile splits) plus an ensemble retrieval scheme combining semantic similarity search with inverted indexing, applied to a curated CVE dataset built from the NVD API and the official CVE GitHub repository with pre- and post-update versions explicitly labeled to isolate genuine version-to-version knowledge conflicts from retrieval noise. Stage II applies a teacher-guided Direct Preference Optimization (DPO) fine-tuning process to enhance the downstream LLM's ability to correctly use retrieved CVE content when generating answers, rather than relying on prompt engineering or Chain-of-Thought alone. The framework is evaluated using a comprehensive metric suite spanning RAG-specific metrics (Faithfulness, Context Recall, Context Precision) and general answer-quality metrics (Answer Relevance, Answer Correctness, Answer Similarity, BLEU, ROUGE-L), comparing against non-RAG baselines (direct prompting, prompt-only, DPO-only) and a Naive RAG baseline to isolate the individual and combined contributions of the improved retrieval stage and the preference-tuning stage.</t>
         </is>
       </c>
       <c r="F96" s="5" t="n"/>
@@ -5897,7 +5893,7 @@
       <c r="H96" s="5" t="n"/>
       <c r="I96" s="5" t="inlineStr">
         <is>
-          <t>812b87876b22260fe046af447c5f40a4ce2906ea</t>
+          <t>a2de6faaa98252c163c088613a04ad2dceb284a4</t>
         </is>
       </c>
     </row>
@@ -5907,7 +5903,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>CodeDelegator: Mitigating Context Pollution via Role Separation in Code-as-Action Agents</t>
+          <t>Context-Aware RL for Agentic and Multimodal LLMs</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -5930,7 +5926,7 @@
       <c r="H97" s="5" t="n"/>
       <c r="I97" s="5" t="inlineStr">
         <is>
-          <t>894af73fb679f95ea1a36eb6bad300bfb80566fa</t>
+          <t>72b5e6023db3b5af8e8f27f8b4a52bc5f1f32ba7</t>
         </is>
       </c>
     </row>
@@ -5940,7 +5936,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>CodeDelegator: Mitigating Context Pollution via Role Separation in Code-as-Action Agents</t>
+          <t>Context-Aware RL for Agentic and Multimodal LLMs</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -5963,7 +5959,7 @@
       <c r="H98" s="5" t="n"/>
       <c r="I98" s="5" t="inlineStr">
         <is>
-          <t>894af73fb679f95ea1a36eb6bad300bfb80566fa</t>
+          <t>72b5e6023db3b5af8e8f27f8b4a52bc5f1f32ba7</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5969,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>CodeDelegator: Mitigating Context Pollution via Role Separation in Code-as-Action Agents</t>
+          <t>Context-Aware RL for Agentic and Multimodal LLMs</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -5996,7 +5992,7 @@
       <c r="H99" s="5" t="n"/>
       <c r="I99" s="5" t="inlineStr">
         <is>
-          <t>894af73fb679f95ea1a36eb6bad300bfb80566fa</t>
+          <t>72b5e6023db3b5af8e8f27f8b4a52bc5f1f32ba7</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6002,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>CodeDelegator: Mitigating Context Pollution via Role Separation in Code-as-Action Agents</t>
+          <t>Context-Aware RL for Agentic and Multimodal LLMs</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -6029,7 +6025,7 @@
       <c r="H100" s="5" t="n"/>
       <c r="I100" s="5" t="inlineStr">
         <is>
-          <t>894af73fb679f95ea1a36eb6bad300bfb80566fa</t>
+          <t>72b5e6023db3b5af8e8f27f8b4a52bc5f1f32ba7</t>
         </is>
       </c>
     </row>
@@ -6039,7 +6035,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>CodeDelegator: Mitigating Context Pollution via Role Separation in Code-as-Action Agents</t>
+          <t>Context-Aware RL for Agentic and Multimodal LLMs</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -6054,7 +6050,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>cross-modal</t>
         </is>
       </c>
       <c r="F101" s="5" t="n"/>
@@ -6062,7 +6058,7 @@
       <c r="H101" s="5" t="n"/>
       <c r="I101" s="5" t="inlineStr">
         <is>
-          <t>894af73fb679f95ea1a36eb6bad300bfb80566fa</t>
+          <t>72b5e6023db3b5af8e8f27f8b4a52bc5f1f32ba7</t>
         </is>
       </c>
     </row>
@@ -6072,7 +6068,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>CodeDelegator: Mitigating Context Pollution via Role Separation in Code-as-Action Agents</t>
+          <t>Context-Aware RL for Agentic and Multimodal LLMs</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -6095,7 +6091,7 @@
       <c r="H102" s="5" t="n"/>
       <c r="I102" s="5" t="inlineStr">
         <is>
-          <t>894af73fb679f95ea1a36eb6bad300bfb80566fa</t>
+          <t>72b5e6023db3b5af8e8f27f8b4a52bc5f1f32ba7</t>
         </is>
       </c>
     </row>
@@ -6105,7 +6101,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>CodeDelegator: Mitigating Context Pollution via Role Separation in Code-as-Action Agents</t>
+          <t>Context-Aware RL for Agentic and Multimodal LLMs</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -6128,7 +6124,7 @@
       <c r="H103" s="5" t="n"/>
       <c r="I103" s="5" t="inlineStr">
         <is>
-          <t>894af73fb679f95ea1a36eb6bad300bfb80566fa</t>
+          <t>72b5e6023db3b5af8e8f27f8b4a52bc5f1f32ba7</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6134,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>CodeDelegator: Mitigating Context Pollution via Role Separation in Code-as-Action Agents</t>
+          <t>Context-Aware RL for Agentic and Multimodal LLMs</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -6161,7 +6157,7 @@
       <c r="H104" s="5" t="n"/>
       <c r="I104" s="5" t="inlineStr">
         <is>
-          <t>894af73fb679f95ea1a36eb6bad300bfb80566fa</t>
+          <t>72b5e6023db3b5af8e8f27f8b4a52bc5f1f32ba7</t>
         </is>
       </c>
     </row>
@@ -6171,7 +6167,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>CodeDelegator: Mitigating Context Pollution via Role Separation in Code-as-Action Agents</t>
+          <t>Context-Aware RL for Agentic and Multimodal LLMs</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -6186,7 +6182,7 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>execution</t>
+          <t>reasoning</t>
         </is>
       </c>
       <c r="F105" s="5" t="n"/>
@@ -6194,7 +6190,7 @@
       <c r="H105" s="5" t="n"/>
       <c r="I105" s="5" t="inlineStr">
         <is>
-          <t>894af73fb679f95ea1a36eb6bad300bfb80566fa</t>
+          <t>72b5e6023db3b5af8e8f27f8b4a52bc5f1f32ba7</t>
         </is>
       </c>
     </row>
@@ -6204,7 +6200,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>CodeDelegator: Mitigating Context Pollution via Role Separation in Code-as-Action Agents</t>
+          <t>Context-Aware RL for Agentic and Multimodal LLMs</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -6219,7 +6215,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>one-shot</t>
+          <t>session-persistent</t>
         </is>
       </c>
       <c r="F106" s="5" t="n"/>
@@ -6227,7 +6223,7 @@
       <c r="H106" s="5" t="n"/>
       <c r="I106" s="5" t="inlineStr">
         <is>
-          <t>894af73fb679f95ea1a36eb6bad300bfb80566fa</t>
+          <t>72b5e6023db3b5af8e8f27f8b4a52bc5f1f32ba7</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6233,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>CodeDelegator: Mitigating Context Pollution via Role Separation in Code-as-Action Agents</t>
+          <t>Context-Aware RL for Agentic and Multimodal LLMs</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -6260,7 +6256,7 @@
       <c r="H107" s="5" t="n"/>
       <c r="I107" s="5" t="inlineStr">
         <is>
-          <t>894af73fb679f95ea1a36eb6bad300bfb80566fa</t>
+          <t>72b5e6023db3b5af8e8f27f8b4a52bc5f1f32ba7</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6266,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>CodeDelegator: Mitigating Context Pollution via Role Separation in Code-as-Action Agents</t>
+          <t>Context-Aware RL for Agentic and Multimodal LLMs</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -6285,7 +6281,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>No code, dataset, or model release statement, GitHub link, or repository URL for CodeDelegator itself was found anywhere in the paper after thorough search (the only GitHub reference found is to a third-party MCP service, 'GitHub,' used as one of the five MCP services in the MCPMark benchmark evaluation).</t>
+          <t>The paper states 'Data and code will be publicly released' in the abstract, and the title page lists 'Website | Code | Model | Dataset' link placeholders, but pdftotext extraction did not surface any concrete URL text for these links (they are likely embedded hyperlinks not captured as plain text, or placeholders pending camera-ready release). No anonymous-review or GitHub/HuggingFace URL string appears anywhere in the extracted references or body text, so the exact link targets could not be confirmed from the text alone.</t>
         </is>
       </c>
       <c r="F108" s="5" t="n"/>
@@ -6293,7 +6289,7 @@
       <c r="H108" s="5" t="n"/>
       <c r="I108" s="5" t="inlineStr">
         <is>
-          <t>894af73fb679f95ea1a36eb6bad300bfb80566fa</t>
+          <t>72b5e6023db3b5af8e8f27f8b4a52bc5f1f32ba7</t>
         </is>
       </c>
     </row>
@@ -6303,7 +6299,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>CodeDelegator: Mitigating Context Pollution via Role Separation in Code-as-Action Agents</t>
+          <t>Context-Aware RL for Agentic and Multimodal LLMs</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -6318,7 +6314,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>DeepSeekV3.2 and GPT-5.0 (at low reasoning level) are used as backbone models for both baselines and CodeDelegator on tau2-bench, with DeepSeekV3.2 also serving as the simulated user for multi-turn dialogue (per tau2-bench's framework requirements) and as the sole backbone for MCPMark (due to cost considerations). In CodeDelegator, the Delegator and Coder agents share the same base model but operate within separate, isolated contexts.</t>
+          <t>Agentic/long-horizon setting: Qwen3-8B and Klear-AgentForge-8B as RL base models, with off-the-shelf reference comparisons against Qwen3-14B, Qwen3-32B, and Qwen3-Coder-30B. Diagnostic probe compares GPT-5.4 and Claude Opus 4.7 (proprietary) against Qwen3 (VL) 8B and Qwen3.5 9B (open-source) on contrastive context selection. Multimodal setting: Qwen2.5-VL-7B and Qwen3-VL-8B as base models trained with GRPO and ContextRL.</t>
         </is>
       </c>
       <c r="F109" s="5" t="n"/>
@@ -6326,7 +6322,7 @@
       <c r="H109" s="5" t="n"/>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>894af73fb679f95ea1a36eb6bad300bfb80566fa</t>
+          <t>72b5e6023db3b5af8e8f27f8b4a52bc5f1f32ba7</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6332,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>CodeDelegator: Mitigating Context Pollution via Role Separation in Code-as-Action Agents</t>
+          <t>Context-Aware RL for Agentic and Multimodal LLMs</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -6351,7 +6347,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Two benchmarks: tau2-bench (Barres et al., 2025), evaluated across its Retail and Airline domains using pass^k accuracy (k in {1,2,3,4}), where a task is only considered passed if all user requirements are satisfied and all backend state changes are correct; and MCPMark, a benchmark of curated tasks requiring extensive CRUD operations across 5 MCP services (Filesystem, GitHub, Notion, Playwright, PostgreSQL), evaluated using pass@1. A preliminary motivating study also uses 50 tasks from the airline domain of tau2-bench with DeepSeekV3.2 as both agent and simulated user, stratified by difficulty level (Low/Medium/High) based on official benchmark success rates.</t>
+          <t>Diagnostic probe: 200 contrastive context pairs each from agentic trajectories and VQA images. Agentic RL training data: 1k contrastive trajectory pairs built from SWE-smith trajectories via condition filtering, combined with 7k standard SWE-Gym and SWE-Smith coding tasks (8k total training instances). Agentic evaluation: 2 in-distribution benchmarks (SWE-Bench Verified, SWE-Bench Lite, resolve rate %) and 3 out-of-distribution benchmarks (LiveCodeBench v6 competitive programming, LongBench v2 long-context QA, Needle-in-a-Haystack/NIAH targeted retrieval) -- 5 long-horizon benchmarks total. Multimodal: 7K contrastive image pairs built via generative editing and similarity search, evaluated across 12 diverse VQA benchmarks. 17 benchmarks total across both settings.</t>
         </is>
       </c>
       <c r="F110" s="5" t="n"/>
@@ -6359,7 +6355,7 @@
       <c r="H110" s="5" t="n"/>
       <c r="I110" s="5" t="inlineStr">
         <is>
-          <t>894af73fb679f95ea1a36eb6bad300bfb80566fa</t>
+          <t>72b5e6023db3b5af8e8f27f8b4a52bc5f1f32ba7</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6365,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>CodeDelegator: Mitigating Context Pollution via Role Separation in Code-as-Action Agents</t>
+          <t>Context-Aware RL for Agentic and Multimodal LLMs</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -6384,7 +6380,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>A preliminary study (Table 1) shows CodeAct incurs substantially more context length than ReAct across all difficulty levels, but with inconsistent returns: CodeAct underperforms ReAct on Low (-5.8 percentage points) and Medium (-2.5 pp) difficulty tasks while outperforming on High difficulty (+7.7 pp), and within CodeAct runs, context length negatively correlates with success on Low and High difficulty tasks -- direct evidence of context pollution degrading performance. On tau2-bench with DeepSeekV3.2 (Table 2), CodeDelegator achieves the highest pass^1 accuracy across both domains (82.0% Retail, 63.5% Airline), and CodeAct consistently underperforms ReAct despite greater expressiveness, confirming that context pollution negates the benefits of code-based actions in long-horizon tasks; CodeDelegator's advantage grows under stricter multi-turn consistency requirements (pass^1 to pass^4 degradation is notably smaller for CodeDelegator than for CodeAct on Airline). On MCPMark with DeepSeekV3.2 (Table 3), CodeDelegator achieves the highest total pass@1 (38.4%) versus CodeAct (26.4%) and ReAct (25.8%), with particularly large gains on GitHub (38.0% vs. 27.9%/18.5%), Notion (34.8% vs. 19.4%/13.4%), and Playwright (27.0% vs. 9.7%/13.0%) tasks, though ReAct still leads on PostgreSQL (52.4% vs. CodeDelegator's 41.7%). Ablations on MCPMark show both proposed components matter: removing EPSS (replacing it with natural-language message passing) causes a 4.7% degradation, and further removing role separation entirely (collapsing to a single code-as-action agent) causes a 10.5% drop.</t>
+          <t>ContextRL improves over standard GRPO by average +2.2% across the 5 long-horizon benchmarks and +1.8% across the 12 multimodal benchmarks (headline abstract numbers); more granular per-model deltas are +3.2% (Klear-AgentForge-8B) and +1.5% (Qwen3-8B) on long-horizon, and +2.0% (Qwen2.5-VL-7B) and +1.6% (Qwen3-VL-8B) on multimodal, on average. On SWE-Bench Verified, ContextRL trained from Klear-AgentForge-8B reaches 30.2% versus RL-baseline 28.0% and base-model 26.6%, and substantially outperforms the 4x-larger Qwen3-32B (8.4%) and code-specialized Qwen3-Coder-30B (28.8%). On NIAH, standard GRPO regresses relative to the base model (98.8%-&gt;98.5% for Qwen3-8B) while ContextRL surpasses the base (99.0%). The contrastive-selection diagnostic probe shows roughly a 40-point gap: GPT-5.4 (99.0%) and Claude Opus 4.7 (98.0%) perform reliably while Qwen3 (VL) 8B (59.5%/58.0%) and Qwen3.5 9B (57.5%/52.5%) sit close to random chance (50%) on agent/multimodal splits respectively, despite competitive standard-benchmark performance. Data-augmentation baselines (DA-SFT, DA-RL) that consume the identical contrastive data via supervised fine-tuning or outcome-based RL 'collapse or fail entirely' -- supervised augmentation drives the long-horizon agent's resolve rate to as low as 0%, while outcome-based augmentation adds essentially nothing.</t>
         </is>
       </c>
       <c r="F111" s="5" t="n"/>
@@ -6392,7 +6388,7 @@
       <c r="H111" s="5" t="n"/>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>894af73fb679f95ea1a36eb6bad300bfb80566fa</t>
+          <t>72b5e6023db3b5af8e8f27f8b4a52bc5f1f32ba7</t>
         </is>
       </c>
     </row>
@@ -6402,7 +6398,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>CodeDelegator: Mitigating Context Pollution via Role Separation in Code-as-Action Agents</t>
+          <t>Context-Aware RL for Agentic and Multimodal LLMs</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -6417,7 +6413,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>ReAct (interleaved reasoning-and-action with structured text, one tool invocation per step) and CodeAct (executable Python as the action space supporting control flow and multi-tool composition within single actions, adapted to a JSON-based function-call interface for evaluation compatibility) -- both operating as single-agent systems with a single shared context across the entire task, isolating the effect of CodeDelegator's hierarchical delegation and EPSS mechanisms. Internal ablations (w/o EPSS, w/o Role Separation) are also used as component-level baselines.</t>
+          <t>Standard GRPO (outcome-only RL) as the primary RL baseline; off-the-shelf larger reference models (Qwen3-14B, Qwen3-32B, Qwen3-Coder-30B) for scale comparison; data-augmentation ablations (DA-SFT and DA-RL) that repurpose the same contrastive context pairs as ordinary query-context-answer training examples rather than via the context-selection auxiliary loss, used to isolate whether gains come from the data or the objective; PAPO cited as a comparison point in the multimodal results table.</t>
         </is>
       </c>
       <c r="F112" s="5" t="n"/>
@@ -6425,7 +6421,7 @@
       <c r="H112" s="5" t="n"/>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>894af73fb679f95ea1a36eb6bad300bfb80566fa</t>
+          <t>72b5e6023db3b5af8e8f27f8b4a52bc5f1f32ba7</t>
         </is>
       </c>
     </row>
@@ -6435,7 +6431,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>CodeDelegator: Mitigating Context Pollution via Role Separation in Code-as-Action Agents</t>
+          <t>Context-Aware RL for Agentic and Multimodal LLMs</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -6450,7 +6446,7 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>N/A - non-adversarial. This is an agent-architecture/context-management paper, not a security paper; the incidental failure mode of interest is 'context pollution' -- when a single code-as-action agent handles both strategic planning and detailed code implementation within one shared context window, debugging traces, intermediate failures, and error-correction attempts from implementation steps progressively dilute and overshadow the task-relevant planning information (exacerbated by the fact that later tokens progressively overshadow earlier content), degrading both planning and implementation capabilities over long-horizon, multi-step tasks.</t>
+          <t>N/A - non-adversarial. This is a capability/training-method paper, not a security or red-teaming study. The incidental failure mode of interest, termed 'context unawareness,' is that models make locally plausible but context-inconsistent predictions even when the decisive evidence is present in the input -- e.g., an agent removes a variable definition still referenced elsewhere in a long code trajectory causing a runtime error, or a VQA model misreads a value in a dense image -- reflecting a failure to ground predictions in available evidence rather than any adversarial manipulation of the context.</t>
         </is>
       </c>
       <c r="F113" s="5" t="n"/>
@@ -6458,7 +6454,7 @@
       <c r="H113" s="5" t="n"/>
       <c r="I113" s="5" t="inlineStr">
         <is>
-          <t>894af73fb679f95ea1a36eb6bad300bfb80566fa</t>
+          <t>72b5e6023db3b5af8e8f27f8b4a52bc5f1f32ba7</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6464,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>CodeDelegator: Mitigating Context Pollution via Role Separation in Code-as-Action Agents</t>
+          <t>Context-Aware RL for Agentic and Multimodal LLMs</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -6483,7 +6479,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>The paper contains an explicit 'Limitations' section (following the Conclusion), stating directly: the current CodeDelegator implementation adopts a sequential task decomposition strategy, which simplifies planning but does not yet support more expressive agent patterns such as directed acyclic graphs (DAGs) of sub-tasks or asynchronous interaction with the environment. In real-world scenarios, tasks often involve parallelizable subtasks or require concurrent tool execution (e.g., monitoring data streams while processing other steps), and the current linear, synchronous agent design may thus underutilize resources and incur unnecessary latency. Extending CodeDelegator to reason about DAG-structured plans and support asynchronous execution and communication while preserving isolation guarantees across multiple agents is stated as an important direction for future work.</t>
+          <t>No 'Limitations' section appears in the main body; a dedicated 'G Limitations' appendix section states two explicit limitations: (1) due to computational constraints, all experiments use base models under 10B parameters, so ContextRL has not been validated at substantially larger scales (30B+ or 70B+); (2) the majority of evaluated base models are drawn from the Qwen family, so validating ContextRL across a broader set of model families would strengthen the generality of the claims. An adjacent 'H Broader Impacts' appendix notes the method could in principle be used to amplify harmful applications like any capability-strengthening technique, though it requires no additional sensitive data and the authors do not anticipate negative societal impacts.</t>
         </is>
       </c>
       <c r="F114" s="5" t="n"/>
@@ -6491,7 +6487,7 @@
       <c r="H114" s="5" t="n"/>
       <c r="I114" s="5" t="inlineStr">
         <is>
-          <t>894af73fb679f95ea1a36eb6bad300bfb80566fa</t>
+          <t>72b5e6023db3b5af8e8f27f8b4a52bc5f1f32ba7</t>
         </is>
       </c>
     </row>
@@ -6501,7 +6497,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>CodeDelegator: Mitigating Context Pollution via Role Separation in Code-as-Action Agents</t>
+          <t>Context-Aware RL for Agentic and Multimodal LLMs</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -6516,7 +6512,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>CodeDelegator addresses 'context pollution' in code-as-action LLM agents (e.g., CodeAct), a phenomenon where using a single agent to handle both strategic task planning (decomposing tasks, analyzing dependencies) and detailed code implementation (writing syntactically correct code, handling errors, debugging) within one shared context causes debugging traces and intermediate failures to progressively dilute task-relevant information, degrading both planning and implementation quality over long-horizon interactions -- a tension the authors empirically demonstrate in a preliminary tau2-bench airline-domain study showing CodeAct's larger context footprint yields inconsistent, often negative, returns relative to ReAct depending on task difficulty. The proposed solution is a two-role multi-agent architecture with strict role separation: a persistent Delegator maintains strategic oversight -- decomposing tasks, writing sub-task specifications, monitoring progress, and dynamically dispatching work -- but never writes or executes implementation code itself, while for each sub-task a new, ephemeral Coder agent is instantiated with a clean context containing only that sub-task's specification, shielding it from the accumulated failures and debugging traces of prior sub-tasks; each Coder executes an interactive generate-observe-diagnose loop within its own isolated execution sandbox, and is discarded upon completion, with its local variables and debugging traces never propagating back to the Delegator. Coordination between the persistent Delegator and ephemeral Coders is managed via Ephemeral-Persistent State Separation (EPSS), a dual-layer workspace architecture: a persistent Orchestration Layer holds global state, task plans, and committed (validated) results, while each Coder's ephemeral execution sandbox confines its local variables and debugging traces, which are discarded upon sub-task completion. Inter-agent communication uses typed, asymmetric, schema-driven messaging rather than lossy natural-language summaries: downward messages carry a typed specification with input object-reference bindings, while upward messages return only artifact references, a summary, and diagnostics -- explicitly excluding raw execution traces -- allowing Coders to manipulate large objects without printing their full contents into context, while the Delegator maintains a compact, near-linear-size planning state. This design is evaluated against ReAct and CodeAct baselines (both single-agent, single-shared-context systems) on tau2-bench (Retail and Airline domains) and MCPMark (a CRUD-heavy multi-MCP-service benchmark spanning Filesystem, GitHub, Notion, Playwright, and PostgreSQL), with ablations confirming both EPSS's structured communication and the underlying dual-agent role separation contribute meaningfully and independently to the overall performance gains.</t>
+          <t>ContextRL augments standard GRPO post-training with an auxiliary context-selection loss that trains the policy to distinguish an anchor context (which supports a given query-answer pair) from a superficially similar confounder context that does not, rather than only rewarding correct final answers. Contrastive context pairs are constructed differently per domain: for coding agents, 1k pairs are built from SWE-smith trajectories via condition filtering (selecting trajectory variants that differ in a way that flips the outcome); for multimodal reasoning, 7K image pairs are built via generative image editing and similarity-based retrieval to produce near-duplicate images that support different answers. The combined training objective is L(theta) = E[L_GRPO] + lambda*E[L_CA], where L_CA is a logit-level contrastive loss favoring the context aligned with the ground-truth answer, applied inside the on-policy GRPO loop with importance-ratio clipping bounding the auxiliary gradient's influence. The central methodological contribution is disentangling the effect of the training objective from the effect of merely having more/better data: ablations that feed the identical contrastive pairs into SFT or outcome-based RL fail to reproduce the gains, indicating the context-selection reward mechanism itself -- not the data -- drives improved grounding in both long-horizon agentic and multimodal settings.</t>
         </is>
       </c>
       <c r="F115" s="5" t="n"/>
@@ -6524,7 +6520,7 @@
       <c r="H115" s="5" t="n"/>
       <c r="I115" s="5" t="inlineStr">
         <is>
-          <t>894af73fb679f95ea1a36eb6bad300bfb80566fa</t>
+          <t>72b5e6023db3b5af8e8f27f8b4a52bc5f1f32ba7</t>
         </is>
       </c>
     </row>
@@ -6534,7 +6530,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Compile, Then Page: Executable SOP Programs and a Capability-Gated Runtime for Procedural LLM Agents</t>
+          <t>Hybrid Real-time Framework for Detecting Adaptive Prompt Injection Attacks in Large Language Models</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -6557,7 +6553,7 @@
       <c r="H116" s="5" t="n"/>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>62e953c40357cfb93027ef8e55b60eacd76bc963</t>
+          <t>dd8e3ff740ecd615b37dfb219d98e73a782f71d1</t>
         </is>
       </c>
     </row>
@@ -6567,7 +6563,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Compile, Then Page: Executable SOP Programs and a Capability-Gated Runtime for Procedural LLM Agents</t>
+          <t>Hybrid Real-time Framework for Detecting Adaptive Prompt Injection Attacks in Large Language Models</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -6582,7 +6578,7 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>ML/AI</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="F117" s="5" t="n"/>
@@ -6590,7 +6586,7 @@
       <c r="H117" s="5" t="n"/>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>62e953c40357cfb93027ef8e55b60eacd76bc963</t>
+          <t>dd8e3ff740ecd615b37dfb219d98e73a782f71d1</t>
         </is>
       </c>
     </row>
@@ -6600,7 +6596,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Compile, Then Page: Executable SOP Programs and a Capability-Gated Runtime for Procedural LLM Agents</t>
+          <t>Hybrid Real-time Framework for Detecting Adaptive Prompt Injection Attacks in Large Language Models</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -6623,7 +6619,7 @@
       <c r="H118" s="5" t="n"/>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>62e953c40357cfb93027ef8e55b60eacd76bc963</t>
+          <t>dd8e3ff740ecd615b37dfb219d98e73a782f71d1</t>
         </is>
       </c>
     </row>
@@ -6633,7 +6629,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Compile, Then Page: Executable SOP Programs and a Capability-Gated Runtime for Procedural LLM Agents</t>
+          <t>Hybrid Real-time Framework for Detecting Adaptive Prompt Injection Attacks in Large Language Models</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -6656,7 +6652,7 @@
       <c r="H119" s="5" t="n"/>
       <c r="I119" s="5" t="inlineStr">
         <is>
-          <t>62e953c40357cfb93027ef8e55b60eacd76bc963</t>
+          <t>dd8e3ff740ecd615b37dfb219d98e73a782f71d1</t>
         </is>
       </c>
     </row>
@@ -6666,7 +6662,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Compile, Then Page: Executable SOP Programs and a Capability-Gated Runtime for Procedural LLM Agents</t>
+          <t>Hybrid Real-time Framework for Detecting Adaptive Prompt Injection Attacks in Large Language Models</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -6689,7 +6685,7 @@
       <c r="H120" s="5" t="n"/>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>62e953c40357cfb93027ef8e55b60eacd76bc963</t>
+          <t>dd8e3ff740ecd615b37dfb219d98e73a782f71d1</t>
         </is>
       </c>
     </row>
@@ -6699,7 +6695,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Compile, Then Page: Executable SOP Programs and a Capability-Gated Runtime for Procedural LLM Agents</t>
+          <t>Hybrid Real-time Framework for Detecting Adaptive Prompt Injection Attacks in Large Language Models</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -6714,7 +6710,7 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>goal-hijack</t>
         </is>
       </c>
       <c r="F121" s="5" t="n"/>
@@ -6722,7 +6718,7 @@
       <c r="H121" s="5" t="n"/>
       <c r="I121" s="5" t="inlineStr">
         <is>
-          <t>62e953c40357cfb93027ef8e55b60eacd76bc963</t>
+          <t>dd8e3ff740ecd615b37dfb219d98e73a782f71d1</t>
         </is>
       </c>
     </row>
@@ -6732,7 +6728,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Compile, Then Page: Executable SOP Programs and a Capability-Gated Runtime for Procedural LLM Agents</t>
+          <t>Hybrid Real-time Framework for Detecting Adaptive Prompt Injection Attacks in Large Language Models</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -6747,7 +6743,7 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F122" s="5" t="n"/>
@@ -6755,7 +6751,7 @@
       <c r="H122" s="5" t="n"/>
       <c r="I122" s="5" t="inlineStr">
         <is>
-          <t>62e953c40357cfb93027ef8e55b60eacd76bc963</t>
+          <t>dd8e3ff740ecd615b37dfb219d98e73a782f71d1</t>
         </is>
       </c>
     </row>
@@ -6765,7 +6761,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Compile, Then Page: Executable SOP Programs and a Capability-Gated Runtime for Procedural LLM Agents</t>
+          <t>Hybrid Real-time Framework for Detecting Adaptive Prompt Injection Attacks in Large Language Models</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -6780,7 +6776,7 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F123" s="5" t="n"/>
@@ -6788,7 +6784,7 @@
       <c r="H123" s="5" t="n"/>
       <c r="I123" s="5" t="inlineStr">
         <is>
-          <t>62e953c40357cfb93027ef8e55b60eacd76bc963</t>
+          <t>dd8e3ff740ecd615b37dfb219d98e73a782f71d1</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6794,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Compile, Then Page: Executable SOP Programs and a Capability-Gated Runtime for Procedural LLM Agents</t>
+          <t>Hybrid Real-time Framework for Detecting Adaptive Prompt Injection Attacks in Large Language Models</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -6813,7 +6809,7 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>execution</t>
+          <t>ingestion</t>
         </is>
       </c>
       <c r="F124" s="5" t="n"/>
@@ -6821,7 +6817,7 @@
       <c r="H124" s="5" t="n"/>
       <c r="I124" s="5" t="inlineStr">
         <is>
-          <t>62e953c40357cfb93027ef8e55b60eacd76bc963</t>
+          <t>dd8e3ff740ecd615b37dfb219d98e73a782f71d1</t>
         </is>
       </c>
     </row>
@@ -6831,7 +6827,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Compile, Then Page: Executable SOP Programs and a Capability-Gated Runtime for Procedural LLM Agents</t>
+          <t>Hybrid Real-time Framework for Detecting Adaptive Prompt Injection Attacks in Large Language Models</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -6846,7 +6842,7 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>session-persistent</t>
+          <t>one-shot</t>
         </is>
       </c>
       <c r="F125" s="5" t="n"/>
@@ -6854,7 +6850,7 @@
       <c r="H125" s="5" t="n"/>
       <c r="I125" s="5" t="inlineStr">
         <is>
-          <t>62e953c40357cfb93027ef8e55b60eacd76bc963</t>
+          <t>dd8e3ff740ecd615b37dfb219d98e73a782f71d1</t>
         </is>
       </c>
     </row>
@@ -6864,7 +6860,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Compile, Then Page: Executable SOP Programs and a Capability-Gated Runtime for Procedural LLM Agents</t>
+          <t>Hybrid Real-time Framework for Detecting Adaptive Prompt Injection Attacks in Large Language Models</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -6887,7 +6883,7 @@
       <c r="H126" s="5" t="n"/>
       <c r="I126" s="5" t="inlineStr">
         <is>
-          <t>62e953c40357cfb93027ef8e55b60eacd76bc963</t>
+          <t>dd8e3ff740ecd615b37dfb219d98e73a782f71d1</t>
         </is>
       </c>
     </row>
@@ -6897,7 +6893,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Compile, Then Page: Executable SOP Programs and a Capability-Gated Runtime for Procedural LLM Agents</t>
+          <t>Hybrid Real-time Framework for Detecting Adaptive Prompt Injection Attacks in Large Language Models</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -6910,17 +6906,13 @@
           <t>secondary</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
-        <is>
-          <t>No public GitHub/HuggingFace link is given; the paper instead describes an 'anonymous archive' submitted for review, consistent with double-blind review. Appendix H states: 'The anonymous archive contains the compiler, runtime snapshot and PG extension, adapter, aggregate/per-task result JSONs used by the paper, generated programs, analysis scripts, configuration templates without credentials, and a SHA-256 manifest,' with raw provider traces/conversation states omitted for privacy but anonymous aggregates included; the main-text Limitations item (vi) states plainly 'Artifacts will be released,' i.e., public release is promised post-review but not yet available under an identifiable URL.</t>
-        </is>
-      </c>
+      <c r="E127" s="2" t="n"/>
       <c r="F127" s="5" t="n"/>
       <c r="G127" s="5" t="n"/>
       <c r="H127" s="5" t="n"/>
       <c r="I127" s="5" t="inlineStr">
         <is>
-          <t>62e953c40357cfb93027ef8e55b60eacd76bc963</t>
+          <t>dd8e3ff740ecd615b37dfb219d98e73a782f71d1</t>
         </is>
       </c>
     </row>
@@ -6930,7 +6922,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Compile, Then Page: Executable SOP Programs and a Capability-Gated Runtime for Procedural LLM Agents</t>
+          <t>Hybrid Real-time Framework for Detecting Adaptive Prompt Injection Attacks in Large Language Models</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -6945,7 +6937,7 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Six models spanning capability tiers: DeepSeek-V4-Flash (low-cost workhorse), Qwen3.7-Plus (strong), GPT-4o-mini and Qwen2.5-7B-Instruct (weak), plus a same-vendor transition-probe pair Qwen3.6-27B/Qwen3.6-35B-A3B. The user simulator for all arms is DeepSeek-V4-Flash. Recomputed official SOPBench leaderboard reference configurations include o4-mini-high (FC), GPT-4o (FC), and Qwen2.5-32B (ReAct).</t>
+          <t>xlm-roberta-large fine-tuned as the semantic-analysis classifier (selected for its 24-layer architecture, ~250k shared subword vocabulary and pretraining over ~2.5 TB of text in 100 languages, argued to help with obfuscated and multilingual injection). Batch size 8, learning rate 2e-5, trained on an NVIDIA T4 GPU in Google Colab. No generative LLM is evaluated as a target system.</t>
         </is>
       </c>
       <c r="F128" s="5" t="n"/>
@@ -6953,7 +6945,7 @@
       <c r="H128" s="5" t="n"/>
       <c r="I128" s="5" t="inlineStr">
         <is>
-          <t>62e953c40357cfb93027ef8e55b60eacd76bc963</t>
+          <t>dd8e3ff740ecd615b37dfb219d98e73a782f71d1</t>
         </is>
       </c>
     </row>
@@ -6963,7 +6955,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Compile, Then Page: Executable SOP Programs and a Capability-Gated Runtime for Procedural LLM Agents</t>
+          <t>Hybrid Real-time Framework for Detecting Adaptive Prompt Injection Attacks in Large Language Models</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -6978,7 +6970,7 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>SOPBench (Li et al., 2025), specifically its Bank domain as the primary attribution benchmark (134 instances over 14 goals, screened down to a clean subset of 125 after excluding 9 defective execute tasks), plus a seven-domain replication (Bank, DMV, Healthcare, Hotel, Library, Online Market, University; 819 common instances for the three-arm V4 comparison) and an authorized, de-identified 13-function/87-step industrial workflow case for qualitative portability.</t>
+          <t>A single labeled prompt-injection classification dataset with a predefined stratified train-test split: 343 benign and 203 injection prompts for training, 56 benign and 60 injection prompts for testing. Minimal preprocessing by design - raw prompts tokenized with the xlm-roberta-large tokenizer, with no stop-word removal, stemming, lemmatization or normalization, on the grounds that such transformations could destroy the embedded malicious instruction patterns being detected. No agentic benchmark (AgentDojo, InjecAgent or similar) is used.</t>
         </is>
       </c>
       <c r="F129" s="5" t="n"/>
@@ -6986,7 +6978,7 @@
       <c r="H129" s="5" t="n"/>
       <c r="I129" s="5" t="inlineStr">
         <is>
-          <t>62e953c40357cfb93027ef8e55b60eacd76bc963</t>
+          <t>dd8e3ff740ecd615b37dfb219d98e73a782f71d1</t>
         </is>
       </c>
     </row>
@@ -6996,7 +6988,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Compile, Then Page: Executable SOP Programs and a Capability-Gated Runtime for Procedural LLM Agents</t>
+          <t>Hybrid Real-time Framework for Detecting Adaptive Prompt Injection Attacks in Large Language Models</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -7011,7 +7003,7 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>On the Bank clean subset with DeepSeek-V4-Flash, compiling the official SOP prose into executable pseudo-code text alone (no runtime) lifts pass rate 70.4%→86.4% (+16.0 points, McNemar 26:6, p&lt;0.001); adding the program-guided (PG) runtime on top adds a further +6.4 points to 92.8% (86.6% on the full 134-task set; 9:1, p=.021), with 100% refusal correctness (86/86). Across all six models the runtime effect is capability-gated: two strong models show independently positive seven-domain PG contrasts (58:19 and 75:31 discordant pairs favoring PG), while two weak models are harmed on Bank by 14–26 points (e.g., GPT-4o-mini drops from flat to pg 9:42 discordant, p&lt;0.001). A full-program cursor ablation (active frame surfaced first, complete program still resident) recovers most of the strong-model refusal gain, isolating the effect to state-discipline/salience rather than context reduction per se.</t>
+          <t>The fine-tuned detection model reports accuracy 0.974, precision 1.000, recall 0.950, and F1 0.974 on the held-out test split - i.e. no false positives and a small number of missed injections. The paper presents per-epoch validation loss, accuracy, precision, recall and F1 to argue stable convergence. These figures should be read against the evaluation's scale, which is small: the predefined stratified split provides 343 benign and 203 injection prompts for training (546 total) and only 56 benign and 60 injection prompts for testing (116 total), so precision of 1.000 rests on roughly sixty positive test cases and a single-run training regime. The analytical result is arguably the more transferable contribution: the argument that KAD's isolation assumption is unsound because detection instruction and untrusted data co-occupy one context window, which explains the observed fragility of KAD against adaptive attacks like DataFlip and motivates behavior-level rather than input-level checks. Reported coverage gaps from the cross-mapping - notably that most existing defenses give only limited protection against indirect prompt injection and obfuscated attacks, and that architectural patterns constrain execution without detecting successful injection - are conclusions drawn from the literature review rather than from measurements taken here.</t>
         </is>
       </c>
       <c r="F130" s="5" t="n"/>
@@ -7019,7 +7011,7 @@
       <c r="H130" s="5" t="n"/>
       <c r="I130" s="5" t="inlineStr">
         <is>
-          <t>62e953c40357cfb93027ef8e55b60eacd76bc963</t>
+          <t>dd8e3ff740ecd615b37dfb219d98e73a782f71d1</t>
         </is>
       </c>
     </row>
@@ -7029,7 +7021,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Compile, Then Page: Executable SOP Programs and a Capability-Gated Runtime for Procedural LLM Agents</t>
+          <t>Hybrid Real-time Framework for Detecting Adaptive Prompt Injection Attacks in Large Language Models</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -7044,7 +7036,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>A three-arm within-harness design: 'offtext' (official verbalized SOP prose, resident every turn — the standard SOP-as-prompt baseline), 'flat' (full text of the compiled pseudo-code program, resident every turn — isolates compilation from runtime), and 'pg' (the same compiled program executed by the paging program-guided runtime — isolates the runtime/paging effect). Diagnostic control arms further separate generic bookkeeping, active-frame salience (full-cursor ablation), and selective visibility, and a content×format 2×2 factorial (official/compiled content × prose/code format) isolates compilation from mere code-formatting. Recomputed official SOPBench leaderboard configurations (o4-mini-high, GPT-4o, Qwen2.5-32B, Qwen2.5-7B) serve as an external reference point.</t>
+          <t>No head-to-head empirical comparison against implemented competing detectors. Comparison is analytical: existing defense families (RLHF, input/output filtering, Known-Answer Detection, LLM supervisor, encoding-based defenses, architectural patterns) are cross-mapped against attack types in Table 3 and argued to leave systematic gaps, with KAD singled out as structurally vulnerable to adaptive attacks such as DataFlip. The reported 0.974/1.000/0.950/0.974 figures are for the proposed model alone, not measured against a baseline detector on the same split.</t>
         </is>
       </c>
       <c r="F131" s="5" t="n"/>
@@ -7052,7 +7044,7 @@
       <c r="H131" s="5" t="n"/>
       <c r="I131" s="5" t="inlineStr">
         <is>
-          <t>62e953c40357cfb93027ef8e55b60eacd76bc963</t>
+          <t>dd8e3ff740ecd615b37dfb219d98e73a782f71d1</t>
         </is>
       </c>
     </row>
@@ -7062,7 +7054,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Compile, Then Page: Executable SOP Programs and a Capability-Gated Runtime for Procedural LLM Agents</t>
+          <t>Hybrid Real-time Framework for Detecting Adaptive Prompt Injection Attacks in Large Language Models</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -7075,17 +7067,13 @@
           <t>freetext</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
-        <is>
-          <t>N/A - non-adversarial (though the domain is safety-critical procedure compliance, e.g., banking/healthcare refusal rules). The incidental failure mode of interest is that resident, unstructured SOP prose in the context window degrades a model's procedure-following under attention competition with the dialogue ('lost in the middle'-style interference), causing skipped verification checks, premature actions, and incorrect refusals; paging is explicitly described as 'soft — attention, not permissions,' so enforcement can be silently bypassed by a model that fails to respect the active frame, which is why the paper stresses irreversible actions still need hard tool-layer guards.</t>
-        </is>
-      </c>
+      <c r="E132" s="2" t="n"/>
       <c r="F132" s="5" t="n"/>
       <c r="G132" s="5" t="n"/>
       <c r="H132" s="5" t="n"/>
       <c r="I132" s="5" t="inlineStr">
         <is>
-          <t>62e953c40357cfb93027ef8e55b60eacd76bc963</t>
+          <t>dd8e3ff740ecd615b37dfb219d98e73a782f71d1</t>
         </is>
       </c>
     </row>
@@ -7095,7 +7083,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Compile, Then Page: Executable SOP Programs and a Capability-Gated Runtime for Procedural LLM Agents</t>
+          <t>Hybrid Real-time Framework for Detecting Adaptive Prompt Injection Attacks in Large Language Models</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -7110,7 +7098,7 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Explicit 'Limitations' section (end of main text) lists: (i) evaluated on one benchmark (seven domains); (ii) simulator/harness differences from the official leaderboard may leave residual affinity despite offtext/anchor/turn-budget controls; (iii) only six models tested, no quantitative capability scale to predict the gate threshold; (iv) pass@1 without sampling-variance estimates (though re-runs preserve each model's gate side); (v) only machine-readable dependency trees were evaluated — natural-language SOP input is unevaluated, and the industrial case is qualitative portability evidence only, not compiler validation; (vi) the decoupling separates protocol-compilation from paging but not state-externalization from disclosure, and artifacts are not yet released (promised for later).</t>
+          <t>The evaluation is small and single-run: 546 training prompts and 116 test prompts, trained once on the dataset's predefined stratified split, so the headline metrics - especially precision of 1.000 - carry wide uncertainty and no variance is reported across seeds or folds. The defense is evaluated on a static labeled corpus of prompts rather than against adaptive adversaries, which is a notable gap given that the paper's own central argument is that KAD fails specifically because attackers adapt to the detector; no adaptive attack (including DataFlip, which motivates the work) is actually run against the proposed framework. The semantic layer's reliance on a repository of known malicious examples inherits a coverage problem the paper itself raises about filtering approaches - whether sufficiently novel obfuscation or encoding can evade it remains open. Deployability constraints are acknowledged rather than measured: the embedding store is prescribed to stay under roughly one million records and 1,000 dimensions for low-latency search, and the latency penalty appears in the training objective, but no end-to-end latency or throughput measurements are reported.</t>
         </is>
       </c>
       <c r="F133" s="5" t="n"/>
@@ -7118,7 +7106,7 @@
       <c r="H133" s="5" t="n"/>
       <c r="I133" s="5" t="inlineStr">
         <is>
-          <t>62e953c40357cfb93027ef8e55b60eacd76bc963</t>
+          <t>dd8e3ff740ecd615b37dfb219d98e73a782f71d1</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7116,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Compile, Then Page: Executable SOP Programs and a Capability-Gated Runtime for Procedural LLM Agents</t>
+          <t>Hybrid Real-time Framework for Detecting Adaptive Prompt Injection Attacks in Large Language Models</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -7143,7 +7131,7 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>The paper treats an enterprise SOP not as text to paste into a prompt but as a program to compile and execute. An offline, deterministic compiler translates a benchmark's machine-readable dependency constraints (the same source its official verbalizer renders as prose) into a two-layer pseudo-code program: process functions (one per user goal) that call rule subroutines, each pairing a constraint with a concrete verification recipe and an evidence-bearing {holds, evidence} return; five mechanisms (stateful subroutines, transitive verifier-gate hoisting, etc.) make this transformation executable rather than cosmetic. An online program-guided (PG) runtime then executes this program as a two-layer virtual machine: a symbolic stack machine handles bookkeeping (call stack, cursor, variables, recovery) and pages only the currently active frame into the LLM's context, while the LLM itself performs semantic execution — conversing, calling tools, and judging whether evidence satisfies a predicate. Enforcement is deliberately 'soft' (attention-based paging, not a hard permission system), trading guaranteed compliance for flexibility, with correctness resting on the model faithfully respecting the active frame. A three-arm design (official prose vs. compiled text vs. compiled program+runtime) on SOPBench, run across six models spanning capability tiers, decomposes end-to-end gains into a compilation effect (representation) and a runtime effect (paging), finding the former is broadly beneficial or neutral while the latter is capability-gated — helping strong models (via improved refusal discipline) while actively harming weak models, a divide traced via full-program cursor ablations to spontaneous state discipline rather than reconstruction ability, and corroborated at the attention level.</t>
+          <t>Proposes a hybrid, multi-layered, real-time detection framework for prompt injection, motivated by a structured review of why single-point defenses fail. The review contribution is a cross-mapping (its Table 3) of ten attack types - direct injection, indirect prompt injection, data exfiltration, code injection, fraud/social engineering, malware transmission, manipulated content, DoS, role-playing/persona exploitation, and obfuscated attacks - against five defense families (RLHF, input/output filtering, Known-Answer Detection, LLM supervisor, encoding-based, architectural patterns), concluding that no existing strategy covers all attack types. Its sharpest analytical point concerns Known-Answer Detection: KAD assumes an injected task cannot observe or condition on the detection instruction, but since the detection instruction and the untrusted external data share one context window, that assumption is structurally false - which is why adaptive attacks such as DataFlip defeat it. The proposed defense responds with three complementary layers: (1) heuristic pre-filtering to discard obvious threats cheaply; (2) semantic analysis, embedding inputs and comparing them by cosine similarity against a vector-database repository of known malicious examples, so obfuscated prompts with no lexical overlap are still caught, backed by a fine-tuned transformer classifier; (3) behavioral pattern recognition applied post-hoc to whether the model behaved as intended, rather than to whether the input looked malicious. Layer scores are combined into a weighted risk score with a three-way decision - block, escalate, or allow - and the whole parameter set is trained by minimizing a composite loss that includes an explicit latency penalty to preserve real-time operation. Situated in this corpus as an ingestion-stage Track A defense whose novelty claim is coverage breadth across input, semantic and behavioral dimensions rather than a new detection primitive.</t>
         </is>
       </c>
       <c r="F134" s="5" t="n"/>
@@ -7151,7 +7139,7 @@
       <c r="H134" s="5" t="n"/>
       <c r="I134" s="5" t="inlineStr">
         <is>
-          <t>62e953c40357cfb93027ef8e55b60eacd76bc963</t>
+          <t>dd8e3ff740ecd615b37dfb219d98e73a782f71d1</t>
         </is>
       </c>
     </row>
@@ -7161,7 +7149,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Breaking ReAct Agents: Foot-in-the-Door Attack Will Get You In</t>
+          <t>DRIP: Defending Prompt Injection via Token-wise Representation Editing and Residual Instruction Fusion</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -7184,7 +7172,7 @@
       <c r="H135" s="5" t="n"/>
       <c r="I135" s="5" t="inlineStr">
         <is>
-          <t>6424243734d098460777049e1f11705d1b5d85c8</t>
+          <t>65d9d85b86ce1b8c3dd01a446ebf28d99fd26bdd</t>
         </is>
       </c>
     </row>
@@ -7194,7 +7182,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Breaking ReAct Agents: Foot-in-the-Door Attack Will Get You In</t>
+          <t>DRIP: Defending Prompt Injection via Token-wise Representation Editing and Residual Instruction Fusion</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -7217,7 +7205,7 @@
       <c r="H136" s="5" t="n"/>
       <c r="I136" s="5" t="inlineStr">
         <is>
-          <t>6424243734d098460777049e1f11705d1b5d85c8</t>
+          <t>65d9d85b86ce1b8c3dd01a446ebf28d99fd26bdd</t>
         </is>
       </c>
     </row>
@@ -7227,7 +7215,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Breaking ReAct Agents: Foot-in-the-Door Attack Will Get You In</t>
+          <t>DRIP: Defending Prompt Injection via Token-wise Representation Editing and Residual Instruction Fusion</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -7250,7 +7238,7 @@
       <c r="H137" s="5" t="n"/>
       <c r="I137" s="5" t="inlineStr">
         <is>
-          <t>6424243734d098460777049e1f11705d1b5d85c8</t>
+          <t>65d9d85b86ce1b8c3dd01a446ebf28d99fd26bdd</t>
         </is>
       </c>
     </row>
@@ -7260,7 +7248,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Breaking ReAct Agents: Foot-in-the-Door Attack Will Get You In</t>
+          <t>DRIP: Defending Prompt Injection via Token-wise Representation Editing and Residual Instruction Fusion</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -7275,7 +7263,7 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>defense</t>
         </is>
       </c>
       <c r="F138" s="5" t="n"/>
@@ -7283,7 +7271,7 @@
       <c r="H138" s="5" t="n"/>
       <c r="I138" s="5" t="inlineStr">
         <is>
-          <t>6424243734d098460777049e1f11705d1b5d85c8</t>
+          <t>65d9d85b86ce1b8c3dd01a446ebf28d99fd26bdd</t>
         </is>
       </c>
     </row>
@@ -7293,7 +7281,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Breaking ReAct Agents: Foot-in-the-Door Attack Will Get You In</t>
+          <t>DRIP: Defending Prompt Injection via Token-wise Representation Editing and Residual Instruction Fusion</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -7308,7 +7296,7 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F139" s="5" t="n"/>
@@ -7316,7 +7304,7 @@
       <c r="H139" s="5" t="n"/>
       <c r="I139" s="5" t="inlineStr">
         <is>
-          <t>6424243734d098460777049e1f11705d1b5d85c8</t>
+          <t>65d9d85b86ce1b8c3dd01a446ebf28d99fd26bdd</t>
         </is>
       </c>
     </row>
@@ -7326,7 +7314,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Breaking ReAct Agents: Foot-in-the-Door Attack Will Get You In</t>
+          <t>DRIP: Defending Prompt Injection via Token-wise Representation Editing and Residual Instruction Fusion</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -7349,7 +7337,7 @@
       <c r="H140" s="5" t="n"/>
       <c r="I140" s="5" t="inlineStr">
         <is>
-          <t>6424243734d098460777049e1f11705d1b5d85c8</t>
+          <t>65d9d85b86ce1b8c3dd01a446ebf28d99fd26bdd</t>
         </is>
       </c>
     </row>
@@ -7359,7 +7347,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Breaking ReAct Agents: Foot-in-the-Door Attack Will Get You In</t>
+          <t>DRIP: Defending Prompt Injection via Token-wise Representation Editing and Residual Instruction Fusion</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -7374,7 +7362,7 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F141" s="5" t="n"/>
@@ -7382,7 +7370,7 @@
       <c r="H141" s="5" t="n"/>
       <c r="I141" s="5" t="inlineStr">
         <is>
-          <t>6424243734d098460777049e1f11705d1b5d85c8</t>
+          <t>65d9d85b86ce1b8c3dd01a446ebf28d99fd26bdd</t>
         </is>
       </c>
     </row>
@@ -7392,7 +7380,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Breaking ReAct Agents: Foot-in-the-Door Attack Will Get You In</t>
+          <t>DRIP: Defending Prompt Injection via Token-wise Representation Editing and Residual Instruction Fusion</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -7415,7 +7403,7 @@
       <c r="H142" s="5" t="n"/>
       <c r="I142" s="5" t="inlineStr">
         <is>
-          <t>6424243734d098460777049e1f11705d1b5d85c8</t>
+          <t>65d9d85b86ce1b8c3dd01a446ebf28d99fd26bdd</t>
         </is>
       </c>
     </row>
@@ -7425,7 +7413,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Breaking ReAct Agents: Foot-in-the-Door Attack Will Get You In</t>
+          <t>DRIP: Defending Prompt Injection via Token-wise Representation Editing and Residual Instruction Fusion</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -7440,7 +7428,7 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>reasoning</t>
         </is>
       </c>
       <c r="F143" s="5" t="n"/>
@@ -7448,7 +7436,7 @@
       <c r="H143" s="5" t="n"/>
       <c r="I143" s="5" t="inlineStr">
         <is>
-          <t>6424243734d098460777049e1f11705d1b5d85c8</t>
+          <t>65d9d85b86ce1b8c3dd01a446ebf28d99fd26bdd</t>
         </is>
       </c>
     </row>
@@ -7458,7 +7446,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Breaking ReAct Agents: Foot-in-the-Door Attack Will Get You In</t>
+          <t>DRIP: Defending Prompt Injection via Token-wise Representation Editing and Residual Instruction Fusion</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -7481,7 +7469,7 @@
       <c r="H144" s="5" t="n"/>
       <c r="I144" s="5" t="inlineStr">
         <is>
-          <t>6424243734d098460777049e1f11705d1b5d85c8</t>
+          <t>65d9d85b86ce1b8c3dd01a446ebf28d99fd26bdd</t>
         </is>
       </c>
     </row>
@@ -7491,7 +7479,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Breaking ReAct Agents: Foot-in-the-Door Attack Will Get You In</t>
+          <t>DRIP: Defending Prompt Injection via Token-wise Representation Editing and Residual Instruction Fusion</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -7506,7 +7494,7 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F145" s="5" t="n"/>
@@ -7514,7 +7502,7 @@
       <c r="H145" s="5" t="n"/>
       <c r="I145" s="5" t="inlineStr">
         <is>
-          <t>6424243734d098460777049e1f11705d1b5d85c8</t>
+          <t>65d9d85b86ce1b8c3dd01a446ebf28d99fd26bdd</t>
         </is>
       </c>
     </row>
@@ -7524,7 +7512,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Breaking ReAct Agents: Foot-in-the-Door Attack Will Get You In</t>
+          <t>DRIP: Defending Prompt Injection via Token-wise Representation Editing and Residual Instruction Fusion</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -7539,7 +7527,7 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Code released, available on the project page (linked in the paper's footnote; no explicit GitHub URL given in the extracted text).</t>
+          <t>A demo/quantitative-study website is referenced ('DRIP anonymous website: Quantitative study for DRIP,' https://sites.google.com/view/drip-prompt/home), but no code repository (e.g., GitHub) or model checkpoint release is stated in the extracted text.</t>
         </is>
       </c>
       <c r="F146" s="5" t="n"/>
@@ -7547,7 +7535,7 @@
       <c r="H146" s="5" t="n"/>
       <c r="I146" s="5" t="inlineStr">
         <is>
-          <t>6424243734d098460777049e1f11705d1b5d85c8</t>
+          <t>65d9d85b86ce1b8c3dd01a446ebf28d99fd26bdd</t>
         </is>
       </c>
     </row>
@@ -7557,7 +7545,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Breaking ReAct Agents: Foot-in-the-Door Attack Will Get You In</t>
+          <t>DRIP: Defending Prompt Injection via Token-wise Representation Editing and Residual Instruction Fusion</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -7572,7 +7560,7 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>Mixtral-8x7B, Llama-3.1-70B, Llama-3-70B, and GPT-4o-mini as ReAct agent backbones under attack. GPT-4o-mini is also used as an LLM proxy to simulate realistic tool observations/responses. The Hesitation Reflector defense uses LLaMA-3-1-70B as the reflector model; GPT-4o is used to generate the harmless thoughts for benign-scenario false-positive testing.</t>
+          <t>LLaMA-8B and Mistral-7B are used as backbone models, fine-tuned with LoRA (rank r=16, alpha=8, dropout=0.05). Compared against baseline defenses StruQ, SecAlign, ISE, and PFT, each applied to the same two backbones, plus an Undefended (no fine-tuning) baseline.</t>
         </is>
       </c>
       <c r="F147" s="5" t="n"/>
@@ -7580,7 +7568,7 @@
       <c r="H147" s="5" t="n"/>
       <c r="I147" s="5" t="inlineStr">
         <is>
-          <t>6424243734d098460777049e1f11705d1b5d85c8</t>
+          <t>65d9d85b86ce1b8c3dd01a446ebf28d99fd26bdd</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7578,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Breaking ReAct Agents: Foot-in-the-Door Attack Will Get You In</t>
+          <t>DRIP: Defending Prompt Injection via Token-wise Representation Editing and Residual Instruction Fusion</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -7605,7 +7593,7 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>Built on the InjectAgent benchmark (Zhan et al., 2024): Direct Harm (DH) attacks (510 distinct single-action harmful attacks, the paper's primary focus) and Data Steal (DS) attacks (544 attacks targeting sensitive information extraction, results in Appendix). Additional custom benchmarks introduced: 8 distractor tools (familiar and unfamiliar to the agent) for FITD evaluation, 4 position/timing configurations (P0/P1 x T0/T1) for distractor placement analysis, and 1,000 generated benign thoughts (via GPT-4o) for false-positive/precision testing of defenses. Metric: Attack Success Rate (ASR) based on valid tool-call outputs (excluding invalid/malformed outputs per InjectAgent's categorization).</t>
+          <t>Evaluated on three prompt injection benchmarks: (1) SEP (9,160 tuples covering domains like information retrieval, content generation, and analytical reasoning, measuring semantic role separation via a witness-string mechanism); (2) AlpacaFarm/Alpaca Evaluation Benchmark (208 filtered examples under the StruQ evaluation protocol, testing 5 heuristic-based attack families -- Naive, Ignore, Completion, Escape, HackaPrompt -- plus optimization-based attacks GCG and NeuralExec); (3) InjecAgent (1,054 test cases combining 17 user tools with 62 attacker tools/injected instructions in ReAct-style agentic tool-use scenarios, evaluated under the 'Enhanced' adversarial-prefix setting). Utility is evaluated on AlpacaEval 2.0, IFEval, and MT-Bench.</t>
         </is>
       </c>
       <c r="F148" s="5" t="n"/>
@@ -7613,7 +7601,7 @@
       <c r="H148" s="5" t="n"/>
       <c r="I148" s="5" t="inlineStr">
         <is>
-          <t>6424243734d098460777049e1f11705d1b5d85c8</t>
+          <t>65d9d85b86ce1b8c3dd01a446ebf28d99fd26bdd</t>
         </is>
       </c>
     </row>
@@ -7623,7 +7611,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Breaking ReAct Agents: Foot-in-the-Door Attack Will Get You In</t>
+          <t>DRIP: Defending Prompt Injection via Token-wise Representation Editing and Residual Instruction Fusion</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -7638,7 +7626,7 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>The Foot-in-the-Door (FITD) attack (prepending a harmless distractor request before the malicious IPI payload) raises mean ASR from 41.9% (vanilla IPI) to 76.4% with familiar distractor tools (an average +34.5 point increase across models), with the largest single-model jump being +44.8 points for GPT-4o-mini (9.3% to 65.5%/54.1% depending on distractor) and +36.3 points for Llama-3-70B. Even with an unfamiliar/inaccessible distractor tool, FITD still raises mean ASR by about 15 points (41.9% to 47-57% depending on tool), demonstrating the effect doesn't require a functioning distractor. A direct 'thought injection' (TI) manipulation -- embedding the malicious intent directly into the agent's initial thought -- pushes ASR above 95% across all models (mean 87.8% for TI alone, 97.1% combined with FITD), and even a 'harmless thought injection' (HTI, only the benign request embedded in the thought) reaches 93.0% mean ASR, confirming that once an action enters the agent's thought, it is executed almost without re-evaluation. Distractor placement matters: the distractor's physical position in the input has a larger effect on ASR (13.1-point difference between early vs. late position) than its chronological timing (4.6-point difference). Of three proposed reflection-based defenses, Self-Reflection (simple prompt addition) gives only modest, inconsistent gains (up to ~15% ASR reduction for IPI in some models); Hesitation Reflection (a dedicated LLaMA-3-70B-based reflector checking for hesitation/reluctance in the agent's thought) provides stable, consistent protection with 0% false positives on 1,000 benign thoughts tested; Safe Reflection (a more general safety reflector evaluating overall appropriateness of each action) is the most effective, substantially reducing attack success (described as 'over 90% effectiveness' in the abstract) but at the cost of a 16% false-positive rate on benign thoughts.</t>
+          <t>On the SEP benchmark, DRIP achieves the highest role-separation score (80.9% on LLaMA-8B, 70.7% on Mistral-7B), outperforming the strongest baseline SecAlign by 49.0 and 12.1 points respectively (Table 3), while ISE and PFT substantially underperform. On AlpacaFarm (Table 5), DRIP achieves 0.0% ASR across nearly all heuristic-based attack families (Naive, Ignore, Completion, Escape, HackaPrompt) on both backbones, and against the strongest optimization-based attack (GCG), DRIP reduces ASR to 1.06% (LLaMA-8B) and 3.37% (Mistral-7B), while all baselines (including SecAlign) exceed 66% ASR under GCG -- a reduction of over 66 percentage points. On InjecAgent (Table 4), DRIP achieves low ASR (0.5% LLaMA-8B, 1.5% Mistral-7B) comparable to or better than SecAlign, while ISE fails completely (marked NA because its responses don't follow the required ReAct format). Utility evaluation (Table 6, IFEval/MT-Bench/AlpacaEval) shows DRIP maintains instruction-following performance comparable to the undefended model, i.e., security gains are not achieved at the cost of utility. Representation-editing visualizations show the learned embedding shift is most pronounced near the data-segment boundary and around directive-intent phrases (e.g., 'ignore all instructions'), and attention-reallocation analysis shows DRIP assigns lower attention weight to injected spans while reinforcing attention on the legitimate top-level instruction, relative to the undefended model.</t>
         </is>
       </c>
       <c r="F149" s="5" t="n"/>
@@ -7646,7 +7634,7 @@
       <c r="H149" s="5" t="n"/>
       <c r="I149" s="5" t="inlineStr">
         <is>
-          <t>6424243734d098460777049e1f11705d1b5d85c8</t>
+          <t>65d9d85b86ce1b8c3dd01a446ebf28d99fd26bdd</t>
         </is>
       </c>
     </row>
@@ -7656,7 +7644,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Breaking ReAct Agents: Foot-in-the-Door Attack Will Get You In</t>
+          <t>DRIP: Defending Prompt Injection via Token-wise Representation Editing and Residual Instruction Fusion</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -7671,7 +7659,7 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>Vanilla Indirect Prompt Injection (IPI, reproduced from the InjectAgent benchmark) serves as the primary baseline against which FITD (familiar and unfamiliar distractor variants), Thought Injection (TI), and Harmless Thought Injection (HTI) are compared. For defenses, the paper compares its own three reflection-based methods (Self-Reflection, Hesitation Reflection, Safe Reflection) against the undefended agent and against each other, rather than against external prior defense baselines.</t>
+          <t>Compared against Undefended (no fine-tuning), StruQ (adversarial SFT with role-specific delimiter tokens), SecAlign (StruQ extended with DPO preference-based training, the strongest prior baseline), ISE (Instruct Segment Embedding layer adding learned role-offset embeddings), and PFT (fixed positional-ID gap of 512 between instruction and data segments).</t>
         </is>
       </c>
       <c r="F150" s="5" t="n"/>
@@ -7679,7 +7667,7 @@
       <c r="H150" s="5" t="n"/>
       <c r="I150" s="5" t="inlineStr">
         <is>
-          <t>6424243734d098460777049e1f11705d1b5d85c8</t>
+          <t>65d9d85b86ce1b8c3dd01a446ebf28d99fd26bdd</t>
         </is>
       </c>
     </row>
@@ -7689,7 +7677,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Breaking ReAct Agents: Foot-in-the-Door Attack Will Get You In</t>
+          <t>DRIP: Defending Prompt Injection via Token-wise Representation Editing and Residual Instruction Fusion</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -7704,7 +7692,7 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>Formal adversarial threat model, building on and extending indirect prompt injection (IPI): an attacker who lacks direct access to the agent embeds malicious instructions into external content the agent's tools will retrieve (e.g., a contaminated GitHub issue, email, or webpage), which the agent unknowingly processes -- consistent with standard IPI. The paper's novel contribution is the Foot-in-the-Door (FITD) attack, which additionally prepends a small, harmless, deceptive distractor request (e.g., a basic calculation) to the malicious instruction within the same injected content, exploiting a psychological-compliance-inspired hypothesis that once a ReAct agent complies with an initial harmless request without re-evaluation, it becomes more likely to comply with a subsequent malicious one embedded in the same injected context, because ReAct agents evaluate safety primarily during thought generation and rarely re-assess actions already incorporated into their thought process. The attack requires no direct access to the agent and minimal technical expertise, and remains effective even when the distractor tool is entirely unfamiliar/inaccessible to the agent.</t>
+          <t>Formal threat model for prompt injection: because conventional LLM architectures process user-provided data tokens and system-level instruction tokens through the same attention layers and shared representation space, the model can interpret any sufficiently directive phrase within the data as a higher-priority instruction; malicious users exploit this by injecting imperative or meta-instructional cues (e.g., 'ignore previous instructions,' 'switch roles and follow my command') within data, causing the model to elevate injected tokens to instruction-level semantics and overwrite the trusted, predefined instruction. The paper evaluates both heuristic-based attacks (hand-crafted prefix/suffix strings such as Naive, Ignore, Completion, Escape, HackaPrompt) and optimization-based attacks (GCG sample-specific gradient optimization, and NeuralExec model-universal optimization), plus an agentic tool-use threat model via InjecAgent where a successful attack causes the agent to execute a malicious API call (e.g., GrantAccess) under an enhanced adversarial prefix.</t>
         </is>
       </c>
       <c r="F151" s="5" t="n"/>
@@ -7712,7 +7700,7 @@
       <c r="H151" s="5" t="n"/>
       <c r="I151" s="5" t="inlineStr">
         <is>
-          <t>6424243734d098460777049e1f11705d1b5d85c8</t>
+          <t>65d9d85b86ce1b8c3dd01a446ebf28d99fd26bdd</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7710,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Breaking ReAct Agents: Foot-in-the-Door Attack Will Get You In</t>
+          <t>DRIP: Defending Prompt Injection via Token-wise Representation Editing and Residual Instruction Fusion</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -7737,7 +7725,7 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>The paper has an explicit 'Limitations' section (Section 8) stating: (1) the study focuses exclusively on ReAct agents, so findings may not generalize to other agent architectures/frameworks without further research; (2) the FITD investigation was conducted only in the context of IPI, and while the authors hypothesize FITD could similarly boost Direct Prompt Injection (DPI) effectiveness via harmless precursor requests, this remains unexplored; (3) experiments used a specific set of models (GPT-4o-mini, Mixtral-8x7B, Llama-3/3.1-70B), and although consistent attack success rates were observed across these, results may vary for larger, more specialized, or differently fine-tuned models not tested; (4) the proposed reflection-based defenses are explicitly described as preliminary (the sentence is cut off in the extracted text but is introduced with 'Although they...', implying acknowledged shortcomings such as the false-positive/alert-fatigue tradeoffs already discussed in Section 5.3).</t>
+          <t>The paper has no explicit 'Limitations' section; the closest analog is the forward-looking 'Looking forward' statement at the end of the Conclusion, which states the authors plan to extend DRIP to larger model scales, multi-turn interactions, and multimodal settings -- implicitly acknowledging the current evaluation is limited to two mid-sized backbones (LLaMA-8B, Mistral-7B), single-turn interactions, and text-only modality. The paper also notes within its discussion of prior work (Section 4.6.2/4.6.3) that detection-based and many inference-time defenses 'operate outside the generation process and offer no guarantee of safe behavior' or 'rely on brittle heuristics or task-specific instrumentation,' framing this as motivation for DRIP's finetuning-based approach rather than a limitation of DRIP itself.</t>
         </is>
       </c>
       <c r="F152" s="5" t="n"/>
@@ -7745,7 +7733,7 @@
       <c r="H152" s="5" t="n"/>
       <c r="I152" s="5" t="inlineStr">
         <is>
-          <t>6424243734d098460777049e1f11705d1b5d85c8</t>
+          <t>65d9d85b86ce1b8c3dd01a446ebf28d99fd26bdd</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7743,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Breaking ReAct Agents: Foot-in-the-Door Attack Will Get You In</t>
+          <t>DRIP: Defending Prompt Injection via Token-wise Representation Editing and Residual Instruction Fusion</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -7770,7 +7758,7 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>This paper introduces the Foot-in-the-Door (FITD) attack, a novel enhancement to indirect prompt injection (IPI) against ReAct-based LLM agents, inspired by the psychological compliance phenomenon where agreeing to a small request increases the likelihood of complying with a larger one. Building on the InjectAgent benchmark's IPI attacks (malicious instructions embedded in external tool-observable content like emails or GitHub issues), FITD prepends a small, harmless, seemingly unrelated distractor request (e.g., 'calculate 2+4') immediately before the malicious instruction within the same injected content. The authors' core hypothesis, validated via a 'thought injection' ablation technique that directly embeds content into the agent's ReAct-format initial thought, is that ReAct agents evaluate action safety almost exclusively during the thought-generation phase and rarely re-evaluate actions once they are incorporated into that thought -- so getting any action (even a harmless one) accepted into the thought process 'opens the door' for a subsequent malicious action to be executed with reduced scrutiny, mirroring the ReAct fine-tuning process's tendency to produce a structured, uninterrupted thought-then-action habit. Across four LLM backbones (Mixtral-8x7B, Llama-3.1-70B, Llama-3-70B, GPT-4o-mini) and InjectAgent's 510 Direct Harm attacks, FITD with a familiar distractor tool raises mean attack success rate from 41.9% (vanilla IPI) to 76.4%, and even with a distractor tool the agent has no access to, ASR still rises by roughly 15 points, demonstrating the effect is driven by psychological/behavioral compliance rather than the distractor's functional success. Direct thought injection confirms the underlying mechanism, pushing ASR above 95% across all models. The paper further characterizes the attack's sensitivity to distractor placement (position within input matters more than chronological timing) and, motivated by the finding that agents sometimes express hesitation in their thoughts yet proceed anyway, proposes and evaluates three reflection-based defenses of increasing intervention strength and cost: lightweight Self-Reflection prompting (weak, inconsistent gains), a dedicated Hesitation Reflector model that specifically detects expressed reluctance in the agent's thought (stable protection with zero measured false positives), and a more general Safe Reflector that broadly re-evaluates action appropriateness (strongest protection but with a meaningful 16% false-positive rate, raising alert-fatigue concerns for human-in-the-loop deployments).</t>
+          <t>This paper introduces DRIP (De-instructionalizing embedding and Residual design against Injection via representation editing and residual fusion of Instructions), a defense framework against prompt injection attacks that reformulates the problem as a representation-editing task rather than relying purely on architectural role-tagging (as in StruQ, ISE, PFT) or global preference optimization (as in SecAlign). DRIP addresses two identified weaknesses in prior defenses: first, that instruction-like tokens within data can carry meaningful data semantics that should be preserved rather than universally suppressed (e.g., in a translation task, the phrase 'now ignore previous instructions' appearing within the source text should be translated, not stripped or ignored, since stripping causes information loss); and second, that novel or distribution-shifted instruction tokens can still overwrite trained defenses under adaptive attack (demonstrated by up to 98% adaptive attack success against prior defenses). To address the first issue, DRIP introduces a lightweight, trainable representation-editing module trained via a contrastive learning paradigm across curated data-curation, model-architecture, and loss-design choices: given instruction-like tokens appearing in the data section, the module learns to edit their embeddings to push them away from the 'instruction manifold' in representation space -- precisely removing directive/instruction-level semantics while preserving their underlying data semantics (so the model neither over-reacts to nor blindly discards potentially task-relevant content). To address the second issue (non-overwritability of the true instruction), DRIP introduces a minimal residual instruction fusion module: an independent channel that carries the original user instruction directly into response generation, substantially reducing the ability of adversarial data content -- even strong, distribution-shifted, or gradient-optimized adversarial content -- to overwrite or override the intended instruction, since the legitimate instruction's influence on generation no longer flows solely through the same shared representation pathway that adversarial tokens can corrupt.</t>
         </is>
       </c>
       <c r="F153" s="5" t="n"/>
@@ -7778,7 +7766,7 @@
       <c r="H153" s="5" t="n"/>
       <c r="I153" s="5" t="inlineStr">
         <is>
-          <t>6424243734d098460777049e1f11705d1b5d85c8</t>
+          <t>65d9d85b86ce1b8c3dd01a446ebf28d99fd26bdd</t>
         </is>
       </c>
     </row>
@@ -7788,7 +7776,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Defending Against Prompt Injection with DataFilter</t>
+          <t>MCPTox: A Benchmark for Tool Poisoning on Real-World MCP Servers</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -7811,7 +7799,7 @@
       <c r="H154" s="5" t="n"/>
       <c r="I154" s="5" t="inlineStr">
         <is>
-          <t>7222e1b74675ebfd85d5f261ef8ab5010111e737</t>
+          <t>34df7d82136868e5d492968647efd17d442a6720</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7809,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Defending Against Prompt Injection with DataFilter</t>
+          <t>MCPTox: A Benchmark for Tool Poisoning on Real-World MCP Servers</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -7844,7 +7832,7 @@
       <c r="H155" s="5" t="n"/>
       <c r="I155" s="5" t="inlineStr">
         <is>
-          <t>7222e1b74675ebfd85d5f261ef8ab5010111e737</t>
+          <t>34df7d82136868e5d492968647efd17d442a6720</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7842,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Defending Against Prompt Injection with DataFilter</t>
+          <t>MCPTox: A Benchmark for Tool Poisoning on Real-World MCP Servers</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -7877,7 +7865,7 @@
       <c r="H156" s="5" t="n"/>
       <c r="I156" s="5" t="inlineStr">
         <is>
-          <t>7222e1b74675ebfd85d5f261ef8ab5010111e737</t>
+          <t>34df7d82136868e5d492968647efd17d442a6720</t>
         </is>
       </c>
     </row>
@@ -7887,7 +7875,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Defending Against Prompt Injection with DataFilter</t>
+          <t>MCPTox: A Benchmark for Tool Poisoning on Real-World MCP Servers</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -7902,7 +7890,7 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>defense</t>
+          <t>neither</t>
         </is>
       </c>
       <c r="F157" s="5" t="n"/>
@@ -7910,7 +7898,7 @@
       <c r="H157" s="5" t="n"/>
       <c r="I157" s="5" t="inlineStr">
         <is>
-          <t>7222e1b74675ebfd85d5f261ef8ab5010111e737</t>
+          <t>34df7d82136868e5d492968647efd17d442a6720</t>
         </is>
       </c>
     </row>
@@ -7920,7 +7908,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Defending Against Prompt Injection with DataFilter</t>
+          <t>MCPTox: A Benchmark for Tool Poisoning on Real-World MCP Servers</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -7935,7 +7923,7 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>tool-metadata</t>
         </is>
       </c>
       <c r="F158" s="5" t="n"/>
@@ -7943,7 +7931,7 @@
       <c r="H158" s="5" t="n"/>
       <c r="I158" s="5" t="inlineStr">
         <is>
-          <t>7222e1b74675ebfd85d5f261ef8ab5010111e737</t>
+          <t>34df7d82136868e5d492968647efd17d442a6720</t>
         </is>
       </c>
     </row>
@@ -7953,7 +7941,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Defending Against Prompt Injection with DataFilter</t>
+          <t>MCPTox: A Benchmark for Tool Poisoning on Real-World MCP Servers</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -7976,7 +7964,7 @@
       <c r="H159" s="5" t="n"/>
       <c r="I159" s="5" t="inlineStr">
         <is>
-          <t>7222e1b74675ebfd85d5f261ef8ab5010111e737</t>
+          <t>34df7d82136868e5d492968647efd17d442a6720</t>
         </is>
       </c>
     </row>
@@ -7986,7 +7974,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Defending Against Prompt Injection with DataFilter</t>
+          <t>MCPTox: A Benchmark for Tool Poisoning on Real-World MCP Servers</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -8009,7 +7997,7 @@
       <c r="H160" s="5" t="n"/>
       <c r="I160" s="5" t="inlineStr">
         <is>
-          <t>7222e1b74675ebfd85d5f261ef8ab5010111e737</t>
+          <t>34df7d82136868e5d492968647efd17d442a6720</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8007,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Defending Against Prompt Injection with DataFilter</t>
+          <t>MCPTox: A Benchmark for Tool Poisoning on Real-World MCP Servers</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -8042,7 +8030,7 @@
       <c r="H161" s="5" t="n"/>
       <c r="I161" s="5" t="inlineStr">
         <is>
-          <t>7222e1b74675ebfd85d5f261ef8ab5010111e737</t>
+          <t>34df7d82136868e5d492968647efd17d442a6720</t>
         </is>
       </c>
     </row>
@@ -8052,7 +8040,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Defending Against Prompt Injection with DataFilter</t>
+          <t>MCPTox: A Benchmark for Tool Poisoning on Real-World MCP Servers</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -8067,7 +8055,7 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>ingestion</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F162" s="5" t="n"/>
@@ -8075,7 +8063,7 @@
       <c r="H162" s="5" t="n"/>
       <c r="I162" s="5" t="inlineStr">
         <is>
-          <t>7222e1b74675ebfd85d5f261ef8ab5010111e737</t>
+          <t>34df7d82136868e5d492968647efd17d442a6720</t>
         </is>
       </c>
     </row>
@@ -8085,7 +8073,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Defending Against Prompt Injection with DataFilter</t>
+          <t>MCPTox: A Benchmark for Tool Poisoning on Real-World MCP Servers</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -8108,7 +8096,7 @@
       <c r="H163" s="5" t="n"/>
       <c r="I163" s="5" t="inlineStr">
         <is>
-          <t>7222e1b74675ebfd85d5f261ef8ab5010111e737</t>
+          <t>34df7d82136868e5d492968647efd17d442a6720</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8106,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Defending Against Prompt Injection with DataFilter</t>
+          <t>MCPTox: A Benchmark for Tool Poisoning on Real-World MCP Servers</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -8133,7 +8121,7 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F164" s="5" t="n"/>
@@ -8141,7 +8129,7 @@
       <c r="H164" s="5" t="n"/>
       <c r="I164" s="5" t="inlineStr">
         <is>
-          <t>7222e1b74675ebfd85d5f261ef8ab5010111e737</t>
+          <t>34df7d82136868e5d492968647efd17d442a6720</t>
         </is>
       </c>
     </row>
@@ -8151,7 +8139,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>Defending Against Prompt Injection with DataFilter</t>
+          <t>MCPTox: A Benchmark for Tool Poisoning on Real-World MCP Servers</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -8166,7 +8154,7 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>The trained DataFilter model (fine-tuned Llama-3.1-8B-Instruct) is released for immediate use, along with code to reproduce all results, both linked in the paper (footnote 1); the paper is to appear at IEEE SaTML 2026.</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F165" s="5" t="n"/>
@@ -8174,7 +8162,7 @@
       <c r="H165" s="5" t="n"/>
       <c r="I165" s="5" t="inlineStr">
         <is>
-          <t>7222e1b74675ebfd85d5f261ef8ab5010111e737</t>
+          <t>34df7d82136868e5d492968647efd17d442a6720</t>
         </is>
       </c>
     </row>
@@ -8184,7 +8172,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Defending Against Prompt Injection with DataFilter</t>
+          <t>MCPTox: A Benchmark for Tool Poisoning on Real-World MCP Servers</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -8199,7 +8187,7 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>DataFilter itself is a fine-tuned Llama-3.1-8B-Instruct filter model, evaluated protecting two backend LLMs: gpt-4o-2024-05-13 (primary backend across AgentDojo, InjecAgent, SEP) and Llama-3.1-8B-Instruct (secondary backend on InjecAgent and SEP); adaptive-attack and overhead experiments also test GPT-5.1 as a protected backend.</t>
+          <t>GPT-4o-mini, GPT-3.5-turbo; DeepSeek-R1, DeepSeek-V3; Qwen3-8b, Qwen3-14b, Qwen3-32b, Qwen3-235b-a22b (each with/without reasoning mode); Llama-3.1-8B, Llama-3.1-70B; o1-mini; Gemini-2.5-flash; Claude-3.7-sonnet; Phi-4; Gemma-2-9b; Mistral (20 model settings total)</t>
         </is>
       </c>
       <c r="F166" s="5" t="n"/>
@@ -8207,7 +8195,7 @@
       <c r="H166" s="5" t="n"/>
       <c r="I166" s="5" t="inlineStr">
         <is>
-          <t>7222e1b74675ebfd85d5f261ef8ab5010111e737</t>
+          <t>34df7d82136868e5d492968647efd17d442a6720</t>
         </is>
       </c>
     </row>
@@ -8217,7 +8205,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Defending Against Prompt Injection with DataFilter</t>
+          <t>MCPTox: A Benchmark for Tool Poisoning on Real-World MCP Servers</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -8232,7 +8220,7 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>AgentDojo (agentic tool-calling, 4 attack types: Direct, Ignore Previous, Important Instructions, Tool Knowledge; benign and under-attack utility), InjecAgent (indirect injections in tool-call outputs/observations, Base and Enhanced attacks), SEP (controlled instruction-following prompt-injection benchmark, 6 attacks: Straightforward, Ignore, Completion, Completion-Ignore, Multi-Turn-Completion, Context), and AlpacaEval2 (general instruction-following utility, length-controlled WinRate). The SFT training dataset for DataFilter is built from all 19K non-empty-data samples of the Alpaca instruction-tuning dataset with synthetic injections spliced in from other Alpaca samples.</t>
+          <t>MCPTox (new benchmark introduced by this paper): 1,312 malicious test cases built on 45 real-world MCP servers and 353 authentic tools spanning 8 application domains and 10 risk categories (e.g. Privacy Leakage, Message Hijacking), constructed via 3 attack paradigms (Explicit Trigger-Function Hijacking: 224 cases; Implicit Trigger-Function Hijacking: 548; Implicit Trigger-Parameter Tampering: 725); compared for effectiveness against repurposed InjecAgent payloads as a cross-benchmark reference</t>
         </is>
       </c>
       <c r="F167" s="5" t="n"/>
@@ -8240,7 +8228,7 @@
       <c r="H167" s="5" t="n"/>
       <c r="I167" s="5" t="inlineStr">
         <is>
-          <t>7222e1b74675ebfd85d5f261ef8ab5010111e737</t>
+          <t>34df7d82136868e5d492968647efd17d442a6720</t>
         </is>
       </c>
     </row>
@@ -8250,7 +8238,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Defending Against Prompt Injection with DataFilter</t>
+          <t>MCPTox: A Benchmark for Tool Poisoning on Real-World MCP Servers</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -8265,7 +8253,7 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>On AgentDojo (Table II), DataFilter reduces ASR to 1.2%/0.1%/0.2%/0.0% across Direct/Ignore Previous/Important Instructions/Tool Knowledge attacks respectively, versus 42.2% and 42.5% undefended ASR on the two strongest attacks, while maintaining 79.4% benign utility (only a 2-point drop from the undefended 81.4%, Table V) and the highest utility-under-attack of any defense (72.4-72.7% vs. next-best Sandwich's 68-78% with much worse security). On InjecAgent (Table III), DataFilter achieves 2.0%/0.0% (gpt-4o) and 2.1%/1.2% (Llama-3.1-8B) ASR on Base/Enhanced attacks, versus 34.4-38.6% and 23.1-37.8% undefended, outperforming PromptArmor (0.7-2.5% avg/max) and vastly outperforming Sandwich (12-14% and 10-14%). On SEP (Table IV) across 6 attacks and 2 backends, DataFilter is the only defense with consistently low ASR (1.4-3.4% on gpt-4o, 2.4-4.6% on Llama-3.1-8B), while all other defenses have blind spots exceeding 20-95% ASR against at least one attack type (e.g., Llama-3.1-8B undefended reaches 95% ASR on Completion-Ignore). Overall across all benchmarks: ASR drops from over 40% to about 2% on average with about 1% average utility loss. On AlpacaEval2, DataFilter shows negligible utility change (54.1%/26.2% vs. 54.0%/25.9% undefended). Against human-designed adaptive attacks targeting the filter itself, DataFilter still reduces ASR to below 1% (Table VII); against the strongest known optimization-based adaptive attack (a genetic-algorithm LLM-mutator attack that breaks all existing defenses), DataFilter achieves the lowest ASR among tested defenses at 83% (vs. 93-100% for others) while also preserving the highest utility (76.3%), though this remains a partial break, not full defense (Table VIII). Computational overhead is marginal: less than $0.0005 additional cost per sample and under 0.6s additional latency per sample (Table IX).</t>
+          <t>Widespread vulnerability to Tool Poisoning Attacks (TPA) across all 20 evaluated LLM agent settings, with an average Attack Success Rate (ASR) of 36.5% and the highest reaching 72.8% (o1-mini), followed by Phi-4 (70.2%), DeepSeek-R1 (70.9%), GPT-4o-mini (61.8%), and Qwen3-235b-a22b reasoning (50.6%). An inverse scaling effect is observed: more capable models (larger scale, or reasoning mode enabled) tend to show higher ASR - e.g. enabling Qwen3's reasoning mode increased average ASR by 27.8 points, and Qwen3-32B's ASR exceeded Qwen3-8B's. Implicit Trigger-Parameter Tampering is the most effective attack paradigm (46.7% average ASR), followed by Explicit Trigger-Function Hijacking (36.7%), with Implicit Trigger-Function Hijacking least effective (26.7%). Prepending classic hijacking/jailbreak prompts to the poisoned tool description only marginally increases ASR (+2.0% and +2.6% for two enhanced settings). Failure-mode analysis shows existing safety alignment is largely ineffective against TPA: even the highest-refusal model (Claude-3.7-Sonnet) rejects the attack in under 3% of cases, with most failures being either 'Ignored' or the still-risky 'Direct Execution' of the poisoned tool itself. Directly repurposing malicious payloads from the IPI benchmark InjecAgent as poisoned tool descriptions drops ASR to nearly 0% (0.1-14%) compared to MCPTox's purpose-built payloads (14-41.8%), confirming TPA requires a dedicated attack design distinct from IPI due to loss of contextual prominence when a payload sits in static tool metadata rather than a tool's execution output.</t>
         </is>
       </c>
       <c r="F168" s="5" t="n"/>
@@ -8273,7 +8261,7 @@
       <c r="H168" s="5" t="n"/>
       <c r="I168" s="5" t="inlineStr">
         <is>
-          <t>7222e1b74675ebfd85d5f261ef8ab5010111e737</t>
+          <t>34df7d82136868e5d492968647efd17d442a6720</t>
         </is>
       </c>
     </row>
@@ -8283,7 +8271,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>Defending Against Prompt Injection with DataFilter</t>
+          <t>MCPTox: A Benchmark for Tool Poisoning on Real-World MCP Servers</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -8298,7 +8286,7 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>Detection-based: PromptGuard and DataSentinel (game-theoretic vulnerable-detector fine-tuning). Prompt-based: Sandwich, Instructional, and Spotlighting (with delimiters). System-level: Tool Filter (restricts available tools before untrusted data is observed). Concurrent filtering approaches: PromptArmor (queries the OpenAI API to detect and strip injections) and PromptLocate (segment-and-detect approach using contextual inconsistency), discussed qualitatively as the closest prior work though PromptLocate is not directly benchmarked.</t>
+          <t>Comparison across 20 LLM agent settings (base vs. reasoning-enabled Qwen3 variants at 4 sizes; across model families GPT, DeepSeek, Llama, o1, Gemini, Claude, Phi, Gemma, Mistral); Base Setting vs. two Enhanced Settings (hijacking prompts prepended to the poisoned tool description) as an ablation; MCPTox purpose-built payloads vs. adapted InjecAgent (IPI-benchmark) payloads as a direct comparative baseline for attack-vector effectiveness</t>
         </is>
       </c>
       <c r="F169" s="5" t="n"/>
@@ -8306,7 +8294,7 @@
       <c r="H169" s="5" t="n"/>
       <c r="I169" s="5" t="inlineStr">
         <is>
-          <t>7222e1b74675ebfd85d5f261ef8ab5010111e737</t>
+          <t>34df7d82136868e5d492968647efd17d442a6720</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8304,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Defending Against Prompt Injection with DataFilter</t>
+          <t>MCPTox: A Benchmark for Tool Poisoning on Real-World MCP Servers</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -8331,7 +8319,7 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>Formal adversarial threat model (Section II): the paper considers indirect prompt injection against an LLM-integrated application/agent where the prompt (system + user instruction) is trusted and the data (retrieved documents, tool outputs, website HTML, etc.) is untrusted and attacker-controlled. The attacker has full knowledge of the benign instruction and prompt template but cannot modify them directly; they inject a malicious instruction into the untrusted data with the goal of having the LLM follow the injected instruction instead of (or alongside) the legitimate task. An attack succeeds if the LLM treats the injection as an instruction to execute rather than as inert data. The defender's goal is to ensure the system always responds to the benign instruction and never follows instructions embedded in data, while preserving utility when no attack is present. The paper explicitly scopes out optimization-based attacks (e.g., GCG variants) from its main threat model as harder to mount against closed-source models, but separately evaluates against the strongest known optimization-based adaptive attack as a worst-case robustness check, and evaluates human-designed adaptive attacks that directly target the filter model itself (e.g., prompts instructing DataFilter to treat the injection as clean data).</t>
+          <t>Tool Poisoning Attack (TPA): an attacker registers a malicious MCP server whose tool metadata (name and natural-language description) embeds malicious instructions during the MCP registration/tool-discovery phase - before any tool is ever executed - distinguishing it from Indirect Prompt Injection (IPI), where malicious content is embedded in a tool's execution output post-execution. Three attack paradigms are studied: Explicit Trigger-Function Hijacking (a poisoned tool mimics a common benign function by name, e.g. get_time, and when the user's benign query would invoke it, instructs the agent to instead call a separate high-privilege legitimate tool, e.g. read_file, to exfiltrate sensitive data like an SSH key); Implicit Trigger-Function Hijacking (a poisoned tool disguised as a background/system process, e.g. security_check, embeds a rule-like instruction triggered implicitly whenever the user performs a related action, manipulating the agent into calling a different legitimate tool without ever invoking the poisoned tool by name); and Implicit Trigger-Parameter Tampering (a poisoned tool's description introduces a global rule that silently alters the parameters used when the agent invokes a genuinely intended, legitimate tool, e.g. redirecting an email's recipient address). Crucially, in all three paradigms the final malicious action is always carried out by a legitimate, already-trusted tool on the server, and the poisoned tool itself is never executed - maximizing stealth and bypassing permission models that would restrict a new, untrusted tool from high-privilege operations.</t>
         </is>
       </c>
       <c r="F170" s="5" t="n"/>
@@ -8339,7 +8327,7 @@
       <c r="H170" s="5" t="n"/>
       <c r="I170" s="5" t="inlineStr">
         <is>
-          <t>7222e1b74675ebfd85d5f261ef8ab5010111e737</t>
+          <t>34df7d82136868e5d492968647efd17d442a6720</t>
         </is>
       </c>
     </row>
@@ -8349,7 +8337,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>Defending Against Prompt Injection with DataFilter</t>
+          <t>MCPTox: A Benchmark for Tool Poisoning on Real-World MCP Servers</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -8364,7 +8352,7 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>The paper has an explicit 'Limitations' paragraph within the Conclusion and Discussions section (Section VI) listing three limitations: (1) DataFilter introduces additional inference overhead since the filter must run on every piece of new untrusted data received; (2) the defense cannot withstand the strongest optimization-based adaptive attacks -- a recent attack that breaks all existing defenses also partially breaks DataFilter (83% ASR, the best among tested defenses but still far from zero); (3) although deployment is lightweight, some integration effort is still required from agent developers, since DataFilter struggles with very long benign user prompts and performs poorly if given an entire user message containing tool introductions, example calls, and policies (as in InjecAgent) rather than just the concise user query -- developers must extract the short user instruction before passing it to the filter, an extra integration step not required by defenses fully embedded in the backend model.</t>
+          <t>The current evaluation is limited to single-turn interaction - it does not model long-term, multi-turn conversational scenarios where an agent's memory could be poisoned over time or where a 'sleeper' instruction waits dormant for a specific future trigger, and the authors state future benchmarks should explore these more complex, stateful attack scenarios; the attack payloads (test cases) in MCPTox are generated via a semi-automated process guided by human-defined attack paradigms, a common characteristic of current prompt-injection benchmarks whose attacks are often generic and based on human experience rather than being adaptively optimized against a specific target defense, and the authors identify developing automated, adaptive attack generation for Tool Poisoning as a significant direction for future work.</t>
         </is>
       </c>
       <c r="F171" s="5" t="n"/>
@@ -8372,7 +8360,7 @@
       <c r="H171" s="5" t="n"/>
       <c r="I171" s="5" t="inlineStr">
         <is>
-          <t>7222e1b74675ebfd85d5f261ef8ab5010111e737</t>
+          <t>34df7d82136868e5d492968647efd17d442a6720</t>
         </is>
       </c>
     </row>
@@ -8382,7 +8370,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Defending Against Prompt Injection with DataFilter</t>
+          <t>MCPTox: A Benchmark for Tool Poisoning on Real-World MCP Servers</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -8397,7 +8385,7 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>DataFilter is a test-time, model-agnostic defense against prompt injection that sits between untrusted data sources and the backend LLM, stripping injected instructions from untrusted data while preserving benign content, so the backend LLM only ever processes sanitized input. It is motivated by the failure of prior defense categories to satisfy three simultaneously desirable properties (security, utility-preservation, and model-agnosticism, formalized in Table I): fine-tuning-based model-level defenses are secure and utility-preserving but require access to model weights (impractical for proprietary commercial LLMs, which no major provider currently offers hardened); prompting-based defenses are model-agnostic and utility-preserving but offer weak security (ASR often above 40%); detection-based defenses are model-agnostic and reasonably secure but suffer heavy utility loss from over-refusing benign inputs; and system-level defenses are secure and model-agnostic but require non-trivial redesign of the agent pipeline and only apply to a limited set of tasks. DataFilter is implemented by supervised fine-tuning Llama-3.1-8B-Instruct as a sequence-to-sequence filter that takes a formatted (trusted prompt u, untrusted data x) pair and outputs a cleaned version xclean, minimizing negative log-likelihood of the ground-truth clean output. Critically, the filter is given the user's trusted prompt as context, which lets it distinguish malicious imperative sentences from benign task-relevant imperative sentences (e.g., a 'TODOs for the week' email) that a naive blanket-removal filter would incorrectly strip -- an ablation confirms that omitting the prompt context yields perfect security but destroys utility by deleting all imperative content indiscriminately. Training data is constructed entirely from the public Alpaca instruction-tuning dataset (19K samples with non-empty data fields) by synthetically splicing another sample's prompt+data as a simulated injection into each data field, making the entire training pipeline model-agnostic and independent of the backend LLM or any adversarial-example-specific dataset; the model also learns to avoid hallucination/repetition failure modes through additional curated training goals. A special &lt;|end_of_instruction|&gt; token is added to Llama's tokenizer to help the filter recognize the prompt/data boundary. Evaluated as a plug-and-play defense across AgentDojo, InjecAgent, and SEP (with gpt-4o and Llama-3.1-8B-Instruct backends), DataFilter reduces attack success rates from over 40% to roughly 2% on average while incurring only about 1% average utility loss, generalizing to attack styles, benchmarks, and multi-turn agentic tool-calling scenarios not seen during its single-turn Alpaca-based training, and remains the strongest defense (though not unbreakable) against human-designed and optimization-based adaptive attacks specifically targeting the filter itself.</t>
+          <t>Introduces MCPTox, the first benchmark to systematically and empirically evaluate LLM agent vulnerability to Tool Poisoning Attacks (TPA) against real-world Model Context Protocol (MCP) servers, addressing a fundamentally different and previously under-quantified attack vector from Indirect Prompt Injection (IPI): rather than malicious content arriving via a tool's execution output (post-execution), TPA embeds malicious instructions directly within a tool's metadata/description during the MCP registration phase (pre-execution), exploiting the agent's unconditional trust in tool descriptions as ground truth during its planning stage. Built on 45 real-world MCP servers and 353 authentic tools across 8 application domains, MCPTox uses SOTA-LLM-assisted, manually-refined few-shot generation to construct 1,312 malicious test cases spanning three attack paradigms - Explicit Trigger-Function Hijacking, Implicit Trigger-Function Hijacking, and Implicit Trigger-Parameter Tampering - all designed so the final malicious action is executed exclusively via a legitimate tool already available on the server (the poisoned tool itself is never called), maximizing stealth and bypassing tool-permission safeguards. Evaluating 20 LLM agent settings across 9 major model families, the paper finds widespread, significant vulnerability (average ASR 36.5%, peak 72.8% for o1-mini), an inverse-scaling relationship where more capable/reasoning-enabled models are more susceptible due to superior instruction-following, that parameter-tampering attacks are the most effective paradigm, that classic hijacking-prompt reinforcement provides only marginal additional gain, that existing content-based safety alignment is essentially ineffective against TPA (refusal rates under 3% even for the most cautious model), and via a controlled comparison that malicious payloads repurposed from an existing IPI benchmark (InjecAgent) are far less effective when embedded in tool descriptions than MCPTox's purpose-built attacks, validating that Tool Poisoning constitutes a genuinely distinct threat requiring its own dedicated benchmark and defenses.</t>
         </is>
       </c>
       <c r="F172" s="5" t="n"/>
@@ -8405,7 +8393,7 @@
       <c r="H172" s="5" t="n"/>
       <c r="I172" s="5" t="inlineStr">
         <is>
-          <t>7222e1b74675ebfd85d5f261ef8ab5010111e737</t>
+          <t>34df7d82136868e5d492968647efd17d442a6720</t>
         </is>
       </c>
     </row>
@@ -8415,7 +8403,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>HAGE: Harnessing Agentic Memory via RL-Driven Weighted Graph Evolution</t>
+          <t>Corpus Poisoning via Approximate Greedy Gradient Descent</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -8438,7 +8426,7 @@
       <c r="H173" s="5" t="n"/>
       <c r="I173" s="5" t="inlineStr">
         <is>
-          <t>95bb7a742af788471295bb3bd6f12d4f6886dfa1</t>
+          <t>19afd7b97061fdf0dd4a4726bef4ed8acd31a0a8</t>
         </is>
       </c>
     </row>
@@ -8448,7 +8436,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>HAGE: Harnessing Agentic Memory via RL-Driven Weighted Graph Evolution</t>
+          <t>Corpus Poisoning via Approximate Greedy Gradient Descent</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -8463,7 +8451,7 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>ML/AI</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="F174" s="5" t="n"/>
@@ -8471,7 +8459,7 @@
       <c r="H174" s="5" t="n"/>
       <c r="I174" s="5" t="inlineStr">
         <is>
-          <t>95bb7a742af788471295bb3bd6f12d4f6886dfa1</t>
+          <t>19afd7b97061fdf0dd4a4726bef4ed8acd31a0a8</t>
         </is>
       </c>
     </row>
@@ -8481,7 +8469,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>HAGE: Harnessing Agentic Memory via RL-Driven Weighted Graph Evolution</t>
+          <t>Corpus Poisoning via Approximate Greedy Gradient Descent</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
@@ -8504,7 +8492,7 @@
       <c r="H175" s="5" t="n"/>
       <c r="I175" s="5" t="inlineStr">
         <is>
-          <t>95bb7a742af788471295bb3bd6f12d4f6886dfa1</t>
+          <t>19afd7b97061fdf0dd4a4726bef4ed8acd31a0a8</t>
         </is>
       </c>
     </row>
@@ -8514,7 +8502,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>HAGE: Harnessing Agentic Memory via RL-Driven Weighted Graph Evolution</t>
+          <t>Corpus Poisoning via Approximate Greedy Gradient Descent</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
@@ -8529,7 +8517,7 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>defense</t>
+          <t>attack</t>
         </is>
       </c>
       <c r="F176" s="5" t="n"/>
@@ -8537,7 +8525,7 @@
       <c r="H176" s="5" t="n"/>
       <c r="I176" s="5" t="inlineStr">
         <is>
-          <t>95bb7a742af788471295bb3bd6f12d4f6886dfa1</t>
+          <t>19afd7b97061fdf0dd4a4726bef4ed8acd31a0a8</t>
         </is>
       </c>
     </row>
@@ -8547,7 +8535,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>HAGE: Harnessing Agentic Memory via RL-Driven Weighted Graph Evolution</t>
+          <t>Corpus Poisoning via Approximate Greedy Gradient Descent</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
@@ -8562,7 +8550,7 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>memory</t>
+          <t>RAG</t>
         </is>
       </c>
       <c r="F177" s="5" t="n"/>
@@ -8570,7 +8558,7 @@
       <c r="H177" s="5" t="n"/>
       <c r="I177" s="5" t="inlineStr">
         <is>
-          <t>95bb7a742af788471295bb3bd6f12d4f6886dfa1</t>
+          <t>19afd7b97061fdf0dd4a4726bef4ed8acd31a0a8</t>
         </is>
       </c>
     </row>
@@ -8580,7 +8568,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>HAGE: Harnessing Agentic Memory via RL-Driven Weighted Graph Evolution</t>
+          <t>Corpus Poisoning via Approximate Greedy Gradient Descent</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
@@ -8595,7 +8583,7 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>silent-corruption</t>
         </is>
       </c>
       <c r="F178" s="5" t="n"/>
@@ -8603,7 +8591,7 @@
       <c r="H178" s="5" t="n"/>
       <c r="I178" s="5" t="inlineStr">
         <is>
-          <t>95bb7a742af788471295bb3bd6f12d4f6886dfa1</t>
+          <t>19afd7b97061fdf0dd4a4726bef4ed8acd31a0a8</t>
         </is>
       </c>
     </row>
@@ -8613,7 +8601,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>HAGE: Harnessing Agentic Memory via RL-Driven Weighted Graph Evolution</t>
+          <t>Corpus Poisoning via Approximate Greedy Gradient Descent</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
@@ -8628,7 +8616,7 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F179" s="5" t="n"/>
@@ -8636,7 +8624,7 @@
       <c r="H179" s="5" t="n"/>
       <c r="I179" s="5" t="inlineStr">
         <is>
-          <t>95bb7a742af788471295bb3bd6f12d4f6886dfa1</t>
+          <t>19afd7b97061fdf0dd4a4726bef4ed8acd31a0a8</t>
         </is>
       </c>
     </row>
@@ -8646,7 +8634,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>HAGE: Harnessing Agentic Memory via RL-Driven Weighted Graph Evolution</t>
+          <t>Corpus Poisoning via Approximate Greedy Gradient Descent</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
@@ -8661,7 +8649,7 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F180" s="5" t="n"/>
@@ -8669,7 +8657,7 @@
       <c r="H180" s="5" t="n"/>
       <c r="I180" s="5" t="inlineStr">
         <is>
-          <t>95bb7a742af788471295bb3bd6f12d4f6886dfa1</t>
+          <t>19afd7b97061fdf0dd4a4726bef4ed8acd31a0a8</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8667,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>HAGE: Harnessing Agentic Memory via RL-Driven Weighted Graph Evolution</t>
+          <t>Corpus Poisoning via Approximate Greedy Gradient Descent</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
@@ -8694,7 +8682,7 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>reasoning</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F181" s="5" t="n"/>
@@ -8702,7 +8690,7 @@
       <c r="H181" s="5" t="n"/>
       <c r="I181" s="5" t="inlineStr">
         <is>
-          <t>95bb7a742af788471295bb3bd6f12d4f6886dfa1</t>
+          <t>19afd7b97061fdf0dd4a4726bef4ed8acd31a0a8</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8700,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>HAGE: Harnessing Agentic Memory via RL-Driven Weighted Graph Evolution</t>
+          <t>Corpus Poisoning via Approximate Greedy Gradient Descent</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
@@ -8727,7 +8715,7 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>session-persistent</t>
+          <t>cross-session-dormant</t>
         </is>
       </c>
       <c r="F182" s="5" t="n"/>
@@ -8735,7 +8723,7 @@
       <c r="H182" s="5" t="n"/>
       <c r="I182" s="5" t="inlineStr">
         <is>
-          <t>95bb7a742af788471295bb3bd6f12d4f6886dfa1</t>
+          <t>19afd7b97061fdf0dd4a4726bef4ed8acd31a0a8</t>
         </is>
       </c>
     </row>
@@ -8745,7 +8733,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>HAGE: Harnessing Agentic Memory via RL-Driven Weighted Graph Evolution</t>
+          <t>Corpus Poisoning via Approximate Greedy Gradient Descent</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
@@ -8760,7 +8748,7 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F183" s="5" t="n"/>
@@ -8768,7 +8756,7 @@
       <c r="H183" s="5" t="n"/>
       <c r="I183" s="5" t="inlineStr">
         <is>
-          <t>95bb7a742af788471295bb3bd6f12d4f6886dfa1</t>
+          <t>19afd7b97061fdf0dd4a4726bef4ed8acd31a0a8</t>
         </is>
       </c>
     </row>
@@ -8778,7 +8766,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>HAGE: Harnessing Agentic Memory via RL-Driven Weighted Graph Evolution</t>
+          <t>Corpus Poisoning via Approximate Greedy Gradient Descent</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
@@ -8793,7 +8781,7 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>Code is released: 'Our code is available at https://github.com/FredJiang0324/HAGE_MVPReview.' The paper explicitly notes no new datasets are introduced (all datasets and models used are publicly available: LoCoMo, HotpotQA, all-MiniLM-L6-v2 under Apache 2.0, GPT-4o-mini via the OpenAI API, Qwen2.5-3B under the Qwen Research License).</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F184" s="5" t="n"/>
@@ -8801,7 +8789,7 @@
       <c r="H184" s="5" t="n"/>
       <c r="I184" s="5" t="inlineStr">
         <is>
-          <t>95bb7a742af788471295bb3bd6f12d4f6886dfa1</t>
+          <t>19afd7b97061fdf0dd4a4726bef4ed8acd31a0a8</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8799,7 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>HAGE: Harnessing Agentic Memory via RL-Driven Weighted Graph Evolution</t>
+          <t>Corpus Poisoning via Approximate Greedy Gradient Descent</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
@@ -8826,7 +8814,7 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>GPT-4o-mini and Qwen2.5-3B are used as backbone LLMs for both HAGE and all baselines. all-MiniLM-L6-v2 is used to initialize node embeddings. HAGE is compared against a Full Context baseline and five state-of-the-art agentic memory architectures: A-MEM (a self-evolving agent memory system), Nemori (graph-based memory with predict-calibrate episodic segmentation), MemoryOS (a hierarchical semantic memory operating system), MAGMA (multi-relational memory with static edge weights and heuristic traversal), and MemSkill (an RL-based skill-evolving memory method).</t>
+          <t>Retrievers: Contriever, Contriever-MS, ANCE, DPR-mul, DPR-nq; downstream generator LLMs for the PoisonedRAG extension experiment: LLaMA-2-7B, LLaMA-2-13B, Vicuna-7B, Vicuna-13B, Vicuna-33B, GPT-3.5, GPT-4</t>
         </is>
       </c>
       <c r="F185" s="5" t="n"/>
@@ -8834,7 +8822,7 @@
       <c r="H185" s="5" t="n"/>
       <c r="I185" s="5" t="inlineStr">
         <is>
-          <t>95bb7a742af788471295bb3bd6f12d4f6886dfa1</t>
+          <t>19afd7b97061fdf0dd4a4726bef4ed8acd31a0a8</t>
         </is>
       </c>
     </row>
@@ -8844,7 +8832,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>HAGE: Harnessing Agentic Memory via RL-Driven Weighted Graph Evolution</t>
+          <t>Corpus Poisoning via Approximate Greedy Gradient Descent</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
@@ -8859,7 +8847,7 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>Two publicly available benchmarks: LoCoMo (Maharana et al., 2024), containing ultra-long conversations averaging 9K tokens designed to assess long-range temporal and causal retrieval, evaluated across Multi-Hop, Temporal, Open-Domain, Single-Hop, and Adversarial query categories via LLM-as-a-Judge scoring (with 5-fold cross-validation at the conversation-sample level to prevent query-level leakage); and HotpotQA (Yang et al., 2018) under the distractor setting, a non-conversational multi-hop QA benchmark used to test generalization beyond conversational memory, evaluated with token-level F1 and LLM-as-a-Judge score.</t>
+          <t>Natural Questions (NQ) and MS MARCO (primary in-domain attack datasets); 5 out-of-domain BEIR-style datasets for transferability evaluation: NFCorpus, Quora, SCIDOCS, SciFact, FiQA-2018</t>
         </is>
       </c>
       <c r="F186" s="5" t="n"/>
@@ -8867,7 +8855,7 @@
       <c r="H186" s="5" t="n"/>
       <c r="I186" s="5" t="inlineStr">
         <is>
-          <t>95bb7a742af788471295bb3bd6f12d4f6886dfa1</t>
+          <t>19afd7b97061fdf0dd4a4726bef4ed8acd31a0a8</t>
         </is>
       </c>
     </row>
@@ -8877,7 +8865,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>HAGE: Harnessing Agentic Memory via RL-Driven Weighted Graph Evolution</t>
+          <t>Corpus Poisoning via Approximate Greedy Gradient Descent</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
@@ -8892,7 +8880,7 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>On LoCoMo, HAGE achieves the best overall LLM-as-a-Judge score under both backbones: with GPT-4o-mini it improves the overall score from the strongest baseline's 0.700 to 0.739, and with Qwen2.5-3B from 0.499 to 0.548, with especially large gains on Adversarial queries (0.839 vs. 0.742 for the next-best baseline, MAGMA, under GPT-4o-mini). On HotpotQA (distractor setting), HAGE again achieves the best overall performance, reaching F1 0.678 / LLM score 0.824 with GPT-4o-mini, outperforming all baselines including MAGMA (F1 0.640) and MemSkill (F1 0.579), and the same pattern holds under Qwen2.5-3B (F1 0.429 vs. next-best 0.350 for MemoryOS). An ablation (Table 4) shows each HAGE component contributes: static edges alone score 0.698 Judge/0.462 F1, LLM-scored edges improve to 0.712/0.500, trainable edges further to 0.724/0.514, and the full HAGE system (trainable edges + trainable router) reaches 0.739/0.548. An accuracy-efficiency analysis (Table 3) shows HAGE achieves the highest average score among all methods while using only moderately more inference cost (3.82K tokens/query, 2.17s average latency) than the most efficient competing baseline.</t>
+          <t>AGGD substantially outperforms HotFlip and random-perturbation baselines when injecting just a single adversarial passage: on the pretrained Contriever model, AGGD achieves 92.5% in-domain top-20 attack success rate (ASR) on NQ (vs. 91.08% HotFlip, 80.24% random) and 85.47% on MS MARCO; the largest gains are against the ANCE retriever, where AGGD improves ASR by 15.24 points on NQ and 17.44 points on MS MARCO over HotFlip (the second-best baseline). AGGD's selected candidate token sets are shown to have both higher overall quality (higher mean validation success rate across 400 sampled passages) and higher probability of containing the truly best candidate (more than 85% of the time, vs. under 13% for HotFlip). Generated adversarial passages transfer well to 5 out-of-domain retrieval tasks/corpora despite being trained only on NQ/MS MARCO queries (e.g. 86.54% ASR on FiQA-2018, 86.92% on Quora with a single injected passage), with MS-MARCO-trained passages generally transferring better than NQ-trained ones. AGGD also serves as a drop-in replacement for HotFlip in other adversarial-attack pipelines: substituting it into PoisonedRAG's white-box knowledge-poisoning attack achieves comparable or better attack success rate than the original HotFlip-based method across 7 downstream LLMs (LLaMA-2, Vicuna variants, GPT-3.5, GPT-4) on both NQ and MS MARCO.</t>
         </is>
       </c>
       <c r="F187" s="5" t="n"/>
@@ -8900,7 +8888,7 @@
       <c r="H187" s="5" t="n"/>
       <c r="I187" s="5" t="inlineStr">
         <is>
-          <t>95bb7a742af788471295bb3bd6f12d4f6886dfa1</t>
+          <t>19afd7b97061fdf0dd4a4726bef4ed8acd31a0a8</t>
         </is>
       </c>
     </row>
@@ -8910,7 +8898,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>HAGE: Harnessing Agentic Memory via RL-Driven Weighted Graph Evolution</t>
+          <t>Corpus Poisoning via Approximate Greedy Gradient Descent</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
@@ -8925,7 +8913,7 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>Full Context (feeding the entire conversation history into the LLM as a brute-force reference for native long-context capability) and five state-of-the-art memory architectures evaluated under the same backbone LLMs: A-MEM, Nemori, MemoryOS, MAGMA (the closest architectural relative, using static/unweighted multi-relational edges and heuristic traversal versus HAGE's learned weighted traversal), and MemSkill.</t>
+          <t>HotFlip (Ebrahimi et al. 2018, the standard prior gradient-based greedy search method for corpus poisoning, per Zhong et al. 2023); Random token perturbation (naive baseline); PoisonedRAG's original HotFlip-based white-box attack used as the baseline when substituting in AGGD as a plug-in replacement</t>
         </is>
       </c>
       <c r="F188" s="5" t="n"/>
@@ -8933,7 +8921,7 @@
       <c r="H188" s="5" t="n"/>
       <c r="I188" s="5" t="inlineStr">
         <is>
-          <t>95bb7a742af788471295bb3bd6f12d4f6886dfa1</t>
+          <t>19afd7b97061fdf0dd4a4726bef4ed8acd31a0a8</t>
         </is>
       </c>
     </row>
@@ -8943,7 +8931,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>HAGE: Harnessing Agentic Memory via RL-Driven Weighted Graph Evolution</t>
+          <t>Corpus Poisoning via Approximate Greedy Gradient Descent</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
@@ -8958,7 +8946,7 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>N/A - non-adversarial. This is a memory-retrieval-architecture paper, not a security paper; the incidental failure mode of interest is degraded retrieval accuracy from treating memory-graph edges as unweighted or fixed rather than query-dependent -- as memory grows, fixed graph-expansion rules and static similarity search fail to discriminate between highly relevant relational pathways and distracting noise, causing agents to fail to prioritize structurally important but semantically distant 'bridge' information relevant to a given query.</t>
+          <t>A malicious user with no need for special system privileges injects a small number of adversarial passages (as few as one) into an openly-editable retrieval corpus (e.g. Wikipedia, Reddit, or other openly-accessible platforms) that a dense retrieval system indexes, crafting these passages via gradient-based discrete token optimization to maximize expected similarity to a broad, unseen distribution of user queries (rather than a single targeted query), so that the adversarial passage is returned among the top-k results for many different queries; potential motivations include black-hat search-engine optimization, promoting advertisements, or disseminating disinformation/hate speech, and the technique is also shown to extend directly to other discrete-optimization-based attacks such as RAG knowledge-poisoning (PoisonedRAG) and adversarial prompt generation.</t>
         </is>
       </c>
       <c r="F189" s="5" t="n"/>
@@ -8966,7 +8954,7 @@
       <c r="H189" s="5" t="n"/>
       <c r="I189" s="5" t="inlineStr">
         <is>
-          <t>95bb7a742af788471295bb3bd6f12d4f6886dfa1</t>
+          <t>19afd7b97061fdf0dd4a4726bef4ed8acd31a0a8</t>
         </is>
       </c>
     </row>
@@ -8976,7 +8964,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>HAGE: Harnessing Agentic Memory via RL-Driven Weighted Graph Evolution</t>
+          <t>Corpus Poisoning via Approximate Greedy Gradient Descent</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
@@ -8991,7 +8979,7 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>The paper contains an explicit 'Limitations' section (placed after the Conclusion) with two named points, quoted/paraphrased directly: (1) 'Benchmark coverage' -- evaluation covers only two benchmarks, LoCoMo (long-term conversational memory) and HotpotQA (non-conversational multi-hop QA), and while these represent complementary retrieval settings, results may not fully generalize to other memory-intensive tasks such as procedural or document-grounded reasoning; (2) 'Dependence on LLM components' -- both query analysis (relation intent extraction) and evaluation (LLM-as-a-Judge) rely on instruction-tuned LLMs, introducing cost and model-specific variability, since the accuracy of the relation intent classifier directly affects the quality of query-conditioned edge features used during traversal. A separate 'Ethical Considerations' section additionally flags privacy concerns from persistent memory accumulating sensitive personal information beyond its intended scope, potential misuse without user consent/safeguards, and the risk that RL-optimized retrieval policies may learn to surface information in ways reflecting training-data biases.</t>
+          <t>The proposed AGGD attack framework, although shown to be versatile and applicable to a wide range of adversarial scenarios formulated as discrete optimization problems, produces adversarial passages that often lack semantic coherence, making the resulting adversarial corpus text easily detectable and filterable (e.g. via perplexity-based or grammaticality-based defenses) - the authors explicitly identify reformulating the problem as a constrained optimization that also enforces semantic meaningfulness (even at some cost to raw attack success rate) as a promising direction for future work, since this would produce adversarial text that is more difficult to defend against.</t>
         </is>
       </c>
       <c r="F190" s="5" t="n"/>
@@ -8999,7 +8987,7 @@
       <c r="H190" s="5" t="n"/>
       <c r="I190" s="5" t="inlineStr">
         <is>
-          <t>95bb7a742af788471295bb3bd6f12d4f6886dfa1</t>
+          <t>19afd7b97061fdf0dd4a4726bef4ed8acd31a0a8</t>
         </is>
       </c>
     </row>
@@ -9009,7 +8997,7 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>HAGE: Harnessing Agentic Memory via RL-Driven Weighted Graph Evolution</t>
+          <t>Corpus Poisoning via Approximate Greedy Gradient Descent</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
@@ -9024,7 +9012,7 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>HAGE (Harnessing Agentic memory via RL-driven weighted Graph Evolution) reconceptualizes agentic memory retrieval as sequential, query-conditioned traversal over a unified weighted multi-relational memory graph, addressing the limitation that existing graph-based memory systems treat edges as unweighted or only weakly weighted (an edge mainly indicates connection existence rather than query-dependent utility), causing them to fail to discriminate between highly relevant relational pathways and noise as memory scales. Memory is organized as relation-specific graph views over shared memory nodes, where each edge carries a trainable relation feature vector encoding multiple relational signals (e.g., temporal, causal, entity-centric). Given an incoming query, an LLM-based classifier identifies the relational intent, and a QueryRouter network dynamically modulates the corresponding dimensions of each edge's embedding; traversal scores are then computed via a learned combination of semantic similarity and these query-conditioned edge representations, letting the system prioritize high-utility relational paths while softly suppressing weakly relevant connections -- enabling query-dependent routing that can efficiently traverse structurally critical but semantically distant 'bridge' nodes. Beyond adaptive traversal, HAGE introduces a reinforcement-learning training framework (formulated as an MDP with policy-gradient optimization, an exponential-moving-average baseline, and an anchor regularization term keeping edge features close to a semantically meaningful initialization) that jointly optimizes routing behavior (QueryRouter weights, higher learning rate) and edge representations (edge features, lower learning rate) using downstream task feedback, creating a co-evolutionary training dynamic between the two parameter groups. The system is implemented in PyTorch with GPU-accelerated graph routing, using all-MiniLM-L6-v2 for initial node embeddings, COO-format edge indices, and typed edge labels, and is trained/evaluated with 5-fold sample-level cross-validation to prevent query leakage. This architecture shifts agentic memory retrieval from fixed heuristic graph-expansion rules toward a learned, relation-aware, query-conditioned traversal policy that jointly adapts memory representations and retrieval behavior.</t>
+          <t>Investigates and identifies specific limitations of HotFlip, the widely-used gradient-based discrete-token search method underlying corpus poisoning attacks on dense retrieval systems: because HotFlip's search proceeds by randomly sampling a single token position per iteration and gathering gradient-based candidates only for that position, it is inefficient, prone to getting stuck in repeated unproductive loops, and its Taylor-approximation-based candidate ranking is empirically shown to correctly identify the truly best token replacement only 9% of the time (with the best candidate falling in the top-10 ranked candidates just 58% of the time). To address these issues, the paper proposes Approximate Greedy Gradient Descent (AGGD), a deterministic best-first search that computes gradient-based candidate token replacements across all token positions in the adversarial passage simultaneously (rather than one randomly sampled position), builds a combined candidate set from the top-ranked tokens at each position, and greedily updates the passage to whichever candidate in this larger, structured set most reduces the loss, escalating to lower-ranked candidate tiers only when no improvement is found - yielding both a higher-quality candidate set and a more systematic, non-repetitive search trajectory. Evaluated on the corpus-poisoning task across 5 dense retrievers and 2 primary QA datasets (NQ, MS MARCO), AGGD achieves substantially higher attack success rates than HotFlip and random-perturbation baselines when injecting a single adversarial passage, is especially effective against the ANCE retriever, generalizes well to 5 out-of-domain retrieval tasks despite being optimized only on in-domain training queries, and is shown to function as a general-purpose, drop-in replacement for HotFlip in other discrete-optimization-based adversarial attacks, including improving PoisonedRAG's white-box RAG knowledge-poisoning attack across multiple downstream LLMs.</t>
         </is>
       </c>
       <c r="F191" s="5" t="n"/>
@@ -9032,7 +9020,7 @@
       <c r="H191" s="5" t="n"/>
       <c r="I191" s="5" t="inlineStr">
         <is>
-          <t>95bb7a742af788471295bb3bd6f12d4f6886dfa1</t>
+          <t>19afd7b97061fdf0dd4a4726bef4ed8acd31a0a8</t>
         </is>
       </c>
     </row>
@@ -9042,7 +9030,7 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>LUMINA: Long-horizon Understanding for Multi-turn Interactive Agents</t>
+          <t>The Task Shield: Enforcing Task Alignment to Defend Against Indirect Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
@@ -9065,7 +9053,7 @@
       <c r="H192" s="5" t="n"/>
       <c r="I192" s="5" t="inlineStr">
         <is>
-          <t>023292350ef95533d99264dab96ffbd271b24b45</t>
+          <t>8af6009a8d55d456213f6819567eb3ace39dd176</t>
         </is>
       </c>
     </row>
@@ -9075,7 +9063,7 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>LUMINA: Long-horizon Understanding for Multi-turn Interactive Agents</t>
+          <t>The Task Shield: Enforcing Task Alignment to Defend Against Indirect Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
@@ -9090,7 +9078,7 @@
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>ML/AI</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="F193" s="5" t="n"/>
@@ -9098,7 +9086,7 @@
       <c r="H193" s="5" t="n"/>
       <c r="I193" s="5" t="inlineStr">
         <is>
-          <t>023292350ef95533d99264dab96ffbd271b24b45</t>
+          <t>8af6009a8d55d456213f6819567eb3ace39dd176</t>
         </is>
       </c>
     </row>
@@ -9108,7 +9096,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>LUMINA: Long-horizon Understanding for Multi-turn Interactive Agents</t>
+          <t>The Task Shield: Enforcing Task Alignment to Defend Against Indirect Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
@@ -9131,7 +9119,7 @@
       <c r="H194" s="5" t="n"/>
       <c r="I194" s="5" t="inlineStr">
         <is>
-          <t>023292350ef95533d99264dab96ffbd271b24b45</t>
+          <t>8af6009a8d55d456213f6819567eb3ace39dd176</t>
         </is>
       </c>
     </row>
@@ -9141,7 +9129,7 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>LUMINA: Long-horizon Understanding for Multi-turn Interactive Agents</t>
+          <t>The Task Shield: Enforcing Task Alignment to Defend Against Indirect Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
@@ -9156,7 +9144,7 @@
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>neither</t>
+          <t>defense</t>
         </is>
       </c>
       <c r="F195" s="5" t="n"/>
@@ -9164,7 +9152,7 @@
       <c r="H195" s="5" t="n"/>
       <c r="I195" s="5" t="inlineStr">
         <is>
-          <t>023292350ef95533d99264dab96ffbd271b24b45</t>
+          <t>8af6009a8d55d456213f6819567eb3ace39dd176</t>
         </is>
       </c>
     </row>
@@ -9174,7 +9162,7 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>LUMINA: Long-horizon Understanding for Multi-turn Interactive Agents</t>
+          <t>The Task Shield: Enforcing Task Alignment to Defend Against Indirect Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
@@ -9189,7 +9177,7 @@
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>tool-output</t>
         </is>
       </c>
       <c r="F196" s="5" t="n"/>
@@ -9197,7 +9185,7 @@
       <c r="H196" s="5" t="n"/>
       <c r="I196" s="5" t="inlineStr">
         <is>
-          <t>023292350ef95533d99264dab96ffbd271b24b45</t>
+          <t>8af6009a8d55d456213f6819567eb3ace39dd176</t>
         </is>
       </c>
     </row>
@@ -9207,7 +9195,7 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>LUMINA: Long-horizon Understanding for Multi-turn Interactive Agents</t>
+          <t>The Task Shield: Enforcing Task Alignment to Defend Against Indirect Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
@@ -9222,7 +9210,7 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>goal-hijack</t>
         </is>
       </c>
       <c r="F197" s="5" t="n"/>
@@ -9230,7 +9218,7 @@
       <c r="H197" s="5" t="n"/>
       <c r="I197" s="5" t="inlineStr">
         <is>
-          <t>023292350ef95533d99264dab96ffbd271b24b45</t>
+          <t>8af6009a8d55d456213f6819567eb3ace39dd176</t>
         </is>
       </c>
     </row>
@@ -9240,7 +9228,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>LUMINA: Long-horizon Understanding for Multi-turn Interactive Agents</t>
+          <t>The Task Shield: Enforcing Task Alignment to Defend Against Indirect Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
@@ -9255,7 +9243,7 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F198" s="5" t="n"/>
@@ -9263,7 +9251,7 @@
       <c r="H198" s="5" t="n"/>
       <c r="I198" s="5" t="inlineStr">
         <is>
-          <t>023292350ef95533d99264dab96ffbd271b24b45</t>
+          <t>8af6009a8d55d456213f6819567eb3ace39dd176</t>
         </is>
       </c>
     </row>
@@ -9273,7 +9261,7 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>LUMINA: Long-horizon Understanding for Multi-turn Interactive Agents</t>
+          <t>The Task Shield: Enforcing Task Alignment to Defend Against Indirect Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
@@ -9288,7 +9276,7 @@
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F199" s="5" t="n"/>
@@ -9296,7 +9284,7 @@
       <c r="H199" s="5" t="n"/>
       <c r="I199" s="5" t="inlineStr">
         <is>
-          <t>023292350ef95533d99264dab96ffbd271b24b45</t>
+          <t>8af6009a8d55d456213f6819567eb3ace39dd176</t>
         </is>
       </c>
     </row>
@@ -9306,7 +9294,7 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>LUMINA: Long-horizon Understanding for Multi-turn Interactive Agents</t>
+          <t>The Task Shield: Enforcing Task Alignment to Defend Against Indirect Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
@@ -9321,7 +9309,7 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>reasoning</t>
         </is>
       </c>
       <c r="F200" s="5" t="n"/>
@@ -9329,7 +9317,7 @@
       <c r="H200" s="5" t="n"/>
       <c r="I200" s="5" t="inlineStr">
         <is>
-          <t>023292350ef95533d99264dab96ffbd271b24b45</t>
+          <t>8af6009a8d55d456213f6819567eb3ace39dd176</t>
         </is>
       </c>
     </row>
@@ -9339,7 +9327,7 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>LUMINA: Long-horizon Understanding for Multi-turn Interactive Agents</t>
+          <t>The Task Shield: Enforcing Task Alignment to Defend Against Indirect Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
@@ -9354,7 +9342,7 @@
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>session-persistent</t>
+          <t>one-shot</t>
         </is>
       </c>
       <c r="F201" s="5" t="n"/>
@@ -9362,7 +9350,7 @@
       <c r="H201" s="5" t="n"/>
       <c r="I201" s="5" t="inlineStr">
         <is>
-          <t>023292350ef95533d99264dab96ffbd271b24b45</t>
+          <t>8af6009a8d55d456213f6819567eb3ace39dd176</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9360,7 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>LUMINA: Long-horizon Understanding for Multi-turn Interactive Agents</t>
+          <t>The Task Shield: Enforcing Task Alignment to Defend Against Indirect Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
@@ -9395,7 +9383,7 @@
       <c r="H202" s="5" t="n"/>
       <c r="I202" s="5" t="inlineStr">
         <is>
-          <t>023292350ef95533d99264dab96ffbd271b24b45</t>
+          <t>8af6009a8d55d456213f6819567eb3ace39dd176</t>
         </is>
       </c>
     </row>
@@ -9405,7 +9393,7 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>LUMINA: Long-horizon Understanding for Multi-turn Interactive Agents</t>
+          <t>The Task Shield: Enforcing Task Alignment to Defend Against Indirect Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
@@ -9420,7 +9408,7 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>No code/artifact release found. The paper does not state a GitHub, HuggingFace, or other public repository release for the three procedurally-generated environments (ListWorld, TreeWorld, GridWorld) or the oracle-intervention framework anywhere in the visible text.</t>
+          <t>N (unconfirmed) — no code, model, or dataset release for Task Shield itself is mentioned in the main text; the only repository link found (https://github.com/ethz-spylab/agentdojo) is to the third-party AgentDojo benchmark used for evaluation, not the authors' own implementation.</t>
         </is>
       </c>
       <c r="F203" s="5" t="n"/>
@@ -9428,7 +9416,7 @@
       <c r="H203" s="5" t="n"/>
       <c r="I203" s="5" t="inlineStr">
         <is>
-          <t>023292350ef95533d99264dab96ffbd271b24b45</t>
+          <t>8af6009a8d55d456213f6819567eb3ace39dd176</t>
         </is>
       </c>
     </row>
@@ -9438,7 +9426,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>LUMINA: Long-horizon Understanding for Multi-turn Interactive Agents</t>
+          <t>The Task Shield: Enforcing Task Alignment to Defend Against Indirect Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
@@ -9453,7 +9441,7 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>Primary analysis uses the Qwen3 model family across four sizes (4B, 8B, 14B, 32B), run in non-thinking mode with chain-of-thought prompting (thinking mode was tried but found to degrade performance due to token limits) at sampling temperature 0.7, with YaRN encoding applied for long-context (&gt;32K) rollouts. Cross-model generalization checks add Gemma3 (4B-it, 12B-it, 27B-it) and GPT-4o on the ListWorld environment.</t>
+          <t>GPT-4o (primary evaluation model, both as the protected agent and as the LLM powering Task Shield's instruction extraction/alignment scoring) and GPT-4o-mini (a safety-aligned model via instruction-hierarchy training); GPT-3.5-turbo is also tested but relegated to the appendix. Task Shield uses the same model family as the agent it protects for its own LLM-based checks.</t>
         </is>
       </c>
       <c r="F204" s="5" t="n"/>
@@ -9461,7 +9449,7 @@
       <c r="H204" s="5" t="n"/>
       <c r="I204" s="5" t="inlineStr">
         <is>
-          <t>023292350ef95533d99264dab96ffbd271b24b45</t>
+          <t>8af6009a8d55d456213f6819567eb3ace39dd176</t>
         </is>
       </c>
     </row>
@@ -9471,7 +9459,7 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>LUMINA: Long-horizon Understanding for Multi-turn Interactive Agents</t>
+          <t>The Task Shield: Enforcing Task Alignment to Defend Against Indirect Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
@@ -9486,7 +9474,7 @@
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>Three procedurally-generated, complexity-tunable game-like multi-turn environments introduced by the paper: ListWorld (mutate a Python list using only pop actions), TreeWorld (iteratively find a target node in a tree using only get_children actions), and GridWorld (spatially navigate a 2D grid to a target location while avoiding holes). Evaluation metrics are success rate (task completion within a horizon budget) and step accuracy (whether each individual action aligns with at least one optimal policy from the current state).</t>
+          <t>AgentDojo benchmark (Debenedetti et al., 2024; MIT-licensed, github.com/ethz-spylab/agentdojo): four task suites simulating realistic multi-turn agent scenarios — Travel (itinerary management), Workspace (document processing), Banking (financial operations), and Slack (communication tasks) — each with clean-utility and under-attack evaluation. Three indirect prompt injection attack types are used: Important Instructions (Debenedetti et al., 2024), InjecAgent-style conflicting-objective attacks (Zhan et al., 2024), and Ignore Previous (Perez and Ribeiro, 2022).</t>
         </is>
       </c>
       <c r="F205" s="5" t="n"/>
@@ -9494,7 +9482,7 @@
       <c r="H205" s="5" t="n"/>
       <c r="I205" s="5" t="inlineStr">
         <is>
-          <t>023292350ef95533d99264dab96ffbd271b24b45</t>
+          <t>8af6009a8d55d456213f6819567eb3ace39dd176</t>
         </is>
       </c>
     </row>
@@ -9504,7 +9492,7 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>LUMINA: Long-horizon Understanding for Multi-turn Interactive Agents</t>
+          <t>The Task Shield: Enforcing Task Alignment to Defend Against Indirect Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
@@ -9519,7 +9507,7 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>Across all three environments, Qwen3 models show strong performance on short-horizon tasks but success rate drops drastically as horizon length increases, even though step accuracy (correctness of individual actions) remains comparatively high -- e.g., step accuracy often exceeds 60% even when success rate is near zero, showing that compounding per-step errors, not single-step incompetence, drive long-horizon failure, and environments like ListWorld are 'irrecoverable' where a single wrong step causes total task failure. Using the oracle-intervention framework (planning P, state tracking S, history pruning H, and their six combinations), the authors find that planning intervention improves success broadly and consistently across model sizes and environments, largely independent of model size, while the usefulness of state tracking and history pruning is environment- and scale-dependent: history pruning benefits smaller Qwen3 models (4B/8B) substantially (e.g., raising ListWorld success from a base of 12% to 29-35% via S+H) but can hurt larger models (14B/32B suffer performance drops from the same intervention), and larger models benefit more from state tracking than smaller ones. Cross-environment comparison shows the oracles' relative impact is highly rules-dependent: history pruning is most impactful in ListWorld (attending to relevant information is the bottleneck), planning is most useful in GridWorld (navigational tasks benefit from knowing the target and path), and state tracking is most impactful in TreeWorld (which requires complex backtracking) while having little effect in GridWorld. Cross-model validation on ListWorld confirms the scale-dependent pattern: Gemma3 models across all sizes and smaller Qwen3 models benefit from history pruning, but the much larger GPT-4o shows performance degradation from the same intervention (68% base to 62% under full S+P+H vs. 83% under S+P alone), reinforcing that history pruning benefits smaller/weaker models but can hurt stronger ones.</t>
+          <t>On GPT-4o, Task Shield reduces the strongest attack (Important Instructions) success rate from 47.69% (no defense) to 2.07%, while maintaining utility under attack (U) at 69.79% (versus 50.08% no-defense) and improving clean utility (CU) from 69.07% to 73.20%. Averaged across all three attack types, Task Shield achieves overall ASR of 2.07% (Important Instructions), 1.11% (InjecAgent), and 0.48% (Ignore Previous), consistently outperforming four baseline defenses. On GPT-4o-mini, Task Shield reduces ASR to 2.23% while achieving 54.53% utility under attack and 68.04% clean utility, again the best among tested defenses. Baseline comparison against Important Instructions attack (Table 2) shows other defenses trade off poorly: PI Detector achieves low ASR (0.00-7.95%) but severely degrades utility (clean utility drops to ~41%), Repeat Prompt maintains high utility but weak defense (27.82% overall ASR on GPT-4o), and Delimiting leaves ASR as high as 41.65% overall. Task Shield is described as consistently residing near the Pareto-optimal frontier of the security-utility tradeoff in both benign and adversarial conditions (Figure 3).</t>
         </is>
       </c>
       <c r="F206" s="5" t="n"/>
@@ -9527,7 +9515,7 @@
       <c r="H206" s="5" t="n"/>
       <c r="I206" s="5" t="inlineStr">
         <is>
-          <t>023292350ef95533d99264dab96ffbd271b24b45</t>
+          <t>8af6009a8d55d456213f6819567eb3ace39dd176</t>
         </is>
       </c>
     </row>
@@ -9537,7 +9525,7 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>LUMINA: Long-horizon Understanding for Multi-turn Interactive Agents</t>
+          <t>The Task Shield: Enforcing Task Alignment to Defend Against Indirect Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
@@ -9552,7 +9540,7 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>The paper does not compare against external prior systems/baselines; instead its comparative structure is internal (a full 2x2x2 factorial oracle-intervention design): a 'base' condition with no oracle assistance is contrasted against six configurations combining planning (P), state tracking (S), and history pruning (H) oracles (P; S+P; S+P+H; base; S; S+H), since history pruning requires state tracking to be active (it removes prior steps from context, which is only interpretable if the state itself is separately tracked).</t>
+          <t>Four established test-time defenses: Data Delimiting (isolates tool outputs with explicit markers), Prompt Injection (PI) Detector (a classifier-based detection method), Prompt Sandwiching/Repeat Prompt (reinforces the original user prompt via repetition), and Tool Filter (restricts available tools based on task requirements, from the original AgentDojo paper). A No Defense baseline is also reported for all experiments.</t>
         </is>
       </c>
       <c r="F207" s="5" t="n"/>
@@ -9560,7 +9548,7 @@
       <c r="H207" s="5" t="n"/>
       <c r="I207" s="5" t="inlineStr">
         <is>
-          <t>023292350ef95533d99264dab96ffbd271b24b45</t>
+          <t>8af6009a8d55d456213f6819567eb3ace39dd176</t>
         </is>
       </c>
     </row>
@@ -9570,7 +9558,7 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>LUMINA: Long-horizon Understanding for Multi-turn Interactive Agents</t>
+          <t>The Task Shield: Enforcing Task Alignment to Defend Against Indirect Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
@@ -9585,7 +9573,7 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>N/A - non-adversarial (this is a capability-diagnosis/interpretability paper isolating which underlying skills bottleneck long-horizon multi-turn agent performance, not a security paper). The incidental failure mode of interest is directly relevant to context management: long, uncurated interaction history accumulates distractors that can impede an agent's ability to attend to relevant information (motivating the 'history pruning' oracle, which rewrites context to remove distractors and provide a compact summary), and the paper's central finding that this pruning helps smaller/weaker models but can actively hurt larger/stronger models is a notable nuance for context-engineering strategies more broadly -- i.e., context compression is not uniformly beneficial and its value is scale- and task-dependent.</t>
+          <t>This is a security/defense paper with an explicit indirect prompt injection threat model. The attacker cannot directly message the agent; instead they embed malicious instructions within external data sources the agent processes during task execution (e.g., webpages, tool outputs, documents, calendar entries), exploiting the fact that more capable LLMs are more susceptible to following such embedded directives ('Inverse Scaling Law'). The attacker's goal is to cause the agent to perform actions that deviate from the user's original intent (e.g., exfiltrating data to an unintended recipient, visiting attacker-controlled URLs) while appearing superficially benign or plausible, so as to evade naive content-based harm filters. Three concrete attack strategies are tested: embedding high-priority-sounding 'important instructions,' embedding conflicting objectives (InjecAgent-style), and instructing the model to 'ignore previous instructions.'</t>
         </is>
       </c>
       <c r="F208" s="5" t="n"/>
@@ -9593,7 +9581,7 @@
       <c r="H208" s="5" t="n"/>
       <c r="I208" s="5" t="inlineStr">
         <is>
-          <t>023292350ef95533d99264dab96ffbd271b24b45</t>
+          <t>8af6009a8d55d456213f6819567eb3ace39dd176</t>
         </is>
       </c>
     </row>
@@ -9603,7 +9591,7 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>LUMINA: Long-horizon Understanding for Multi-turn Interactive Agents</t>
+          <t>The Task Shield: Enforcing Task Alignment to Defend Against Indirect Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
@@ -9618,7 +9606,7 @@
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>Explicit 'Limitations' section: the paper explicitly frames itself as 'the first step towards explaining the performance degradation of capable LLMs in multi-turn long-horizon agent tasks,' stating that 'while we find valuable insights, many important steps remain to fully understand the performance degradation' (the section is truncated in the extracted text at this point, but this framing establishes the work as a foundational/exploratory study rather than a complete explanation).</t>
+          <t>The paper has an explicit 'Limitations' section (Section 7, following the Conclusion). It states the framework's reliance on LLMs for task instruction extraction and ContributesTo alignment scoring introduces two key vulnerabilities: (1) potential performance degradation when using weaker language models for these internal checks, and (2) susceptibility to adaptive attacks that specifically target the extraction/scoring mechanism itself. It also notes that resource constraints (the high cost of LLM queries) restricted evaluation to a single benchmark (AgentDojo) and a single model family, limiting generalizability claims. A separate 'Future Work' section lists open directions: improving efficiency/robustness of the LLM-based extraction and verification, extending Task Shield to broader threats beyond prompt injection (e.g., jailbreaks, system-prompt extraction), adapting it to domain-specific business contexts, and using the task-alignment concept to generate synthetic training data for misalignment scenarios.</t>
         </is>
       </c>
       <c r="F209" s="5" t="n"/>
@@ -9626,7 +9614,7 @@
       <c r="H209" s="5" t="n"/>
       <c r="I209" s="5" t="inlineStr">
         <is>
-          <t>023292350ef95533d99264dab96ffbd271b24b45</t>
+          <t>8af6009a8d55d456213f6819567eb3ace39dd176</t>
         </is>
       </c>
     </row>
@@ -9636,7 +9624,7 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>LUMINA: Long-horizon Understanding for Multi-turn Interactive Agents</t>
+          <t>The Task Shield: Enforcing Task Alignment to Defend Against Indirect Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
@@ -9651,7 +9639,7 @@
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>This paper investigates why LLMs that excel at complex single-turn reasoning tasks underperform on multi-turn, long-horizon agentic tasks, by introducing an oracle counterfactual intervention framework that isolates the causal contribution of three specific underlying skills to agent success: planning (providing a description of the correct single-turn subtask on the optimal trajectory), state tracking (providing an accurate, ground-truth state description at each turn), and history pruning (rewriting the context to remove distractors and prior steps, providing a compact summary instead of the full interaction history -- a manipulation that structurally depends on state tracking being active, since pruning removes information that only the state-tracking oracle would otherwise preserve). Because real-world multi-turn benchmarks admit many equally optimal paths to a goal (making exhaustive oracle annotation intractable), the authors introduce three procedurally-generated, complexity-tunable game-like environments (ListWorld, TreeWorld, GridWorld) in which the set of optimal actions at any given state can be computed exactly, enabling precise, confound-free oracle interventions and a factorial design over all six meaningful combinations of the three interventions. Using ReAct-style prompting to interleave reasoning traces with actions, the authors evaluate Qwen3 models (4B-32B) as the primary analysis, with Gemma3 and GPT-4o used to validate generalization on ListWorld. The central findings are that planning assistance improves performance broadly and fairly uniformly across model scales and environments, while the value of state tracking and especially history pruning is highly contingent on both model scale (history pruning helps smaller/weaker models but can degrade larger/stronger models' performance) and environment structure (which skill is most impactful varies by the task's inherent challenge -- attention to relevant information in ListWorld, backtracking-heavy state tracking in TreeWorld, spatial planning in GridWorld). The paper additionally shows that step-level accuracy remains relatively high even as overall task success collapses with horizon length, indicating that long-horizon failure is driven primarily by the compounding of occasional per-step errors over many turns rather than by any single catastrophic reasoning failure, with some environments (e.g., ListWorld) being fully irrecoverable from a single misstep.</t>
+          <t>The paper reframes LLM agent security away from detecting 'harmful' content and toward verifying 'task alignment' — whether every instruction and tool call in a conversation actually serves the user's stated objectives. It formalizes this via a message-privilege hierarchy (system/user/assistant/tool levels) and defines task instructions as actionable directives extracted from any message; a ContributesTo(e, t) relation captures whether one instruction e helps achieve another instruction t within the conversation history; and an instruction satisfies the Task Instruction Alignment Condition if it contributes (via a continuous, LLM-scored fuzzy relevance score rather than a rigid binary classification) to at least one user-level task instruction. A conversation achieves full Task Alignment when all assistant-level instructions satisfy this condition, meaning injected malicious directives — which by construction do not serve the user's original goal — are naturally identified and filtered regardless of whether their content looks superficially harmful. The authors implement this as Task Shield, a test-time defense with three components: (1) an LLM-prompted instruction-extraction stage that pulls out explicit and implicit actionable directives from every incoming message (user, assistant, and tool-output) and rewrites information-seeking queries as explicit instructions; (2) an alignment-check stage that computes fuzzy ContributesTo scores against the accumulated User Task Set and flags an instruction as misaligned if its total contribution score is zero; and (3) a feedback-generation stage that, upon detecting misalignment, returns a structured alert (identifying the misaligned instruction, explaining the risk, and reminding the agent of current user objectives) to steer the agent back on track, while blocking execution of misaligned tool calls outright. This creates multiple layered checkpoints — at tool-output ingestion, at assistant response/tool-call generation, and via continuous validation against the accumulated user task set — so an injected instruction faces several independent chances to be caught before it can be executed.</t>
         </is>
       </c>
       <c r="F210" s="5" t="n"/>
@@ -9659,7 +9647,7 @@
       <c r="H210" s="5" t="n"/>
       <c r="I210" s="5" t="inlineStr">
         <is>
-          <t>023292350ef95533d99264dab96ffbd271b24b45</t>
+          <t>8af6009a8d55d456213f6819567eb3ace39dd176</t>
         </is>
       </c>
     </row>
@@ -9669,7 +9657,7 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>AgentProg: Empowering Long-Horizon GUI Agents with Program-guided Context Management</t>
+          <t>PIShield: Detecting Prompt Injection Attacks via Intrinsic LLM Features</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
@@ -9692,7 +9680,7 @@
       <c r="H211" s="5" t="n"/>
       <c r="I211" s="5" t="inlineStr">
         <is>
-          <t>420c63cc0480a1990a348b741612cbde516b3f30</t>
+          <t>1db392d42f020925561c0686ec24831fcd78bcae</t>
         </is>
       </c>
     </row>
@@ -9702,7 +9690,7 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>AgentProg: Empowering Long-Horizon GUI Agents with Program-guided Context Management</t>
+          <t>PIShield: Detecting Prompt Injection Attacks via Intrinsic LLM Features</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
@@ -9717,7 +9705,7 @@
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>ML/AI</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="F212" s="5" t="n"/>
@@ -9725,7 +9713,7 @@
       <c r="H212" s="5" t="n"/>
       <c r="I212" s="5" t="inlineStr">
         <is>
-          <t>420c63cc0480a1990a348b741612cbde516b3f30</t>
+          <t>1db392d42f020925561c0686ec24831fcd78bcae</t>
         </is>
       </c>
     </row>
@@ -9735,7 +9723,7 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>AgentProg: Empowering Long-Horizon GUI Agents with Program-guided Context Management</t>
+          <t>PIShield: Detecting Prompt Injection Attacks via Intrinsic LLM Features</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
@@ -9758,7 +9746,7 @@
       <c r="H213" s="5" t="n"/>
       <c r="I213" s="5" t="inlineStr">
         <is>
-          <t>420c63cc0480a1990a348b741612cbde516b3f30</t>
+          <t>1db392d42f020925561c0686ec24831fcd78bcae</t>
         </is>
       </c>
     </row>
@@ -9768,7 +9756,7 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>AgentProg: Empowering Long-Horizon GUI Agents with Program-guided Context Management</t>
+          <t>PIShield: Detecting Prompt Injection Attacks via Intrinsic LLM Features</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
@@ -9791,7 +9779,7 @@
       <c r="H214" s="5" t="n"/>
       <c r="I214" s="5" t="inlineStr">
         <is>
-          <t>420c63cc0480a1990a348b741612cbde516b3f30</t>
+          <t>1db392d42f020925561c0686ec24831fcd78bcae</t>
         </is>
       </c>
     </row>
@@ -9801,7 +9789,7 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>AgentProg: Empowering Long-Horizon GUI Agents with Program-guided Context Management</t>
+          <t>PIShield: Detecting Prompt Injection Attacks via Intrinsic LLM Features</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
@@ -9816,7 +9804,7 @@
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>tool-output</t>
         </is>
       </c>
       <c r="F215" s="5" t="n"/>
@@ -9824,7 +9812,7 @@
       <c r="H215" s="5" t="n"/>
       <c r="I215" s="5" t="inlineStr">
         <is>
-          <t>420c63cc0480a1990a348b741612cbde516b3f30</t>
+          <t>1db392d42f020925561c0686ec24831fcd78bcae</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9822,7 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>AgentProg: Empowering Long-Horizon GUI Agents with Program-guided Context Management</t>
+          <t>PIShield: Detecting Prompt Injection Attacks via Intrinsic LLM Features</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
@@ -9849,7 +9837,7 @@
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>goal-hijack</t>
         </is>
       </c>
       <c r="F216" s="5" t="n"/>
@@ -9857,7 +9845,7 @@
       <c r="H216" s="5" t="n"/>
       <c r="I216" s="5" t="inlineStr">
         <is>
-          <t>420c63cc0480a1990a348b741612cbde516b3f30</t>
+          <t>1db392d42f020925561c0686ec24831fcd78bcae</t>
         </is>
       </c>
     </row>
@@ -9867,7 +9855,7 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>AgentProg: Empowering Long-Horizon GUI Agents with Program-guided Context Management</t>
+          <t>PIShield: Detecting Prompt Injection Attacks via Intrinsic LLM Features</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
@@ -9882,7 +9870,7 @@
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F217" s="5" t="n"/>
@@ -9890,7 +9878,7 @@
       <c r="H217" s="5" t="n"/>
       <c r="I217" s="5" t="inlineStr">
         <is>
-          <t>420c63cc0480a1990a348b741612cbde516b3f30</t>
+          <t>1db392d42f020925561c0686ec24831fcd78bcae</t>
         </is>
       </c>
     </row>
@@ -9900,7 +9888,7 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>AgentProg: Empowering Long-Horizon GUI Agents with Program-guided Context Management</t>
+          <t>PIShield: Detecting Prompt Injection Attacks via Intrinsic LLM Features</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
@@ -9915,7 +9903,7 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F218" s="5" t="n"/>
@@ -9923,7 +9911,7 @@
       <c r="H218" s="5" t="n"/>
       <c r="I218" s="5" t="inlineStr">
         <is>
-          <t>420c63cc0480a1990a348b741612cbde516b3f30</t>
+          <t>1db392d42f020925561c0686ec24831fcd78bcae</t>
         </is>
       </c>
     </row>
@@ -9933,7 +9921,7 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>AgentProg: Empowering Long-Horizon GUI Agents with Program-guided Context Management</t>
+          <t>PIShield: Detecting Prompt Injection Attacks via Intrinsic LLM Features</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
@@ -9948,7 +9936,7 @@
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>ingestion</t>
+          <t>reasoning</t>
         </is>
       </c>
       <c r="F219" s="5" t="n"/>
@@ -9956,7 +9944,7 @@
       <c r="H219" s="5" t="n"/>
       <c r="I219" s="5" t="inlineStr">
         <is>
-          <t>420c63cc0480a1990a348b741612cbde516b3f30</t>
+          <t>1db392d42f020925561c0686ec24831fcd78bcae</t>
         </is>
       </c>
     </row>
@@ -9966,7 +9954,7 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>AgentProg: Empowering Long-Horizon GUI Agents with Program-guided Context Management</t>
+          <t>PIShield: Detecting Prompt Injection Attacks via Intrinsic LLM Features</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
@@ -9981,7 +9969,7 @@
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>session-persistent</t>
+          <t>one-shot</t>
         </is>
       </c>
       <c r="F220" s="5" t="n"/>
@@ -9989,7 +9977,7 @@
       <c r="H220" s="5" t="n"/>
       <c r="I220" s="5" t="inlineStr">
         <is>
-          <t>420c63cc0480a1990a348b741612cbde516b3f30</t>
+          <t>1db392d42f020925561c0686ec24831fcd78bcae</t>
         </is>
       </c>
     </row>
@@ -9999,7 +9987,7 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>AgentProg: Empowering Long-Horizon GUI Agents with Program-guided Context Management</t>
+          <t>PIShield: Detecting Prompt Injection Attacks via Intrinsic LLM Features</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
@@ -10022,7 +10010,7 @@
       <c r="H221" s="5" t="n"/>
       <c r="I221" s="5" t="inlineStr">
         <is>
-          <t>420c63cc0480a1990a348b741612cbde516b3f30</t>
+          <t>1db392d42f020925561c0686ec24831fcd78bcae</t>
         </is>
       </c>
     </row>
@@ -10032,7 +10020,7 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>AgentProg: Empowering Long-Horizon GUI Agents with Program-guided Context Management</t>
+          <t>PIShield: Detecting Prompt Injection Attacks via Intrinsic LLM Features</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
@@ -10047,7 +10035,7 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>The system is open-sourced at https://github.com/MobileLLM/AgentProg, including the AgentProg framework implementation. The paper also introduces and releases a new evaluation suite, AW-Extend, a 19-task extended long-horizon benchmark built on top of AndroidWorld, spanning compositional tasks (combining interdependent sub-tasks) and iterative tasks (scaling sub-task repetition counts to n=10 and n=20).</t>
+          <t>The paper states in the Introduction footnote 'Our code is publicly available at https://github.com/weizou52/PIShield,' confirming a public code release for the PIShield detection method.</t>
         </is>
       </c>
       <c r="F222" s="5" t="n"/>
@@ -10055,7 +10043,7 @@
       <c r="H222" s="5" t="n"/>
       <c r="I222" s="5" t="inlineStr">
         <is>
-          <t>420c63cc0480a1990a348b741612cbde516b3f30</t>
+          <t>1db392d42f020925561c0686ec24831fcd78bcae</t>
         </is>
       </c>
     </row>
@@ -10065,7 +10053,7 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>AgentProg: Empowering Long-Horizon GUI Agents with Program-guided Context Management</t>
+          <t>PIShield: Detecting Prompt Injection Attacks via Intrinsic LLM Features</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
@@ -10080,7 +10068,7 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>AgentProg is implemented with Gemini-2.5-Pro as the backbone planning/reasoning model and UI-TARS-1.5-API for UI element grounding/localization. Comparison baselines span a range of backbones: MobileGPT, AutoDroid-V2, M3A (paired with GPT-4-Turbo or Gemini-2.5-Pro, using either accessibility-tree or Set-of-Mark observation modes), GLM-4.1V-9B-Thinking, UI-TARS (UI-TARS-7B and UI-TARS-1.5-API variants), V-Droid, MobileUse, UI-Venus, Agent S3, and Mobile-Agent-v3 (paired with GUI-Owl-7B or GUI-Owl-32B).</t>
+          <t>Llama-3.1-8B-Instruct is the primary detection LLM used to extract residual-stream vectors (Layer 14). Additional instruction-tuned models are evaluated for generalization: Llama-3.1-70B-Instruct (Layer 34) and Qwen3-4B-Instruct (Layer 27). A non-instruction-tuned base model, Llama-3.1-8B (base, without instruction tuning), is also tested as a comparison to show that no layer achieves good separation without instruction tuning. Baseline detectors use their own respective backbone LLMs: PromptGuard (Meta's fine-tuned classifier), ProtectAI-deberta (DeBERTa-based), DataSentinel (Mistral-7B per its open-source implementation), InjecGuard (Qwen2-1.5B-Instruct), and TaskTracker (evaluated with Llama-3-8B-Instruct).</t>
         </is>
       </c>
       <c r="F223" s="5" t="n"/>
@@ -10088,7 +10076,7 @@
       <c r="H223" s="5" t="n"/>
       <c r="I223" s="5" t="inlineStr">
         <is>
-          <t>420c63cc0480a1990a348b741612cbde516b3f30</t>
+          <t>1db392d42f020925561c0686ec24831fcd78bcae</t>
         </is>
       </c>
     </row>
@@ -10098,7 +10086,7 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>AgentProg: Empowering Long-Horizon GUI Agents with Program-guided Context Management</t>
+          <t>PIShield: Detecting Prompt Injection Attacks via Intrinsic LLM Features</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
@@ -10113,7 +10101,7 @@
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>AndroidWorld (a standard, widely-used benchmark for mobile device-control agents) and AW-Extend, a new 19-task extended long-horizon benchmark constructed by the authors, comprising compositional tasks (requiring critical information maintenance across multiple interdependent sub-tasks/applications) and iterative tasks (scaling repeated sub-task counts to n=10/20 to test memory-filtering robustness), designed specifically because existing methods perform well on standard AndroidWorld but the authors observed catastrophic degradation on longer, more complex task sequences.</t>
+          <t>Utility (false positive rate) is evaluated on four short-context datasets -- OpenPromptInjection (OPI), Dolly, MMLU, BoolQ -- and two long-context datasets from LongBench, Musique and NarrativeQA. Robustness (false negative rate) is evaluated on eight malicious datasets: attack variants of the four short-context sets (OPI-P, Dolly-P, MMLU-P, BoolQ-P, constructed using eight different attack strategies with FNR averaged across them), attack variants of the two long-context sets (Musique-P, NarrativeQA-P, created by injecting a manually designed malicious instruction three times per sample), plus two existing malicious benchmarks, TaskTracker and CyberSecEval2, covering real-world prompt injection attacks. Training data for PIShield's linear classifier uses Cleaned-Alpaca and a preprocessed English dataset (clean/contaminated construction detailed in the appendix).</t>
         </is>
       </c>
       <c r="F224" s="5" t="n"/>
@@ -10121,7 +10109,7 @@
       <c r="H224" s="5" t="n"/>
       <c r="I224" s="5" t="inlineStr">
         <is>
-          <t>420c63cc0480a1990a348b741612cbde516b3f30</t>
+          <t>1db392d42f020925561c0686ec24831fcd78bcae</t>
         </is>
       </c>
     </row>
@@ -10131,7 +10119,7 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>AgentProg: Empowering Long-Horizon GUI Agents with Program-guided Context Management</t>
+          <t>PIShield: Detecting Prompt Injection Attacks via Intrinsic LLM Features</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
@@ -10146,7 +10134,7 @@
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>AgentProg achieves a new state-of-the-art 78.0% success rate on AndroidWorld, surpassing the prior best (Mobile-Agent-v3 with GUI-Owl-32B, 73.3%) by 4.7 percentage points, and outperforms all baselines at every task difficulty level, with the largest margin on medium-difficulty tasks (+25.0 points over MobileUse). On the new AW-Extend long-horizon suite, AgentProg reaches 68.4% success versus the best baseline UI-TARS at 36.8% -- nearly double -- while baseline methods that perform reasonably on AndroidWorld (e.g., UI-TARS at 64.2%, Mobile-Agent-v3-32B at 73.3%) show catastrophic degradation on AW-Extend (down to 36.8% and 28.9% respectively), confirming the paper's central claim that existing context-management strategies (sliding window, summarization, hierarchical planning) fail to scale to long-horizon tasks. Component ablations show global belief state contributes the largest single gain (removing it drops AndroidWorld success from 78.0% to 53.9%, a 24.1-point loss, and AW-Extend from 68.4% to 35.1%, a 33.3-point loss); removing the Execution Tree (control-flow-based context pruning) drops AW-Extend success from 68.4% to 39.5% and AndroidWorld from 78.0% to 61.6%; removing Explicit Variables drops AndroidWorld from 78.0% to 64.2% and AW-Extend from 68.4% to 50.0%. AgentProg maintains near-constant dynamic context token usage (~9k tokens) over 50 execution steps versus Mobile-Agent-v3's persistently high ~17k tokens and UI-TARS's continuously growing context, though AgentProg incurs a larger static prompt prefix (12.5k tokens/call, mostly cacheable) and generates substantially more output tokens (179.7k total vs. 22.1k for Mobile-Agent-v3 and 3.2k for UI-TARS) and correspondingly higher latency (2662s vs. 1604s and 312s), attributed to its explicit belief-state and program-counter bookkeeping overhead. Only 2.5% of generated Semantic Task Programs contained unrecoverable planning errors, indicating high reliability of the STP generation stage itself.</t>
+          <t>PIShield achieves the best average false positive rate (0.5%) and false negative rate (1.4%) among all 8 compared baselines. On FPR (Table 1), PIShield's average of 0.005 beats PIGuard (0.007), PromptArmor (0.013), ProtectAI-deberta (0.101), InjecGuard (0.082), TaskTracker (0.274), AttentionTracker (0.328), and DataSentinel (0.336), with several baselines (DataSentinel, AttentionTracker, TaskTracker) showing severe over-defense on long-context datasets like Musique/NarrativeQA (FPR up to 0.99-1.00) while PIShield stays at 0.02/0.00. On FNR (Table 2), PIShield's average of 0.014 substantially outperforms all baselines, the closest being PromptGuard at 0.087 and DataSentinel at 0.104, while several baselines (ProtectAI-deberta 0.759, PIGuard 0.702, InjecGuard 0.663) fail badly. Efficiency: PIShield reduces testing cost by 23x compared to DataSentinel (S&amp;P'25), since it requires only a single forward pass through the backend LLM plus a lightweight linear classifier, avoiding model fine-tuning or additional generation. Under strong, white-box adaptive attacks (attacker has access to both the backend LLM and the linear classifier), PIShield remains effective, maintaining low FNR (specific per-dataset adaptive-attack FNR reported in Table 4). Generalization tests across Llama-3.1-70B-Instruct and Qwen3-4B-Instruct show similarly low FPR/FNR (e.g., 0.00-0.05 range across datasets), while the non-instruction-tuned Llama-3.1-8B base model shows no layer achieving simultaneously low FPR and FNR, confirming the method's dependence on instruction-tuning-induced internal representations.</t>
         </is>
       </c>
       <c r="F225" s="5" t="n"/>
@@ -10154,7 +10142,7 @@
       <c r="H225" s="5" t="n"/>
       <c r="I225" s="5" t="inlineStr">
         <is>
-          <t>420c63cc0480a1990a348b741612cbde516b3f30</t>
+          <t>1db392d42f020925561c0686ec24831fcd78bcae</t>
         </is>
       </c>
     </row>
@@ -10164,7 +10152,7 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>AgentProg: Empowering Long-Horizon GUI Agents with Program-guided Context Management</t>
+          <t>PIShield: Detecting Prompt Injection Attacks via Intrinsic LLM Features</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
@@ -10179,7 +10167,7 @@
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>AndroidWorld baselines: MobileGPT, AutoDroid-V2, M3A (multiple backbone/observation-mode variants), GLM-4.1V-9B-Thinking, UI-TARS (7B and 1.5-API), V-Droid, MobileUse, UI-Venus, Agent S3, and Mobile-Agent-v3 (GUI-Owl-7B/32B). AW-Extend baselines (a curated subset representing three distinct context-management paradigms): M3A representing summarization-based context management, UI-TARS representing sliding-window context management, and Mobile-Agent-v3 representing hierarchical-planning-based context management.</t>
+          <t>Eight baselines across industry and academic sources: ProtectAI-deberta and PromptGuard (released by industry, Meta and ProtectAI respectively), plus PromptArmor, PIGuard, InjecGuard, DataSentinel, AttentionTracker, and TaskTracker (from research papers/blogs). These span prompting-based detection (PromptArmor), fine-tuned classifier detection (PromptGuard, PIGuard, InjecGuard, ProtectAI-deberta), game-theoretic fine-tuned detection (DataSentinel), and internal-state/attention-shift detection (AttentionTracker, TaskTracker).</t>
         </is>
       </c>
       <c r="F226" s="5" t="n"/>
@@ -10187,7 +10175,7 @@
       <c r="H226" s="5" t="n"/>
       <c r="I226" s="5" t="inlineStr">
         <is>
-          <t>420c63cc0480a1990a348b741612cbde516b3f30</t>
+          <t>1db392d42f020925561c0686ec24831fcd78bcae</t>
         </is>
       </c>
     </row>
@@ -10197,7 +10185,7 @@
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>AgentProg: Empowering Long-Horizon GUI Agents with Program-guided Context Management</t>
+          <t>PIShield: Detecting Prompt Injection Attacks via Intrinsic LLM Features</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
@@ -10212,7 +10200,7 @@
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>N/A - non-adversarial. This is a capability/systems paper on long-horizon mobile GUI task automation rather than a security study; the incidental failure mode of interest is context degradation under long-horizon execution -- specifically, three empirically observed failure patterns in existing GUI agents: (1) lack of overall planning, causing premature task termination when agents mistakenly believe multi-step tasks are complete; (2) failure to remember critical intermediate information (e.g., losing a to-do list's items across sub-task execution) due to context-management schemes lacking task-aware sensitivity; and (3) poor understanding of dynamic/partially-observable environment states, causing agents to act on stale or incorrect beliefs about hidden device state (e.g., misjudging the current date and consequently deleting the wrong calendar events across multiple weeks).</t>
+          <t>The paper adopts the same threat model as prior prompt injection literature. The attacker's goal is to compromise the data portion of a prompt so the backend LLM performs an attacker-chosen injected task instead of the intended one (e.g., skewing sentiment in a product-review summary, or more severe outcomes like extracting sensitive user information or initiating unauthorized financial transactions). Attacker background knowledge is assumed strong: the attacker knows the backend LLM (with white-box access if open-source), can access the original instruction and data prompt, and additionally has white-box access to the detection model itself -- enabling optimization-based adaptive attacks specifically designed to evade PIShield's linear classifier, which the paper explicitly evaluates. Attacker capabilities are limited to manipulating the data portion of the prompt (e.g., injecting a malicious instruction into email/webpage/API content), consistent with the standard indirect prompt injection setting.</t>
         </is>
       </c>
       <c r="F227" s="5" t="n"/>
@@ -10220,7 +10208,7 @@
       <c r="H227" s="5" t="n"/>
       <c r="I227" s="5" t="inlineStr">
         <is>
-          <t>420c63cc0480a1990a348b741612cbde516b3f30</t>
+          <t>1db392d42f020925561c0686ec24831fcd78bcae</t>
         </is>
       </c>
     </row>
@@ -10230,7 +10218,7 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>AgentProg: Empowering Long-Horizon GUI Agents with Program-guided Context Management</t>
+          <t>PIShield: Detecting Prompt Injection Attacks via Intrinsic LLM Features</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
@@ -10245,7 +10233,7 @@
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>The paper has no section explicitly titled 'Limitations,' but a subsection late in the Discussion/Conclusion area (before Section 7 Conclusion) enumerates several forward-looking caveats functioning as the closest analog. First, on latency/practicality: AgentProg exhibits higher output-token generation and longer end-to-end latency than baselines due to its explicit belief-state and program-counter bookkeeping overhead, and the authors note 'fast agents become impractical if they require frequent human intervention for failures,' anticipating future model-level (faster inference, distillation) and system-level (merging Program Counter Update and Action Generation into a single LLM call) optimizations as mitigations. Second, on-device deployment: AgentProg currently relies on cloud-based LLMs, introducing network latency and privacy concerns, which the authors propose to address in future work via distilling the STP Execution phase into on-device Small Language Models while keeping STP Generation (requiring stronger reasoning) in the cloud. Third, generalization scope: although AgentProg is evaluated only on mobile GUI tasks, the authors state the program-guided context-management approach should generalize to web navigation, desktop automation, and tool-use settings, but explicitly leave empirical validation on non-mobile domains to future work. Additionally, the paper notes step-count comparisons across methods (Table 4) should be interpreted cautiously since different agents issue varying numbers of LLM queries per environment step, complicating apples-to-apples efficiency comparison.</t>
+          <t>The paper has an explicit 'Limitations' section stating two points. (1) Like other training- or fine-tuning-based approaches, PIShield relies on labeled training data to generalize across different domains and prompt distributions, so its effectiveness may depend on the diversity of the training data used to capture different prompt styles. (2) PIShield may produce false positives when benign instructions are legitimately included within the data prompt, reflecting a broader, inherent ambiguity in defining prompt injection: the distinction between benign instructional content and malicious injected instructions is not always clear-cut. The authors frame their contribution as focusing on a widely applicable characteristic of prompt injection (instruction-like content in untrusted data) and argue detecting this signal remains feasible and effective in practice despite this ambiguity. A companion Ethical Considerations section also explicitly acknowledges dual-use risk -- that adversaries could study the released detection strategy to craft more evasive attacks -- but argues the benefit of open community access to an effective detection tool outweighs this risk.</t>
         </is>
       </c>
       <c r="F228" s="5" t="n"/>
@@ -10253,7 +10241,7 @@
       <c r="H228" s="5" t="n"/>
       <c r="I228" s="5" t="inlineStr">
         <is>
-          <t>420c63cc0480a1990a348b741612cbde516b3f30</t>
+          <t>1db392d42f020925561c0686ec24831fcd78bcae</t>
         </is>
       </c>
     </row>
@@ -10263,7 +10251,7 @@
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>AgentProg: Empowering Long-Horizon GUI Agents with Program-guided Context Management</t>
+          <t>PIShield: Detecting Prompt Injection Attacks via Intrinsic LLM Features</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
@@ -10278,7 +10266,7 @@
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>AgentProg is a program-guided context-management framework for long-horizon mobile GUI agents, motivated by three empirically identified failure modes in existing methods on extended (dozens-to-hundreds-of-step) tasks: poor overall task planning/progress tracking, failure to retain task-critical information amid ever-growing interaction history, and poor understanding of dynamic, partially-observable environment states. The core insight is an analogy to traditional programs, which manage extremely long execution with limited memory via functions, variables, and control-flow scoping; AgentProg reframes an agent's interaction history as an executing program rather than a flat, ever-expanding sequence. Concretely, the framework introduces Semantic Task Program (STP), a domain-specific language that extends natural-language task instructions with structured control flow (loops, conditionals, functions) and explicit variable declarations/assignments (e.g., 'record them as {task_list}'), unlike rigid symbolic programming languages -- STP instructions remain fuzzy/natural-language-style and are interpreted adaptively at runtime against the actual (partially observed) environment state, since a program generated purely upfront would otherwise be brittle to unforeseen environment conditions. AgentProg operates in two stages: (1) STP Generation, where the agent performs global planning to produce a structured program with identified critical variables based on the task requirements, and (2) STP Execution, where the agent incrementally interprets the program step-by-step, using the program's control-flow structure to determine what context to retain (data flowing through active variables and the current execution-tree branch) versus discard (completed loop iterations, non-taken branches), yielding principled control-flow-based context pruning rather than heuristic summarization or fixed sliding windows. To handle the environment dynamicity inherent in the agent-program analogy (which traditional programming paradigms lack), AgentProg further incorporates a Global Belief State mechanism, inspired by the Belief-MDP framework, that continuously validates and updates the agent's hypotheses about hidden environment variables and can detect a 'Belief-Reality Gap' at runtime (e.g., an expected UI-state change that does not occur, indicating an unmodeled obstacle) and trigger adaptive rerouting rather than blindly continuing a failing STP-derived strategy. Evaluated with a Gemini-2.5-Pro backbone on AndroidWorld and a newly introduced AW-Extend long-horizon benchmark (19 compositional and iterative tasks), AgentProg achieves new state-of-the-art success rates on both, with especially large margins over sliding-window, summarization, and hierarchical-planning baselines on AW-Extend, while maintaining near-constant dynamic context-token usage across 50-step trajectories -- at the cost of higher output-token generation and end-to-end latency relative to lighter-weight baselines.</t>
+          <t>PIShield is a lightweight prompt injection detection method that exploits an intrinsic property of instruction-tuned LLMs rather than requiring model fine-tuning or an additional LLM inference call at test time. Its central observation is that because injected prompt-injection content is itself an instruction, instruction-tuned LLMs internally encode representations that distinguish prompts containing an embedded instruction from genuinely benign data -- specifically, at certain intermediate layers, the residual-stream vector of the final token of a data prompt is linearly separable between clean and contaminated (instruction-injected) inputs (empirically visualized via PCA on Llama-3.1-8B-Instruct's Layer 14 representations). Building directly on this observation, PIShield extracts the residual-stream vector for the last token of a given data prompt from a chosen detection LLM (which may be the backend LLM itself if the defender has white-box access, or a smaller open-source proxy model such as Llama-3.1-8B-Instruct otherwise) and trains a simple linear classifier on these vectors using labeled clean and contaminated training examples (constructed from Cleaned-Alpaca and preprocessed English text corpora), then applies this classifier at inference time to flag contaminated prompts. Because detection requires only a single forward pass through the LLM to obtain the internal representation (no fine-tuning of the backend model, no generated response to analyze, and no separate detector LLM to run) rather than the additional model calls or fine-tuning that competing approaches like PromptArmor, DataSentinel, or PromptGuard require, PIShield achieves substantially lower per-prompt testing cost while also generalizing more robustly to long-context inputs than attention-shift-based (AttentionTracker) or internal-state-deviation-based (TaskTracker) alternatives, which the paper shows suffer severe false-positive rates in long-context settings. The method is also evaluated against strong adaptive attackers who have white-box access to both the backend LLM and the linear classifier itself, and is shown to remain effective under this worst-case assumption.</t>
         </is>
       </c>
       <c r="F229" s="5" t="n"/>
@@ -10286,7 +10274,7 @@
       <c r="H229" s="5" t="n"/>
       <c r="I229" s="5" t="inlineStr">
         <is>
-          <t>420c63cc0480a1990a348b741612cbde516b3f30</t>
+          <t>1db392d42f020925561c0686ec24831fcd78bcae</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10284,7 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>ICON: Indirect Prompt Injection Defense for Agents based on Inference-Time Correction</t>
+          <t>Rethinking All Evidence: Enhancing Trustworthy Retrieval-Augmented Generation via Conflict-Driven Summarization</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
@@ -10319,7 +10307,7 @@
       <c r="H230" s="5" t="n"/>
       <c r="I230" s="5" t="inlineStr">
         <is>
-          <t>9a559291c36be0ac35a9db4682d18acc6ccff2d3</t>
+          <t>0a06adbce02a4f5db3b3f08f23394e3acfc9a573</t>
         </is>
       </c>
     </row>
@@ -10329,7 +10317,7 @@
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>ICON: Indirect Prompt Injection Defense for Agents based on Inference-Time Correction</t>
+          <t>Rethinking All Evidence: Enhancing Trustworthy Retrieval-Augmented Generation via Conflict-Driven Summarization</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
@@ -10344,7 +10332,7 @@
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>ML/AI</t>
         </is>
       </c>
       <c r="F231" s="5" t="n"/>
@@ -10352,7 +10340,7 @@
       <c r="H231" s="5" t="n"/>
       <c r="I231" s="5" t="inlineStr">
         <is>
-          <t>9a559291c36be0ac35a9db4682d18acc6ccff2d3</t>
+          <t>0a06adbce02a4f5db3b3f08f23394e3acfc9a573</t>
         </is>
       </c>
     </row>
@@ -10362,7 +10350,7 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>ICON: Indirect Prompt Injection Defense for Agents based on Inference-Time Correction</t>
+          <t>Rethinking All Evidence: Enhancing Trustworthy Retrieval-Augmented Generation via Conflict-Driven Summarization</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
@@ -10385,7 +10373,7 @@
       <c r="H232" s="5" t="n"/>
       <c r="I232" s="5" t="inlineStr">
         <is>
-          <t>9a559291c36be0ac35a9db4682d18acc6ccff2d3</t>
+          <t>0a06adbce02a4f5db3b3f08f23394e3acfc9a573</t>
         </is>
       </c>
     </row>
@@ -10395,7 +10383,7 @@
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>ICON: Indirect Prompt Injection Defense for Agents based on Inference-Time Correction</t>
+          <t>Rethinking All Evidence: Enhancing Trustworthy Retrieval-Augmented Generation via Conflict-Driven Summarization</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
@@ -10418,7 +10406,7 @@
       <c r="H233" s="5" t="n"/>
       <c r="I233" s="5" t="inlineStr">
         <is>
-          <t>9a559291c36be0ac35a9db4682d18acc6ccff2d3</t>
+          <t>0a06adbce02a4f5db3b3f08f23394e3acfc9a573</t>
         </is>
       </c>
     </row>
@@ -10428,7 +10416,7 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>ICON: Indirect Prompt Injection Defense for Agents based on Inference-Time Correction</t>
+          <t>Rethinking All Evidence: Enhancing Trustworthy Retrieval-Augmented Generation via Conflict-Driven Summarization</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
@@ -10443,7 +10431,7 @@
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>RAG</t>
         </is>
       </c>
       <c r="F234" s="5" t="n"/>
@@ -10451,7 +10439,7 @@
       <c r="H234" s="5" t="n"/>
       <c r="I234" s="5" t="inlineStr">
         <is>
-          <t>9a559291c36be0ac35a9db4682d18acc6ccff2d3</t>
+          <t>0a06adbce02a4f5db3b3f08f23394e3acfc9a573</t>
         </is>
       </c>
     </row>
@@ -10461,7 +10449,7 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>ICON: Indirect Prompt Injection Defense for Agents based on Inference-Time Correction</t>
+          <t>Rethinking All Evidence: Enhancing Trustworthy Retrieval-Augmented Generation via Conflict-Driven Summarization</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
@@ -10476,7 +10464,7 @@
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>silent-corruption</t>
         </is>
       </c>
       <c r="F235" s="5" t="n"/>
@@ -10484,7 +10472,7 @@
       <c r="H235" s="5" t="n"/>
       <c r="I235" s="5" t="inlineStr">
         <is>
-          <t>9a559291c36be0ac35a9db4682d18acc6ccff2d3</t>
+          <t>0a06adbce02a4f5db3b3f08f23394e3acfc9a573</t>
         </is>
       </c>
     </row>
@@ -10494,7 +10482,7 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>ICON: Indirect Prompt Injection Defense for Agents based on Inference-Time Correction</t>
+          <t>Rethinking All Evidence: Enhancing Trustworthy Retrieval-Augmented Generation via Conflict-Driven Summarization</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
@@ -10509,7 +10497,7 @@
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F236" s="5" t="n"/>
@@ -10517,7 +10505,7 @@
       <c r="H236" s="5" t="n"/>
       <c r="I236" s="5" t="inlineStr">
         <is>
-          <t>9a559291c36be0ac35a9db4682d18acc6ccff2d3</t>
+          <t>0a06adbce02a4f5db3b3f08f23394e3acfc9a573</t>
         </is>
       </c>
     </row>
@@ -10527,7 +10515,7 @@
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>ICON: Indirect Prompt Injection Defense for Agents based on Inference-Time Correction</t>
+          <t>Rethinking All Evidence: Enhancing Trustworthy Retrieval-Augmented Generation via Conflict-Driven Summarization</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
@@ -10542,7 +10530,7 @@
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F237" s="5" t="n"/>
@@ -10550,7 +10538,7 @@
       <c r="H237" s="5" t="n"/>
       <c r="I237" s="5" t="inlineStr">
         <is>
-          <t>9a559291c36be0ac35a9db4682d18acc6ccff2d3</t>
+          <t>0a06adbce02a4f5db3b3f08f23394e3acfc9a573</t>
         </is>
       </c>
     </row>
@@ -10560,7 +10548,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>ICON: Indirect Prompt Injection Defense for Agents based on Inference-Time Correction</t>
+          <t>Rethinking All Evidence: Enhancing Trustworthy Retrieval-Augmented Generation via Conflict-Driven Summarization</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -10583,7 +10571,7 @@
       <c r="H238" s="5" t="n"/>
       <c r="I238" s="5" t="inlineStr">
         <is>
-          <t>9a559291c36be0ac35a9db4682d18acc6ccff2d3</t>
+          <t>0a06adbce02a4f5db3b3f08f23394e3acfc9a573</t>
         </is>
       </c>
     </row>
@@ -10593,7 +10581,7 @@
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>ICON: Indirect Prompt Injection Defense for Agents based on Inference-Time Correction</t>
+          <t>Rethinking All Evidence: Enhancing Trustworthy Retrieval-Augmented Generation via Conflict-Driven Summarization</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
@@ -10616,7 +10604,7 @@
       <c r="H239" s="5" t="n"/>
       <c r="I239" s="5" t="inlineStr">
         <is>
-          <t>9a559291c36be0ac35a9db4682d18acc6ccff2d3</t>
+          <t>0a06adbce02a4f5db3b3f08f23394e3acfc9a573</t>
         </is>
       </c>
     </row>
@@ -10626,7 +10614,7 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>ICON: Indirect Prompt Injection Defense for Agents based on Inference-Time Correction</t>
+          <t>Rethinking All Evidence: Enhancing Trustworthy Retrieval-Augmented Generation via Conflict-Driven Summarization</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
@@ -10649,7 +10637,7 @@
       <c r="H240" s="5" t="n"/>
       <c r="I240" s="5" t="inlineStr">
         <is>
-          <t>9a559291c36be0ac35a9db4682d18acc6ccff2d3</t>
+          <t>0a06adbce02a4f5db3b3f08f23394e3acfc9a573</t>
         </is>
       </c>
     </row>
@@ -10659,7 +10647,7 @@
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>ICON: Indirect Prompt Injection Defense for Agents based on Inference-Time Correction</t>
+          <t>Rethinking All Evidence: Enhancing Trustworthy Retrieval-Augmented Generation via Conflict-Driven Summarization</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
@@ -10674,7 +10662,7 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>No code, dataset, or model release URL/statement (e.g., GitHub) is found in the extracted text; the Impact Statement discusses ethical implications but does not mention a public artifact release.</t>
+          <t>The paper states in its contributions that the authors 'distill and release a conflict detection model based on LLaMA-3.2-3B, capable of analyzing and identifying potential conflicts among input evidence'; no specific GitHub/HuggingFace URL for this model or for the repaired QA datasets is given in the extracted text.</t>
         </is>
       </c>
       <c r="F241" s="5" t="n"/>
@@ -10682,7 +10670,7 @@
       <c r="H241" s="5" t="n"/>
       <c r="I241" s="5" t="inlineStr">
         <is>
-          <t>9a559291c36be0ac35a9db4682d18acc6ccff2d3</t>
+          <t>0a06adbce02a4f5db3b3f08f23394e3acfc9a573</t>
         </is>
       </c>
     </row>
@@ -10692,7 +10680,7 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>ICON: Indirect Prompt Injection Defense for Agents based on Inference-Time Correction</t>
+          <t>Rethinking All Evidence: Enhancing Trustworthy Retrieval-Augmented Generation via Conflict-Driven Summarization</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
@@ -10707,7 +10695,7 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>Text-only agentic backbones: Qwen-3-8B, Llama-3.1-8B, and Mistral-8B. Multi-modal (vision-language) agentic backbones: Qwen3-VL, InternVL, and MiniCPM. Qwen3Guard and Gemini are used as fine-tuning-based defense upper bounds (LLM-Detector baseline).</t>
+          <t>Open-source backbones: Mistral-7B-v0.3, LLaMA-3.2-8B, and Qwen2.5-7B. Closed-source backbones: Claude-3.5-Haiku, Gemini-2.0-Flash, and GPT-4.1-Nano. A distilled LLaMA-3.2-3B model (trained from DeepSeek-V3-generated rationales) serves as the dedicated conflict-detection/summarization module used across all backbone configurations. A separate QA-repair validation experiment also reports improved F1 for Qwen3-235B-A22B.</t>
         </is>
       </c>
       <c r="F242" s="5" t="n"/>
@@ -10715,7 +10703,7 @@
       <c r="H242" s="5" t="n"/>
       <c r="I242" s="5" t="inlineStr">
         <is>
-          <t>9a559291c36be0ac35a9db4682d18acc6ccff2d3</t>
+          <t>0a06adbce02a4f5db3b3f08f23394e3acfc9a573</t>
         </is>
       </c>
     </row>
@@ -10725,7 +10713,7 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>ICON: Indirect Prompt Injection Defense for Agents based on Inference-Time Correction</t>
+          <t>Rethinking All Evidence: Enhancing Trustworthy Retrieval-Augmented Generation via Conflict-Driven Summarization</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
@@ -10740,7 +10728,7 @@
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>Evaluated on InjecAgent and AgentDojo (widely used IPI attack benchmarks) for text-only agents, with TrojanTools (adaptive indirect prompt injection via malicious tool-calling) used for training and out-of-distribution generalization testing. For multi-modal agents, evaluated on Visual Prompt Injection Benchmarks provided by Meta. Attack types include Ignore Instruction, Combined Attacks, and TrojanTools (adaptive).</t>
+          <t>Five QA benchmarks are used, each passed through the paper's own 'QA Repair' procedure to correct outdated/mismatched gold answers, yielding revised versions denoted NQ*, TriviaQA*, HotpotQA*, ASQA*, and WikiQA* (2WikiMultiHopQA): Natural Questions, TriviaQA, HotpotQA, ASQA, and 2WikiMultiHopQA/WikiQA, covering open-domain and multi-hop QA. Table 1 quantifies the prevalence of outdated/mismatched ground-truth annotations found across these datasets before repair.</t>
         </is>
       </c>
       <c r="F243" s="5" t="n"/>
@@ -10748,7 +10736,7 @@
       <c r="H243" s="5" t="n"/>
       <c r="I243" s="5" t="inlineStr">
         <is>
-          <t>9a559291c36be0ac35a9db4682d18acc6ccff2d3</t>
+          <t>0a06adbce02a4f5db3b3f08f23394e3acfc9a573</t>
         </is>
       </c>
     </row>
@@ -10758,7 +10746,7 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>ICON: Indirect Prompt Injection Defense for Agents based on Inference-Time Correction</t>
+          <t>Rethinking All Evidence: Enhancing Trustworthy Retrieval-Augmented Generation via Conflict-Driven Summarization</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
@@ -10773,7 +10761,7 @@
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>ICON achieves a competitive average Attack Success Rate (ASR) of 0.4%, comparable to the fine-tuned commercial-grade LLM-Detector (Qwen3Guard) baseline's 0.2% ASR, while delivering over 50% higher task Utility under Attack (UA) than that same detector baseline -- e.g., on Qwen-3-8B, ICON maintains 53.8% average UA vs. the next-best defense's sub-49% UA. Against the tool-filtering baseline MELON, ICON reduces ASR by an additional ~3% while providing a ~10% UA boost, since MELON cannot re-run reasoning after a filter trigger and thus loses utility. Template-based defenses (Repeat Prompt, Delimiting) show some effectiveness against basic Ignore Instruction attacks but struggle significantly against adaptive TrojanTools attacks. On out-of-distribution benchmarks (Table 3), ICON trained only on TrojanTools achieves an Attack Detection Rate (ADR) of 80.1% (Qwen-3-8B) to 98.0% (AgentDojo) and a Utility Recovery Rate (URR) of 47.6-69.6%, versus 0% for undefended models, demonstrating strong zero-shot transfer. On multi-modal agents (Table 5), ICON reduces ASR from 69.0% (no defense) to an average of 2.9% while maintaining substantially higher UA (47.2%) than the LLM-Detector baseline (28.8% UA at 0.0% ASR), showing the attention-steering mechanism generalizes to multi-modal attack structures. Efficiency analysis (Table 4) shows ICON requires less than 2 minutes of training on only 255 samples (31,553 parameters), versus Qwen3Guard's over 10 hours of training on 1.19M samples (8B parameters).</t>
+          <t>CARE-RAG achieves the highest EM/F1 across all five repaired benchmarks and all six model backbones, improving over standard RAG by up to 17.2 EM/17.1 F1 and beating the strongest prior baseline (InstructRAG) by an average of 3.8 EM and 3.7 F1. Concrete numbers: on NQ* with LLaMA-3.2-8B, CARE-RAG reaches 63.9/64.3 EM/F1 vs. 40.3/42.5 for plain RAG (a 23.6-point EM gain matching the abstract's headline claim) and 59.7/60.9 for InstructRAG; with Claude-3.5-Haiku, CARE-RAG reaches 68.8 EM on NQ* and 85.9 EM on TriviaQA* versus 51.9 and 78.7 for plain RAG respectively. The QA Repair step alone (independent of the CARE-RAG architecture) raises F1 from 85.09 to 86.17 for Qwen3-235B-A22B. An ablation (Table 4) shows all three CARE-RAG stages contribute: removing Stage 1 (parameter record comparison) or Stage 3 (conflict-driven summarization) causes moderate drops, while removing Stage 2 (retrieved-evidence refinement) causes the largest drop (e.g., LLaMA-3.2-8B NQ* EM falls from 63.9 to 39.9, near the No-RAG baseline), showing that structured refinement of external evidence is the single largest contributor. A retrieval-volume sensitivity study (K=5 to 25) shows CARE-RAG performance peaks around K=15-20 and then plateaus with minimal degradation, unlike simpler RAG baselines that degrade with noise accumulation.</t>
         </is>
       </c>
       <c r="F244" s="5" t="n"/>
@@ -10781,7 +10769,7 @@
       <c r="H244" s="5" t="n"/>
       <c r="I244" s="5" t="inlineStr">
         <is>
-          <t>9a559291c36be0ac35a9db4682d18acc6ccff2d3</t>
+          <t>0a06adbce02a4f5db3b3f08f23394e3acfc9a573</t>
         </is>
       </c>
     </row>
@@ -10791,7 +10779,7 @@
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>ICON: Indirect Prompt Injection Defense for Agents based on Inference-Time Correction</t>
+          <t>Rethinking All Evidence: Enhancing Trustworthy Retrieval-Augmented Generation via Conflict-Driven Summarization</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
@@ -10806,7 +10794,7 @@
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>Compared against three defense mechanism categories: template-based (Repeat Prompt, which reiterates system instructions; Delimiting, which uses special tokens to isolate untrusted content), filter-based (MELON, a state-of-the-art tool-filtering framework), and fine-tuning-based (Qwen3Guard and Gemini, used as an upper-bound reference for intrinsic model robustness via a dedicated external guardrail/LLM-Detector).</t>
+          <t>CARE-RAG is compared against No-RAG (parametric-only), standard RAG, InstructRAG, GenRead, and Self-RAG across all five datasets and six model backbones (Tables 3 and 5). An additional analysis (Figure 4) compares CARE-RAG against 'contextual-only,' 'parameter-only,' and a 'direct combination' of the two evidence sources to isolate the value of conflict-aware synthesis specifically.</t>
         </is>
       </c>
       <c r="F245" s="5" t="n"/>
@@ -10814,7 +10802,7 @@
       <c r="H245" s="5" t="n"/>
       <c r="I245" s="5" t="inlineStr">
         <is>
-          <t>9a559291c36be0ac35a9db4682d18acc6ccff2d3</t>
+          <t>0a06adbce02a4f5db3b3f08f23394e3acfc9a573</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10812,7 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>ICON: Indirect Prompt Injection Defense for Agents based on Inference-Time Correction</t>
+          <t>Rethinking All Evidence: Enhancing Trustworthy Retrieval-Augmented Generation via Conflict-Driven Summarization</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
@@ -10839,7 +10827,7 @@
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>Formal threat model for adaptive Indirect Prompt Injection (IPI) attacks: LLM agents integrate external data sources (emails, web pages, tool outputs) and, because LLMs fundamentally conflate instructions with data, malicious payloads embedded within this retrieved third-party content can hijack the agent's decision-making process, forcing it to execute unauthorized tool calls while bypassing traditional safety guardrails. The paper specifically targets 'adaptive' IPI attacks (e.g., TrojanTools) that are increasingly indistinguishable from benign task contexts, strategically exploiting subtle semantic boundaries between instructions and data to bypass static, surface-level-pattern-based defenses (template-based and filter-based methods) as well as intrinsic model alignment.</t>
+          <t>N/A - non-adversarial. This is a RAG reliability/trustworthiness paper, not a security paper, though it briefly notes relevance to 'adversarial or noisy retrieval settings' and cites graph-based single-node attacks as related risk. The incidental failure mode of interest is unresolved knowledge conflict: contradictions between an LLM's parametric knowledge and retrieved external evidence (and among multiple retrieved passages themselves), which standard RAG handles in a 'black-box manner' and which the paper argues causes factual inaccuracy and undermines generation trustworthiness.</t>
         </is>
       </c>
       <c r="F246" s="5" t="n"/>
@@ -10847,7 +10835,7 @@
       <c r="H246" s="5" t="n"/>
       <c r="I246" s="5" t="inlineStr">
         <is>
-          <t>9a559291c36be0ac35a9db4682d18acc6ccff2d3</t>
+          <t>0a06adbce02a4f5db3b3f08f23394e3acfc9a573</t>
         </is>
       </c>
     </row>
@@ -10857,7 +10845,7 @@
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>ICON: Indirect Prompt Injection Defense for Agents based on Inference-Time Correction</t>
+          <t>Rethinking All Evidence: Enhancing Trustworthy Retrieval-Augmented Generation via Conflict-Driven Summarization</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
@@ -10872,7 +10860,7 @@
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>The paper has no explicit 'Limitations' section; the closest analog is an 'Impact Statement' (in place of a limitations discussion) stating the work aims to advance AI security and agent robustness, that it helps mitigate risks of adversarial manipulation in LLMs, and that potential societal consequences 'mostly contribute to the safe and ethical deployment of AI, and none of which we feel must be specifically highlighted here beyond its contribution to general system reliability' -- i.e., the paper does not identify specific technical weaknesses or failure cases of ICON itself in a dedicated limitations discussion.</t>
+          <t>The paper has an explicit 'Limitations' section stating that CARE-RAG's multi-stage approach inherently incurs greater computational overhead than simpler RAG frameworks, potentially impacting inference efficiency, and that the method's performance -- particularly the conflict detection and resolution capability -- remains closely tied to the quality of the underlying language models and their fine-tuning, meaning gains may not transfer uniformly to weaker or differently-tuned backbones.</t>
         </is>
       </c>
       <c r="F247" s="5" t="n"/>
@@ -10880,7 +10868,7 @@
       <c r="H247" s="5" t="n"/>
       <c r="I247" s="5" t="inlineStr">
         <is>
-          <t>9a559291c36be0ac35a9db4682d18acc6ccff2d3</t>
+          <t>0a06adbce02a4f5db3b3f08f23394e3acfc9a573</t>
         </is>
       </c>
     </row>
@@ -10890,7 +10878,7 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>ICON: Indirect Prompt Injection Defense for Agents based on Inference-Time Correction</t>
+          <t>Rethinking All Evidence: Enhancing Trustworthy Retrieval-Augmented Generation via Conflict-Driven Summarization</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
@@ -10905,7 +10893,7 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>This paper introduces ICON (Inference-Time Correction), a probing-to-mitigation defense framework against adaptive Indirect Prompt Injection (IPI) attacks on LLM agents that neutralizes attacks while preserving task continuity, addressing the over-refusal problem of existing filtering/refusal-based defenses that prematurely terminate valid agentic workflows. ICON is grounded in an empirical insight: successful IPI attacks that trigger a specific adversarial intent induce abnormally concentrated ('over-focusing') attention on a small subset of injected tokens in the latent space, in contrast to benign trajectories that integrate long-horizon context more diffusely. The framework first computes a Focus Intensity Score (FIS) to quantify attention anomalies across critical layers and attention heads, identifying which layers/heads carry the most diagnostic signal. A Latent Space Trace Prober (LSTP) then serves as a lightweight detector, flagging trajectories with high-intensity attention signatures characteristic of an attack. Upon detection, rather than aborting the task (as refusal-vector-based interventions do), a Mitigating Rectifier (MR) performs surgical attention steering: it selectively suppresses the anomalous adversarial query-key dependencies while implicitly amplifying task-relevant context, steering the model's latent representation back toward its benign functional manifold and restoring the agent's original intent and execution trajectory. This inference-time correction approach requires no model retraining (only a lightweight probing/rectification component trained on a small synthesized dataset, TrojanTools, in under 2 minutes), and the paper demonstrates it transfers effectively across different backbone LLMs (Qwen, Llama, Mistral), out-of-distribution attack benchmarks (InjecAgent, AgentDojo), and multi-modal agentic backbones (Qwen3-VL, InternVL, MiniCPM) without per-model or per-benchmark retraining.</t>
+          <t>CARE-RAG (Conflict-Aware and Reliable Evidence for RAG) is a four-stage framework designed to make RAG systems more trustworthy by having the LLM systematically 'rethink all evidence' -- both its own parametric knowledge and retrieved external content -- rather than synthesizing an answer directly from retrieved passages in a black-box manner. Stage 1 (parameter-aware evidence) generates diverse internal viewpoints by prompting the model with its own previously generated parametric answers and asking it to produce alternative perspectives, surfacing latent internal inconsistencies/hallucination candidates. Stage 2 (context-aware evidence) refines the top-K retrieved passages by removing irrelevant or redundant content, producing denser, more relevant external evidence while reducing token usage. Stage 3 (conflict-driven summarization) uses a dedicated conflict-detection module -- a LLaMA-3.2-3B model distilled from DeepSeek-V3-generated conflict-assessment rationales -- to cross-check all parameter-aware and context-aware evidence pairwise, identify contradictions, and produce a structured conflict report that is passed to the generator LLM alongside the raw evidence to guide final answer synthesis (Stage 4). To address evaluation-integrity confounds from outdated or ambiguous gold answers in standard QA benchmarks (e.g., a benchmark's reference answer becoming stale as facts change over time), the paper additionally introduces a lightweight 'QA Repair' preprocessing procedure, applied once before training/evaluation and used consistently across all five benchmarks, that corrects such mismatched ground-truth answers and is shown to independently improve measured performance even without the CARE-RAG architecture.</t>
         </is>
       </c>
       <c r="F248" s="5" t="n"/>
@@ -10913,7 +10901,7 @@
       <c r="H248" s="5" t="n"/>
       <c r="I248" s="5" t="inlineStr">
         <is>
-          <t>9a559291c36be0ac35a9db4682d18acc6ccff2d3</t>
+          <t>0a06adbce02a4f5db3b3f08f23394e3acfc9a573</t>
         </is>
       </c>
     </row>
@@ -10923,7 +10911,7 @@
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>Research on Security Enhancement Methods for Adversarial Robust Large Language Model Intelligent Agents for Medical Decision-Making Tasks</t>
+          <t>PISanitizer: Preventing Prompt Injection to Long-Context LLMs via Prompt Sanitization</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
@@ -10946,7 +10934,7 @@
       <c r="H249" s="5" t="n"/>
       <c r="I249" s="5" t="inlineStr">
         <is>
-          <t>59f623857e6d89dc1d0f2ca4cb433f0017b768db</t>
+          <t>177137fd3d07855a6fa2e0bdcee3606d0159fa3d</t>
         </is>
       </c>
     </row>
@@ -10956,7 +10944,7 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>Research on Security Enhancement Methods for Adversarial Robust Large Language Model Intelligent Agents for Medical Decision-Making Tasks</t>
+          <t>PISanitizer: Preventing Prompt Injection to Long-Context LLMs via Prompt Sanitization</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
@@ -10979,7 +10967,7 @@
       <c r="H250" s="5" t="n"/>
       <c r="I250" s="5" t="inlineStr">
         <is>
-          <t>59f623857e6d89dc1d0f2ca4cb433f0017b768db</t>
+          <t>177137fd3d07855a6fa2e0bdcee3606d0159fa3d</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10977,7 @@
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>Research on Security Enhancement Methods for Adversarial Robust Large Language Model Intelligent Agents for Medical Decision-Making Tasks</t>
+          <t>PISanitizer: Preventing Prompt Injection to Long-Context LLMs via Prompt Sanitization</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
@@ -11012,7 +11000,7 @@
       <c r="H251" s="5" t="n"/>
       <c r="I251" s="5" t="inlineStr">
         <is>
-          <t>59f623857e6d89dc1d0f2ca4cb433f0017b768db</t>
+          <t>177137fd3d07855a6fa2e0bdcee3606d0159fa3d</t>
         </is>
       </c>
     </row>
@@ -11022,7 +11010,7 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>Research on Security Enhancement Methods for Adversarial Robust Large Language Model Intelligent Agents for Medical Decision-Making Tasks</t>
+          <t>PISanitizer: Preventing Prompt Injection to Long-Context LLMs via Prompt Sanitization</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
@@ -11045,7 +11033,7 @@
       <c r="H252" s="5" t="n"/>
       <c r="I252" s="5" t="inlineStr">
         <is>
-          <t>59f623857e6d89dc1d0f2ca4cb433f0017b768db</t>
+          <t>177137fd3d07855a6fa2e0bdcee3606d0159fa3d</t>
         </is>
       </c>
     </row>
@@ -11055,7 +11043,7 @@
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>Research on Security Enhancement Methods for Adversarial Robust Large Language Model Intelligent Agents for Medical Decision-Making Tasks</t>
+          <t>PISanitizer: Preventing Prompt Injection to Long-Context LLMs via Prompt Sanitization</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
@@ -11078,7 +11066,7 @@
       <c r="H253" s="5" t="n"/>
       <c r="I253" s="5" t="inlineStr">
         <is>
-          <t>59f623857e6d89dc1d0f2ca4cb433f0017b768db</t>
+          <t>177137fd3d07855a6fa2e0bdcee3606d0159fa3d</t>
         </is>
       </c>
     </row>
@@ -11088,7 +11076,7 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>Research on Security Enhancement Methods for Adversarial Robust Large Language Model Intelligent Agents for Medical Decision-Making Tasks</t>
+          <t>PISanitizer: Preventing Prompt Injection to Long-Context LLMs via Prompt Sanitization</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
@@ -11111,7 +11099,7 @@
       <c r="H254" s="5" t="n"/>
       <c r="I254" s="5" t="inlineStr">
         <is>
-          <t>59f623857e6d89dc1d0f2ca4cb433f0017b768db</t>
+          <t>177137fd3d07855a6fa2e0bdcee3606d0159fa3d</t>
         </is>
       </c>
     </row>
@@ -11121,7 +11109,7 @@
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>Research on Security Enhancement Methods for Adversarial Robust Large Language Model Intelligent Agents for Medical Decision-Making Tasks</t>
+          <t>PISanitizer: Preventing Prompt Injection to Long-Context LLMs via Prompt Sanitization</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
@@ -11144,7 +11132,7 @@
       <c r="H255" s="5" t="n"/>
       <c r="I255" s="5" t="inlineStr">
         <is>
-          <t>59f623857e6d89dc1d0f2ca4cb433f0017b768db</t>
+          <t>177137fd3d07855a6fa2e0bdcee3606d0159fa3d</t>
         </is>
       </c>
     </row>
@@ -11154,7 +11142,7 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>Research on Security Enhancement Methods for Adversarial Robust Large Language Model Intelligent Agents for Medical Decision-Making Tasks</t>
+          <t>PISanitizer: Preventing Prompt Injection to Long-Context LLMs via Prompt Sanitization</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
@@ -11177,7 +11165,7 @@
       <c r="H256" s="5" t="n"/>
       <c r="I256" s="5" t="inlineStr">
         <is>
-          <t>59f623857e6d89dc1d0f2ca4cb433f0017b768db</t>
+          <t>177137fd3d07855a6fa2e0bdcee3606d0159fa3d</t>
         </is>
       </c>
     </row>
@@ -11187,7 +11175,7 @@
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>Research on Security Enhancement Methods for Adversarial Robust Large Language Model Intelligent Agents for Medical Decision-Making Tasks</t>
+          <t>PISanitizer: Preventing Prompt Injection to Long-Context LLMs via Prompt Sanitization</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
@@ -11202,7 +11190,7 @@
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>execution</t>
+          <t>ingestion</t>
         </is>
       </c>
       <c r="F257" s="5" t="n"/>
@@ -11210,7 +11198,7 @@
       <c r="H257" s="5" t="n"/>
       <c r="I257" s="5" t="inlineStr">
         <is>
-          <t>59f623857e6d89dc1d0f2ca4cb433f0017b768db</t>
+          <t>177137fd3d07855a6fa2e0bdcee3606d0159fa3d</t>
         </is>
       </c>
     </row>
@@ -11220,7 +11208,7 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>Research on Security Enhancement Methods for Adversarial Robust Large Language Model Intelligent Agents for Medical Decision-Making Tasks</t>
+          <t>PISanitizer: Preventing Prompt Injection to Long-Context LLMs via Prompt Sanitization</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
@@ -11243,7 +11231,7 @@
       <c r="H258" s="5" t="n"/>
       <c r="I258" s="5" t="inlineStr">
         <is>
-          <t>59f623857e6d89dc1d0f2ca4cb433f0017b768db</t>
+          <t>177137fd3d07855a6fa2e0bdcee3606d0159fa3d</t>
         </is>
       </c>
     </row>
@@ -11253,7 +11241,7 @@
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>Research on Security Enhancement Methods for Adversarial Robust Large Language Model Intelligent Agents for Medical Decision-Making Tasks</t>
+          <t>PISanitizer: Preventing Prompt Injection to Long-Context LLMs via Prompt Sanitization</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
@@ -11276,7 +11264,7 @@
       <c r="H259" s="5" t="n"/>
       <c r="I259" s="5" t="inlineStr">
         <is>
-          <t>59f623857e6d89dc1d0f2ca4cb433f0017b768db</t>
+          <t>177137fd3d07855a6fa2e0bdcee3606d0159fa3d</t>
         </is>
       </c>
     </row>
@@ -11286,7 +11274,7 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>Research on Security Enhancement Methods for Adversarial Robust Large Language Model Intelligent Agents for Medical Decision-Making Tasks</t>
+          <t>PISanitizer: Preventing Prompt Injection to Long-Context LLMs via Prompt Sanitization</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
@@ -11301,7 +11289,7 @@
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>No code, model weights, or dataset release is mentioned anywhere in the paper. The 10,000-sample dataset (7,000 train / 1,500 validation / 1,000 test) is described as built from public medical datasets (referred to as "China Med" and "Moda") plus manual labeling, but no repository link, license, or public access mechanism is provided.</t>
+          <t>The code is publicly released at https://github.com/sleeepeer/PISanitizer. No new model checkpoints are released; PISanitizer uses an off-the-shelf open-source LLM (e.g., Llama-3.1-8B-Instruct) as its sanitizer without any fine-tuning, and the paper does not introduce a new benchmark dataset (it repurposes existing LongBench, Open-Prompt-Injection, and AgentDojo benchmarks).</t>
         </is>
       </c>
       <c r="F260" s="5" t="n"/>
@@ -11309,7 +11297,7 @@
       <c r="H260" s="5" t="n"/>
       <c r="I260" s="5" t="inlineStr">
         <is>
-          <t>59f623857e6d89dc1d0f2ca4cb433f0017b768db</t>
+          <t>177137fd3d07855a6fa2e0bdcee3606d0159fa3d</t>
         </is>
       </c>
     </row>
@@ -11319,7 +11307,7 @@
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>Research on Security Enhancement Methods for Adversarial Robust Large Language Model Intelligent Agents for Medical Decision-Making Tasks</t>
+          <t>PISanitizer: Preventing Prompt Injection to Long-Context LLMs via Prompt Sanitization</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
@@ -11334,7 +11322,7 @@
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>The paper does not name specific underlying LLM backbones (e.g., GPT-4, Llama) for any of the compared agents. Instead it compares five agent-level systems: the proposed ARSM-Agent, LLM-Agent (a plain baseline), Retrieval-Agent, Filter-Agent, and Adv-Train-Agent (adversarial-training baseline), all evaluated on the same underlying (unspecified) medical-decision task pipeline.</t>
+          <t>As backend (victim) LLMs: 3 open-source models (Llama-3.1-8B-Instruct, Llama-3.1-70B-Instruct, Qwen3-Omni-30B-A3B-Instruct) and 4 closed-source models (GPT-4o, GPT-4o-mini, GPT-4.1, GPT-5), with GPT-4o-mini noted as specifically trained by OpenAI with an instruction hierarchy for prompt-injection resistance. Llama-3.1-8B-Instruct is used by default as both the default backend LLM and as PISanitizer's own sanitization LLM (chosen because it is open-source and thus exposes attention weights, which PISanitizer's mechanism requires).</t>
         </is>
       </c>
       <c r="F261" s="5" t="n"/>
@@ -11342,7 +11330,7 @@
       <c r="H261" s="5" t="n"/>
       <c r="I261" s="5" t="inlineStr">
         <is>
-          <t>59f623857e6d89dc1d0f2ca4cb433f0017b768db</t>
+          <t>177137fd3d07855a6fa2e0bdcee3606d0159fa3d</t>
         </is>
       </c>
     </row>
@@ -11352,7 +11340,7 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>Research on Security Enhancement Methods for Adversarial Robust Large Language Model Intelligent Agents for Medical Decision-Making Tasks</t>
+          <t>PISanitizer: Preventing Prompt Injection to Long-Context LLMs via Prompt Sanitization</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
@@ -11367,7 +11355,7 @@
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>A self-constructed 10,000-sample dataset (7,000 train / 1,500 validation / 1,000 test) built from public medical datasets ("China Med" and "Moda") plus manual labeling, submitted to Clinical Practice Guidelines. Three task types are evaluated: symptom triage, treatment-suggestion, and medication-risk question answering. Adversarial subsets were constructed as fixed proportions of the test set: semantic-perturbation samples (20%, synonym rewriting/word-order adjustment), prompt-injection samples (20%, malicious misleading instructions), drug-name-obfuscation samples (20%, similar drug names), false-evidence-splicing samples (20%, fabricated medical evidence), and normal samples (remaining 20%).</t>
+          <t>Primary evaluation uses 6 datasets drawn from the LongBench benchmark (4,000-20,000 token contexts, 100 randomly sampled examples per dataset): Qasper and HotpotQA (question answering), GovReport and MultiNews (summarization), LCC (code generation), and PassageRetrieval (information retrieval), with HotpotQA as the default. Supplementary experiments use the Open-Prompt-Injection benchmark (to test injected-data rather than injected-instruction attacks) and AgentDojo (a tool-use/agent prompt-injection benchmark, used to test PISanitizer's handling of benign in-context instructions like tool-call results). Four injected-task types are evaluated: target answer generation, hacked generation ('Hacked!'), classic NLP tasks (e.g., sentiment analysis), and general instructions.</t>
         </is>
       </c>
       <c r="F262" s="5" t="n"/>
@@ -11375,7 +11363,7 @@
       <c r="H262" s="5" t="n"/>
       <c r="I262" s="5" t="inlineStr">
         <is>
-          <t>59f623857e6d89dc1d0f2ca4cb433f0017b768db</t>
+          <t>177137fd3d07855a6fa2e0bdcee3606d0159fa3d</t>
         </is>
       </c>
     </row>
@@ -11385,7 +11373,7 @@
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>Research on Security Enhancement Methods for Adversarial Robust Large Language Model Intelligent Agents for Medical Decision-Making Tasks</t>
+          <t>PISanitizer: Preventing Prompt Injection to Long-Context LLMs via Prompt Sanitization</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
@@ -11400,7 +11388,7 @@
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>ARSM-Agent achieved 92.3% accuracy and 91.8% F1 on the test set, outperforming all four baselines (LLM-Agent: 76.6%/76.9%, Retrieval-Agent: 85.1%/85.0%, Filter-Agent: 83.8%/83.9%, Adv-Train-Agent: 86.0%/86.0%). Under combined adversarial conditions (semantic perturbation, prompt injection, drug-name confusion, false-evidence attacks), ARSM-Agent reduced overall attack success rate to 8.7% (vs. 42.1% for LLM-Agent, 27.5% for Retrieval-Agent, 25.3% for Filter-Agent, 18.9% for Adv-Train-Agent), while achieving a 12.3% safe-rejection rate, 2.1% hallucination rate, 0.91 knowledge-consistency score, and 186ms average decision latency. Per-attack-type breakdown showed ARSM-Agent's lowest attack success rates were 6.2% (semantic perturbation), 9.5% (prompt injection), 7.8% (drug-name confusion), and 11.3% (false evidence) -- all substantially below comparison models, with LLM-Agent showing no effective defense against prompt injection specifically. Ablation experiments quantified each module's contribution: removing risk perception, evidence retrieval, consistency verification, and confidence reweighting reduced accuracy by 6.7%, 9.1%, 7.6%, and 4.4% respectively, and increased attack success rate by 13.8%, 11.1%, 8.6%, and 6.9% respectively. Parameter sensitivity analysis found optimal performance at risk threshold 0.5-0.6, evidence-retrieval depth m between 3-5, and adversarial-sample ratio 30%.</t>
+          <t>Across all 6 LongBench datasets and 6 attack types (Naive, Escape Character, Context Ignoring, Fake Completion, Combined Attack, and GCG/nano-GCG optimization-based attack), PISanitizer reduces attack success rate (ASR) to near 0 (mostly 0.0, with a handful of small residual values up to 0.04) while restoring utility to within a few points of the no-attack baseline -- e.g., on HotpotQA, Combined Attack drops utility from 0.59 (clean) to 0.24 (attacked, no defense) with 0.66 ASR, but PISanitizer restores utility to 0.59 with ASR of only 0.01. PISanitizer generalizes across all 7 evaluated backend LLMs (3 open-source, 4 closed-source including GPT-5) under Combined Attack, and is shown to outperform state-of-the-art baselines including Meta-SecAlign, which the authors show remains vulnerable to optimization-based (GCG) attacks and additionally suffers utility loss on certain tasks and cannot be applied to closed-source LLMs like GPT-5/Gemini. Detection-based baselines (DataSentinel, PromptGuard, AttentionTracker) and attribution-based baselines (PromptArmor, PromptLocate, AttnTrace combined with detectors) are shown to be substantially less accurate at detecting/localizing injections in long contexts than in the short-context settings they were designed for. PISanitizer is also shown effective and near-utility-preserving in the short-context and LLM-agent (AgentDojo) settings, robust to adaptive attacks explicitly optimized against its attention-based detection mechanism (Table 10), and efficient, taking approximately 1.8 seconds to sanitize a context with thousands of tokens on a 96GB H100 GPU.</t>
         </is>
       </c>
       <c r="F263" s="5" t="n"/>
@@ -11408,7 +11396,7 @@
       <c r="H263" s="5" t="n"/>
       <c r="I263" s="5" t="inlineStr">
         <is>
-          <t>59f623857e6d89dc1d0f2ca4cb433f0017b768db</t>
+          <t>177137fd3d07855a6fa2e0bdcee3606d0159fa3d</t>
         </is>
       </c>
     </row>
@@ -11418,7 +11406,7 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>Research on Security Enhancement Methods for Adversarial Robust Large Language Model Intelligent Agents for Medical Decision-Making Tasks</t>
+          <t>PISanitizer: Preventing Prompt Injection to Long-Context LLMs via Prompt Sanitization</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
@@ -11433,7 +11421,7 @@
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>Four baseline agent architectures: LLM-Agent (plain large language model agent with no defensive modules), Retrieval-Agent (evidence-retrieval-only), Filter-Agent (input/output filtering only), and Adv-Train-Agent (adversarial-training-only defense), all compared against the proposed multi-module ARSM-Agent on the same three medical-decision tasks and four adversarial attack types.</t>
+          <t>Prevention-based: Sandwich prevention, Instructional prevention, Meta-SecAlign (state-of-the-art fine-tuning defense, improved over StruQ/SecAlign which are excluded as strictly dominated), and DataFilter (a concurrent sequence-to-sequence filtering model, noted as primarily designed for short contexts). Detection-based: DataSentinel (state-of-the-art detection method, formulates detection as a minimax game), PromptGuard (Meta's released detector), and AttentionTracker. Detection-plus-attribution-based: PromptArmor (GPT-4o-based detection/removal, reimplemented by the authors since no public implementation exists) and PromptLocate (integrates DataSentinel for localization), plus AttnTrace (a generic attribution method) combined with state-of-the-art detectors to remove flagged text.</t>
         </is>
       </c>
       <c r="F264" s="5" t="n"/>
@@ -11441,7 +11429,7 @@
       <c r="H264" s="5" t="n"/>
       <c r="I264" s="5" t="inlineStr">
         <is>
-          <t>59f623857e6d89dc1d0f2ca4cb433f0017b768db</t>
+          <t>177137fd3d07855a6fa2e0bdcee3606d0159fa3d</t>
         </is>
       </c>
     </row>
@@ -11451,7 +11439,7 @@
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>Research on Security Enhancement Methods for Adversarial Robust Large Language Model Intelligent Agents for Medical Decision-Making Tasks</t>
+          <t>PISanitizer: Preventing Prompt Injection to Long-Context LLMs via Prompt Sanitization</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
@@ -11466,7 +11454,7 @@
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>Formal adversarial setting for a medical decision-making LLM agent, covering four attack types explicitly constructed and tested: (1) semantic perturbation (synonym rewriting, word-order changes, and local input perturbations designed to evade meaning-preserving detection), (2) prompt injection (malicious instructions inserted into input attempting to divert the model from its medical decision-making objective), (3) drug-name confusion/obfuscation (substitution with similar-sounding or visually similar drug names to induce medication errors), and (4) false-evidence/pseudo-medical-evidence splicing attacks (fabricated medical evidence combined with legitimate input to corrupt the model's reasoning). The attacker's goal in each case is to cause the agent to produce a decision result that deviates from correct clinical logic, potentially endangering patient safety, quantified via an "attack success rate" metric across all four scenario types.</t>
+          <t>The attacker's goal is to inject a malicious instruction into a long target context so that the backend LLM follows the injected instruction rather than the target instruction, enabling purposes such as manipulating RAG-system answers, forcing a positive paper review, skewing a review summary, or generating malicious code in AI-assisted coding. The paper adopts a strong (white-box) attacker: full access to the backend LLM's parameters and system prompt, full visibility into the entire target context and knowledge of the target instruction, and the ability to arbitrarily place the injected instruction anywhere in the context (beginning, middle, or end) -- the authors explicitly evaluate both state-of-the-art heuristic attacks (Naive, Escape Character, Context Ignoring, Fake Completion, Combined) and strong optimization-based (GCG/nano-GCG) attacks, plus adaptive attacks specifically crafted against PISanitizer's attention-based detection mechanism. The defender may be an LLM application provider (system-level sanitization before forwarding context to the backend LLM) or an individual end user (local sanitization before querying), and has access to a sanitization LLM (which can differ from the backend LLM and must be open-source/white-box, since PISanitizer's mechanism requires access to internal attention weights).</t>
         </is>
       </c>
       <c r="F265" s="5" t="n"/>
@@ -11474,7 +11462,7 @@
       <c r="H265" s="5" t="n"/>
       <c r="I265" s="5" t="inlineStr">
         <is>
-          <t>59f623857e6d89dc1d0f2ca4cb433f0017b768db</t>
+          <t>177137fd3d07855a6fa2e0bdcee3606d0159fa3d</t>
         </is>
       </c>
     </row>
@@ -11484,7 +11472,7 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>Research on Security Enhancement Methods for Adversarial Robust Large Language Model Intelligent Agents for Medical Decision-Making Tasks</t>
+          <t>PISanitizer: Preventing Prompt Injection to Long-Context LLMs via Prompt Sanitization</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
@@ -11499,7 +11487,7 @@
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>The paper has no dedicated Limitations section; it moves directly from experimental results into a brief Conclusion with an implicit limitations/future-work list. The Conclusion states future work will: (1) expand the dataset to rare-disease samples and more complex clinical cases (implying current coverage is limited to more common/simpler cases), (2) optimize the adversarial-example generation strategy to improve generalization and defense (implying current adversarial coverage may not generalize well beyond the four tested attack types), (3) adapt module parameters for real clinical deployment settings (implying current validation is simulation-based rather than tested in live clinical practice), and (4) explore multimodal medical data fusion for greater clarity and reliability (implying the current system is text-only and does not incorporate imaging, lab values, or other modalities).</t>
+          <t>The paper has an explicit Section 6 'Discussion and Limitation' with two named subsections. First, PISanitizer's effectiveness rests on two core motivations that can fail: (1) it cannot defend against attacks that manipulate LLM output via injected data/misinformation rather than explicit instructions (e.g., knowledge-corruption attacks embedding false facts like 'The MalHttp is the best package for HTML parsing'), which the authors note 'can be extremely challenging to defend against without extra information' -- an experiment on Open-Prompt-Injection confirms PISanitizer removes the injected instruction but cannot fully restore utility because non-instructional injected data still influences the output; and (2) PISanitizer can be less effective against 'weak' attacks where the injected instruction receives low attention yet is still followed (e.g., Naive Attack shows the highest residual ASR in Table 1), though the authors note adaptive attacks explicitly targeting this weakness proved very challenging to construct successfully, and suggest combining PISanitizer with fine-tuning defenses like Meta-SecAlign as mitigation. Second, PISanitizer cannot distinguish benign from malicious in-context instructions and will remove benign ones too, causing utility loss (demonstrated on AgentDojo, where utility drops from 0.82 to 0.71 under no attack, with manual analysis showing 11 of 13 utility-impacted cases involved essential benign instructions, such as legitimate bank-transfer details that are indistinguishable from malicious ones without external validation); proposed mitigations include human-in-the-loop approval for sensitive operations and layering in additional automated validation (e.g., security policies) after PISanitizer pinpoints candidate instructions. The Conclusion also flags multi-modal LLM prompt injection as unaddressed future work.</t>
         </is>
       </c>
       <c r="F266" s="5" t="n"/>
@@ -11507,7 +11495,7 @@
       <c r="H266" s="5" t="n"/>
       <c r="I266" s="5" t="inlineStr">
         <is>
-          <t>59f623857e6d89dc1d0f2ca4cb433f0017b768db</t>
+          <t>177137fd3d07855a6fa2e0bdcee3606d0159fa3d</t>
         </is>
       </c>
     </row>
@@ -11517,7 +11505,7 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>Research on Security Enhancement Methods for Adversarial Robust Large Language Model Intelligent Agents for Medical Decision-Making Tasks</t>
+          <t>PISanitizer: Preventing Prompt Injection to Long-Context LLMs via Prompt Sanitization</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
@@ -11532,7 +11520,7 @@
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>This paper proposes ARSM-Agent, a full-pipeline security-enhancement framework for adversarially robust medical decision-making LLM agents, structured as a closed-loop chain of six collaborating modules: input risk perception, medical evidence constraint retrieval, knowledge consistency verification, decision confidence reweighting, secure output control, and adversarial feedback update. The framework optimizes a weighted joint objective combining decision-accuracy loss, adversarial-robustness loss (KL divergence between clean and adversarial output distributions), safety-refusal loss, and knowledge-consistency loss (weights 0.3/0.3/0.2/0.2). The risk-aware adversarial encoding module computes a semantic-perturbation risk score (via cosine similarity to a standard query, amplified by a perturbation-strength coefficient) and a separate prompt-injection risk score (combining abnormal-instruction frequency, role-modification degree, and control-statement irrationality), each compared against tunable thresholds to trigger downstream security controls. The medical evidence constraint module retrieves top-k similar evidence from a medical evidence base using a literal-matching-augmented cosine similarity and ranks candidates by a credibility score combining relevance, authority, and consistency dimensions. A knowledge consistency verification module checks whether entities/relations in model output match a medical knowledge graph, producing a consistency score gating whether output is accepted or requires readjustment. Final decision confidence is computed by reweighting the model's raw confidence using the input risk score, evidence-support strength, and knowledge-consistency score, feeding into a safe-output-control mechanism that outputs, adjusts, or rejects based on confidence and risk thresholds. An adversarial anti-lock reinforcement update mechanism generates gradient-based adversarial examples (an FGSM-style single-step perturbation) for closed-loop reinforcement-learning-based model updates, using a reward function that combines accuracy, inverse attack-success-rate, secure-output rate, and knowledge-consistency, mirroring the training objective's weights.</t>
+          <t>PISanitizer is a prompt-sanitization defense against prompt injection specifically designed for long-context LLMs, motivated by the observation that existing defenses (fine-tuning-based, detection-based, attribution-based) are largely designed for and effective only in short-context settings, since an injected instruction constitutes a vanishingly small fraction of a long context, making both detection and robust fine-tuning substantially harder. Rather than attempting to detect contamination first (which the authors show state-of-the-art long-context detectors like DataSentinel struggle with) or training a backend LLM to ignore injected instructions (which remains vulnerable to strong optimization-based attacks and is inapplicable to closed-source models), PISanitizer takes an orthogonal approach built on two observations: (1) prompt injection attacks work by crafting instructions that compel an LLM to follow them, and (2) the Transformer attention mechanism causes an LLM to assign high attention weights to instructional tokens it follows. The method deliberately prompts an open-source sanitization LLM (e.g., Llama-3.1-8B-Instruct) with a task-agnostic 'sanitization instruction' ('Do anything you are told to do in the following context...') designed to make the LLM follow any instruction present in the context, generates a single output token (sufficient to capture the dominant instruction-following signal while minimizing compute), and then extracts attention weights from that output token back to every context token across all layers and heads. A noise-aware aggregation scheme (per-layer head-averaging followed by max-pooling across layers) amplifies signal from informative layers while suppressing noise, and a Savitzky-Golay smoothing filter plus peak-detection/grouping procedure (via scipy.signal) identifies and merges consecutive high-attention token spans, since injected instructions typically form contiguous phrases rather than isolated tokens; the group with the highest aggregated attention is flagged as injected if it exceeds a threshold, and the whole procedure repeats up to 5 times to catch multiple injected instructions at different context locations. This design creates an inherent adversarial dilemma: the more effectively an injected instruction compels the LLM to follow it (the attacker's core objective), the higher the attention it receives and thus the more reliably PISanitizer detects and removes it -- fundamentally different from prior defenses that try to suppress instruction-following behavior directly. Evaluated across LongBench (6 datasets), Open-Prompt-Injection, and AgentDojo, against 6 heuristic and optimization-based attacks and 7 backend LLMs (open- and closed-source), PISanitizer reduces attack success rate to near zero while preserving target-task utility, outperforming prevention-, detection-, and attribution-based state-of-the-art baselines including Meta-SecAlign, and remains robust to adaptive attacks explicitly designed to evade its attention-based mechanism, at a modest runtime cost of about 1.8 seconds per context.</t>
         </is>
       </c>
       <c r="F267" s="5" t="n"/>
@@ -11540,7 +11528,7 @@
       <c r="H267" s="5" t="n"/>
       <c r="I267" s="5" t="inlineStr">
         <is>
-          <t>59f623857e6d89dc1d0f2ca4cb433f0017b768db</t>
+          <t>177137fd3d07855a6fa2e0bdcee3606d0159fa3d</t>
         </is>
       </c>
     </row>
@@ -11550,7 +11538,7 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>ESLD (External Surrogate Latent Defense): A Latent-Space Architecture for Faster, Stronger Prompt-Injection Defense</t>
+          <t>CASCADE: A Cascaded Hybrid Defense Architecture for Prompt Injection Detection in MCP-Based Systems</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
@@ -11573,7 +11561,7 @@
       <c r="H268" s="5" t="n"/>
       <c r="I268" s="5" t="inlineStr">
         <is>
-          <t>bd1a5abc01ecfeb7a4723c4cf46b0b37c27273fb</t>
+          <t>b874b9a07cc89ff9501f87daddb54c9fff48bfa8</t>
         </is>
       </c>
     </row>
@@ -11583,7 +11571,7 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>ESLD (External Surrogate Latent Defense): A Latent-Space Architecture for Faster, Stronger Prompt-Injection Defense</t>
+          <t>CASCADE: A Cascaded Hybrid Defense Architecture for Prompt Injection Detection in MCP-Based Systems</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
@@ -11606,7 +11594,7 @@
       <c r="H269" s="5" t="n"/>
       <c r="I269" s="5" t="inlineStr">
         <is>
-          <t>bd1a5abc01ecfeb7a4723c4cf46b0b37c27273fb</t>
+          <t>b874b9a07cc89ff9501f87daddb54c9fff48bfa8</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11604,7 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>ESLD (External Surrogate Latent Defense): A Latent-Space Architecture for Faster, Stronger Prompt-Injection Defense</t>
+          <t>CASCADE: A Cascaded Hybrid Defense Architecture for Prompt Injection Detection in MCP-Based Systems</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
@@ -11639,7 +11627,7 @@
       <c r="H270" s="5" t="n"/>
       <c r="I270" s="5" t="inlineStr">
         <is>
-          <t>bd1a5abc01ecfeb7a4723c4cf46b0b37c27273fb</t>
+          <t>b874b9a07cc89ff9501f87daddb54c9fff48bfa8</t>
         </is>
       </c>
     </row>
@@ -11649,7 +11637,7 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>ESLD (External Surrogate Latent Defense): A Latent-Space Architecture for Faster, Stronger Prompt-Injection Defense</t>
+          <t>CASCADE: A Cascaded Hybrid Defense Architecture for Prompt Injection Detection in MCP-Based Systems</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
@@ -11672,7 +11660,7 @@
       <c r="H271" s="5" t="n"/>
       <c r="I271" s="5" t="inlineStr">
         <is>
-          <t>bd1a5abc01ecfeb7a4723c4cf46b0b37c27273fb</t>
+          <t>b874b9a07cc89ff9501f87daddb54c9fff48bfa8</t>
         </is>
       </c>
     </row>
@@ -11682,7 +11670,7 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>ESLD (External Surrogate Latent Defense): A Latent-Space Architecture for Faster, Stronger Prompt-Injection Defense</t>
+          <t>CASCADE: A Cascaded Hybrid Defense Architecture for Prompt Injection Detection in MCP-Based Systems</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
@@ -11697,7 +11685,7 @@
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>tool-metadata</t>
         </is>
       </c>
       <c r="F272" s="5" t="n"/>
@@ -11705,7 +11693,7 @@
       <c r="H272" s="5" t="n"/>
       <c r="I272" s="5" t="inlineStr">
         <is>
-          <t>bd1a5abc01ecfeb7a4723c4cf46b0b37c27273fb</t>
+          <t>b874b9a07cc89ff9501f87daddb54c9fff48bfa8</t>
         </is>
       </c>
     </row>
@@ -11715,7 +11703,7 @@
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>ESLD (External Surrogate Latent Defense): A Latent-Space Architecture for Faster, Stronger Prompt-Injection Defense</t>
+          <t>CASCADE: A Cascaded Hybrid Defense Architecture for Prompt Injection Detection in MCP-Based Systems</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
@@ -11738,7 +11726,7 @@
       <c r="H273" s="5" t="n"/>
       <c r="I273" s="5" t="inlineStr">
         <is>
-          <t>bd1a5abc01ecfeb7a4723c4cf46b0b37c27273fb</t>
+          <t>b874b9a07cc89ff9501f87daddb54c9fff48bfa8</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11736,7 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>ESLD (External Surrogate Latent Defense): A Latent-Space Architecture for Faster, Stronger Prompt-Injection Defense</t>
+          <t>CASCADE: A Cascaded Hybrid Defense Architecture for Prompt Injection Detection in MCP-Based Systems</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
@@ -11771,7 +11759,7 @@
       <c r="H274" s="5" t="n"/>
       <c r="I274" s="5" t="inlineStr">
         <is>
-          <t>bd1a5abc01ecfeb7a4723c4cf46b0b37c27273fb</t>
+          <t>b874b9a07cc89ff9501f87daddb54c9fff48bfa8</t>
         </is>
       </c>
     </row>
@@ -11781,7 +11769,7 @@
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>ESLD (External Surrogate Latent Defense): A Latent-Space Architecture for Faster, Stronger Prompt-Injection Defense</t>
+          <t>CASCADE: A Cascaded Hybrid Defense Architecture for Prompt Injection Detection in MCP-Based Systems</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
@@ -11804,7 +11792,7 @@
       <c r="H275" s="5" t="n"/>
       <c r="I275" s="5" t="inlineStr">
         <is>
-          <t>bd1a5abc01ecfeb7a4723c4cf46b0b37c27273fb</t>
+          <t>b874b9a07cc89ff9501f87daddb54c9fff48bfa8</t>
         </is>
       </c>
     </row>
@@ -11814,7 +11802,7 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>ESLD (External Surrogate Latent Defense): A Latent-Space Architecture for Faster, Stronger Prompt-Injection Defense</t>
+          <t>CASCADE: A Cascaded Hybrid Defense Architecture for Prompt Injection Detection in MCP-Based Systems</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
@@ -11829,7 +11817,7 @@
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>reasoning</t>
+          <t>ingestion</t>
         </is>
       </c>
       <c r="F276" s="5" t="n"/>
@@ -11837,7 +11825,7 @@
       <c r="H276" s="5" t="n"/>
       <c r="I276" s="5" t="inlineStr">
         <is>
-          <t>bd1a5abc01ecfeb7a4723c4cf46b0b37c27273fb</t>
+          <t>b874b9a07cc89ff9501f87daddb54c9fff48bfa8</t>
         </is>
       </c>
     </row>
@@ -11847,7 +11835,7 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>ESLD (External Surrogate Latent Defense): A Latent-Space Architecture for Faster, Stronger Prompt-Injection Defense</t>
+          <t>CASCADE: A Cascaded Hybrid Defense Architecture for Prompt Injection Detection in MCP-Based Systems</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
@@ -11870,7 +11858,7 @@
       <c r="H277" s="5" t="n"/>
       <c r="I277" s="5" t="inlineStr">
         <is>
-          <t>bd1a5abc01ecfeb7a4723c4cf46b0b37c27273fb</t>
+          <t>b874b9a07cc89ff9501f87daddb54c9fff48bfa8</t>
         </is>
       </c>
     </row>
@@ -11880,7 +11868,7 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>ESLD (External Surrogate Latent Defense): A Latent-Space Architecture for Faster, Stronger Prompt-Injection Defense</t>
+          <t>CASCADE: A Cascaded Hybrid Defense Architecture for Prompt Injection Detection in MCP-Based Systems</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
@@ -11903,7 +11891,7 @@
       <c r="H278" s="5" t="n"/>
       <c r="I278" s="5" t="inlineStr">
         <is>
-          <t>bd1a5abc01ecfeb7a4723c4cf46b0b37c27273fb</t>
+          <t>b874b9a07cc89ff9501f87daddb54c9fff48bfa8</t>
         </is>
       </c>
     </row>
@@ -11913,7 +11901,7 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>ESLD (External Surrogate Latent Defense): A Latent-Space Architecture for Faster, Stronger Prompt-Injection Defense</t>
+          <t>CASCADE: A Cascaded Hybrid Defense Architecture for Prompt Injection Detection in MCP-Based Systems</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
@@ -11928,7 +11916,7 @@
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>No public code, model, or dataset release link found anywhere in the paper (checked main text and references for GitHub/HuggingFace/release statements; none present).</t>
+          <t>Y - pinned code revision, evaluation corpus (SHA-256 digest), reference set, per-sample decision records, runtime manifest and analysis scripts archived at Zenodo (DOI 10.5281/zenodo.22277939), code under MIT and data/docs under CC BY 4.0</t>
         </is>
       </c>
       <c r="F279" s="5" t="n"/>
@@ -11936,7 +11924,7 @@
       <c r="H279" s="5" t="n"/>
       <c r="I279" s="5" t="inlineStr">
         <is>
-          <t>bd1a5abc01ecfeb7a4723c4cf46b0b37c27273fb</t>
+          <t>b874b9a07cc89ff9501f87daddb54c9fff48bfa8</t>
         </is>
       </c>
     </row>
@@ -11946,7 +11934,7 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>ESLD (External Surrogate Latent Defense): A Latent-Space Architecture for Faster, Stronger Prompt-Injection Defense</t>
+          <t>CASCADE: A Cascaded Hybrid Defense Architecture for Prompt Injection Detection in MCP-Based Systems</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
@@ -11961,7 +11949,7 @@
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>Four open-weight guard LLMs used as ESLD's host models: LlamaGuard-3, ShieldGemma-9B, Granite-Guardian-8B, and WildGuard-7B. ESLD itself is a lightweight linear probe (Linear Discriminant Analysis with Ledoit-Wolf shrinkage) trained on frozen prefill-stage hidden states extracted from these hosts, not a separate LLM.</t>
+          <t>BGE embedding model (semantic layer); local Llama3 8B Q4_0 (optional review stage); regex/entropy-based rule layer (no LLM)</t>
         </is>
       </c>
       <c r="F280" s="5" t="n"/>
@@ -11969,7 +11957,7 @@
       <c r="H280" s="5" t="n"/>
       <c r="I280" s="5" t="inlineStr">
         <is>
-          <t>bd1a5abc01ecfeb7a4723c4cf46b0b37c27273fb</t>
+          <t>b874b9a07cc89ff9501f87daddb54c9fff48bfa8</t>
         </is>
       </c>
     </row>
@@ -11979,7 +11967,7 @@
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>ESLD (External Surrogate Latent Defense): A Latent-Space Architecture for Faster, Stronger Prompt-Injection Defense</t>
+          <t>CASCADE: A Cascaded Hybrid Defense Architecture for Prompt Injection Detection in MCP-Based Systems</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
@@ -11994,7 +11982,7 @@
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>10 UPIA (direct/user prompt injection) and 8 XPIA (indirect/cross-prompt injection) attack sources plus 4 benign sources, drawn from publicly released red-teaming datasets (leakage-audited for lexical/semantic overlap, Table 3), evaluated under a strict leave-one-source-out (LOSO) protocol so evaluation always uses data sources never seen during probe training.</t>
+          <t>A frozen, self-assembled 5,000-sample MCP-attack corpus drawn from multiple third-party collections (e.g., VulnerableMCP entries, GitHub adversarial commands, a prompt-injection dataset) plus template-generated/synthetic material; audited in full for provenance class, exact-duplicate rate (27.0% repeated text) and reference-set overlap</t>
         </is>
       </c>
       <c r="F281" s="5" t="n"/>
@@ -12002,7 +11990,7 @@
       <c r="H281" s="5" t="n"/>
       <c r="I281" s="5" t="inlineStr">
         <is>
-          <t>bd1a5abc01ecfeb7a4723c4cf46b0b37c27273fb</t>
+          <t>b874b9a07cc89ff9501f87daddb54c9fff48bfa8</t>
         </is>
       </c>
     </row>
@@ -12012,7 +12000,7 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>ESLD (External Surrogate Latent Defense): A Latent-Space Architecture for Faster, Stronger Prompt-Injection Defense</t>
+          <t>CASCADE: A Cascaded Hybrid Defense Architecture for Prompt Injection Detection in MCP-Based Systems</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
@@ -12027,7 +12015,7 @@
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>ESLD improves balanced accuracy (BAcc) over the host guard's own decoded verdict on 7 of 8 (host, task) cells, with a mean improvement of +16.4 percentage points, while achieving a geometric-mean wall-clock speedup of 3.29x over the full guard (per-cell range 2.35x-4.18x). The largest win is ShieldGemma-9B on XPIA (indirect): the host guard verdict is at chance (BAcc 0.50) while ESLD reaches 0.91 (+40.4pp) at 4.18x speedup, saving ~276ms per call (the largest absolute latency win, since ShieldGemma-9B is the slowest full guard at ~363ms/prompt). The only cell where ESLD trails is WildGuard-7B on UPIA (direct), where it loses by 2.6pp (though its underlying AUC of 0.88 remains strong) -- explained by WildGuard-7B being specifically fine-tuned for direct harmful-request detection on a closely related data mix, making this a narrow case rather than evidence against the latent signal. A consistent cross-host pattern emerges: XPIA (indirect) is far harder for host guards' decoded verdicts than UPIA (direct) -- host BAcc ranges 0.50-0.72 on XPIA vs. 0.72-0.83 on UPIA -- but ESLD closes this gap entirely, reaching 0.91-0.92 BAcc on XPIA across every host. Selected deployment layers fall between 50-80% of host network depth (via a Pareto-optimal shallowest-sufficient-layer selection rule), and the speedup advantage grows with host model size (largest for the largest host, ShieldGemma-9B), since the full guard's cost scales with model size while ESLD's cost scales only with prefill depth to the selected layer.</t>
+          <t>Component ablation on the frozen corpus: rule-based layer alone reaches 61.05% recall (95% CI 59.42-62.66), adding the BGE semantic stage raises recall to 94.77% (93.98-95.46); counting human-review referrals as positives reports an 11.70% false-positive rate versus 1.51% if only outright denials count (a 7.7x difference), and 68.5% of traffic reaches a human reviewer under that convention; recall is not provenance-invariant, ranging from 86.20% on original material to 99.88% on template-generated material; the optional local Llama3 review stage is invoked on 32.56% of requests at 2.51s each but changes zero final classifications.</t>
         </is>
       </c>
       <c r="F282" s="5" t="n"/>
@@ -12035,7 +12023,7 @@
       <c r="H282" s="5" t="n"/>
       <c r="I282" s="5" t="inlineStr">
         <is>
-          <t>bd1a5abc01ecfeb7a4723c4cf46b0b37c27273fb</t>
+          <t>b874b9a07cc89ff9501f87daddb54c9fff48bfa8</t>
         </is>
       </c>
     </row>
@@ -12045,7 +12033,7 @@
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>ESLD (External Surrogate Latent Defense): A Latent-Space Architecture for Faster, Stronger Prompt-Injection Defense</t>
+          <t>CASCADE: A Cascaded Hybrid Defense Architecture for Prompt Injection Detection in MCP-Based Systems</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
@@ -12060,7 +12048,7 @@
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>The sole baseline is each host guard LLM's own native decoded safe/unsafe verdict (the standard production pattern of running the guard model to full text-generation output), compared directly against ESLD's linear-probe verdict read from the same host's frozen intermediate hidden states, across the same 8 (host, task) evaluation cells.</t>
+          <t>None - no external MCP defense system was reimplemented or run on this corpus; the paper explicitly states literature figures for other MCP defenses are quoted descriptively (Table 1) under different datasets/protocols and support no comparative claim. The 'comparison' performed is an internal ablation across the paper's own three configurations (rule-only, rule+semantic, rule+semantic+LLM review).</t>
         </is>
       </c>
       <c r="F283" s="5" t="n"/>
@@ -12068,7 +12056,7 @@
       <c r="H283" s="5" t="n"/>
       <c r="I283" s="5" t="inlineStr">
         <is>
-          <t>bd1a5abc01ecfeb7a4723c4cf46b0b37c27273fb</t>
+          <t>b874b9a07cc89ff9501f87daddb54c9fff48bfa8</t>
         </is>
       </c>
     </row>
@@ -12078,7 +12066,7 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>ESLD (External Surrogate Latent Defense): A Latent-Space Architecture for Faster, Stronger Prompt-Injection Defense</t>
+          <t>CASCADE: A Cascaded Hybrid Defense Architecture for Prompt Injection Detection in MCP-Based Systems</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
@@ -12093,7 +12081,7 @@
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>Prompt injection against agentic LLM systems, covering both User Prompt Injection Attacks (UPIA/direct, malicious instructions placed directly in the user query) and Cross-Prompt Injection Attacks (XPIA/indirect, malicious instructions hidden in external content such as retrieved documents, emails, or tool outputs that the user never sees but the assistant reads and may act on). The paper frames the deployed defensive architecture as a 'guard model' sitting in front of the primary assistant, reading every incoming piece of text and returning a safe/unsafe verdict before the assistant is allowed to act; the paper's threat model is thus defense-side (how to detect injected content fast and accurately) rather than offense-side, with an explicitly out-of-scope adaptive/white-box threat (an attacker with access to the host's hidden states who could craft inputs to evade the probe's decision boundary) flagged as future work rather than evaluated.</t>
+          <t>An adversary targets an MCP-based LLM system by embedding malicious instructions in tool descriptions/metadata (tool poisoning: rug pulls, schema poisoning, tool shadowing), in tool outputs (indirect prompt injection), or seeks to exfiltrate data via tool invocations; the defense operates entirely locally (no external API calls) and inspects input before it reaches the LLM host.</t>
         </is>
       </c>
       <c r="F284" s="5" t="n"/>
@@ -12101,7 +12089,7 @@
       <c r="H284" s="5" t="n"/>
       <c r="I284" s="5" t="inlineStr">
         <is>
-          <t>bd1a5abc01ecfeb7a4723c4cf46b0b37c27273fb</t>
+          <t>b874b9a07cc89ff9501f87daddb54c9fff48bfa8</t>
         </is>
       </c>
     </row>
@@ -12111,7 +12099,7 @@
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>ESLD (External Surrogate Latent Defense): A Latent-Space Architecture for Faster, Stronger Prompt-Injection Defense</t>
+          <t>CASCADE: A Cascaded Hybrid Defense Architecture for Prompt Injection Detection in MCP-Based Systems</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
@@ -12126,7 +12114,7 @@
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>Explicit 'Limitations' subsection (8.3) with four named points. (1) Hardware and batching: latency is measured only on a single A100-80GB GPU at batch size 1, fp16, sequence length 1024; while batch size 1 is argued to be the operationally relevant setting for low-latency per-tool-call safety screening, absolute milliseconds and relative speedup will differ on other accelerators (consumer GPUs, CPUs, mobile NPUs) and at higher batch sizes, though the qualitative claim (stopping early plus avoiding sequential decode saves time) is expected to generalize whenever decode is sequential. (2) Language and domain coverage: all training and evaluation sources are English; prompt-injection attacks in other languages, in code, or in long structured documents (legal text, long-form web pages) are not exercised, and the leakage audit only controls for cross-source overlap within the studied English distribution without certifying generalization beyond it. (3) Probe family: the detector is deliberately a single linear probe (LDA with Ledoit-Wolf shrinkage) on the last-token hidden state of one chosen layer; multi-token pooling, multi-layer features, and small nonlinear probes are noted as plausible extensions that could improve quality at modest additional latency cost, but were deliberately not used since the single-layer linear design is meant to minimize deployment complexity and cleanly demonstrate that the safety signal is linearly present at a single layer. (4) Adversarial robustness: ESLD is evaluated only on attack distributions drawn from public benchmarks and is not stress-tested against an adaptive attacker with white-box access to the host's hidden states who could craft inputs moving the representation orthogonal to the probe's decision boundary -- the leakage audit mitigates source-level overlap optimism but does not simulate an active adversary, and a dedicated study of adaptive attacks against latent-space detectors is explicitly left to future work. A fifth point ('Scope of the comparison') notes the paper's only baseline is the host LLM's own guard verdict, not other defense families such as training-time alignment or input-transformation defenses.</t>
+          <t>Extensive and explicit: thresholds were fitted on the same 5,000-sample corpus used for evaluation with no held-out set, so reported figures are optimistic; no group-based/held-out partition exists despite 27.0% exact-duplicate and template-lineage overlap; the corpus is dominated by derived/synthetic material (65.7%) and its benign base and labels were not independently audited; a 31-label attack taxonomy is severely imbalanced (two labels cover 3,393 of 3,479 malicious records); Layer 3 (output-channel filtering) is implemented but evaluated only against a synthetic surrogate, not a live MCP host; no live multi-step/cross-server/adaptive-attack evaluation was performed; no external baseline detector was reimplemented; only a single LLM (Llama3 8B) was tested with no fixed seed, so the review stage is not bit-level reproducible; cost measurements are single-run with no confidence intervals.</t>
         </is>
       </c>
       <c r="F285" s="5" t="n"/>
@@ -12134,7 +12122,7 @@
       <c r="H285" s="5" t="n"/>
       <c r="I285" s="5" t="inlineStr">
         <is>
-          <t>bd1a5abc01ecfeb7a4723c4cf46b0b37c27273fb</t>
+          <t>b874b9a07cc89ff9501f87daddb54c9fff48bfa8</t>
         </is>
       </c>
     </row>
@@ -12144,7 +12132,7 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>ESLD (External Surrogate Latent Defense): A Latent-Space Architecture for Faster, Stronger Prompt-Injection Defense</t>
+          <t>CASCADE: A Cascaded Hybrid Defense Architecture for Prompt Injection Detection in MCP-Based Systems</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
@@ -12159,7 +12147,7 @@
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>This paper proposes ESLD (External Surrogate Latent Defense), a model-agnostic architecture for speeding up and improving the accuracy of LLM guard models used to detect prompt injection in agentic systems, where a separate 'guard' LLM screens every incoming piece of text (user input, retrieved documents, tool outputs) for malicious content before the primary assistant acts on it. The key insight is that guard LLMs suffer a serious latency bottleneck because standard deployment requires running the full autoregressive decode phase to produce a text verdict ('safe'/'unsafe'), even though the information needed for that verdict may already be present in the model's internal hidden states during the much cheaper prefill (input-encoding) phase. ESLD instead reads the guard's hidden state at a single selected intermediate layer L* and applies a small frozen linear probe (an LDA classifier with Ledoit-Wolf shrinkage regularization) directly to that internal representation to produce an attack/benign verdict, entirely bypassing token generation. The deployment layer is chosen via a principled three-step procedure: an outer leave-one-source-out cross-validation protocol combined with a leakage audit (filtering lexical/semantic overlap between training and evaluation attack sources) establishes an audit-best layer, then a Pareto rule selects the shallowest layer whose detection quality falls within a small tolerance (epsilon=0.005) of that audit-best layer's quality, formalizing the empirical observation that detection quality plateaus over a wide band of middle-to-late transformer layers while latency continues to fall as the chosen layer becomes shallower. Evaluated across four open-weight guard models (LlamaGuard-3, ShieldGemma-9B, Granite-Guardian-8B, WildGuard-7B) on both direct (UPIA) and indirect (XPIA) prompt-injection attack sources under a strict cross-validation protocol that prevents any train/test source leakage, ESLD is shown to be simultaneously faster and more accurate than the guard's own native output in the overwhelming majority of settings, with indirect/XPIA attacks showing the largest accuracy gains -- interpreted by the authors as evidence that the guard's decoded output head applies a narrow decision boundary shaped by its safety-fine-tuning objective, discarding richer prompt-injection signal that is nonetheless linearly present in the underlying hidden-state representation.</t>
+          <t>Introduces CASCADE (Cascaded Analysis for Secure Content And Detection Engine), a fully local three-layer defense for MCP-based systems combining regex/entropy pre-filtering, BGE-embedding semantic analysis with an optional local-Llama3 ambiguous-case review, and a pattern-based output filter, exposing a three-valued ALLOW/REVIEW/BLOCK decision interface. The paper's larger contribution, however, is a methodological audit of how MCP-defense evaluations are reported: it shows the choice of aggregation convention (counting human-review referrals as false positives versus only outright denials) changes the headline false-positive rate by a factor of 7.7, that detection recall is highly provenance-dependent (86.20% on original vs 99.88% on template-generated material), that the true operating threshold used in the released system cannot be read off the published configuration and must be recovered from the score distribution, and that the optional LLM review stage, while invoked on a third of traffic, changes no final classification outcome. All findings come from a fully reproducible, digest-pinned 5,000-sample corpus with per-sample released decision records.</t>
         </is>
       </c>
       <c r="F286" s="5" t="n"/>
@@ -12167,7 +12155,7 @@
       <c r="H286" s="5" t="n"/>
       <c r="I286" s="5" t="inlineStr">
         <is>
-          <t>bd1a5abc01ecfeb7a4723c4cf46b0b37c27273fb</t>
+          <t>b874b9a07cc89ff9501f87daddb54c9fff48bfa8</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -12266,7 +12254,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Trojan's Whisper: Stealthy Manipulation of OpenClaw through Injected Bootstrapped Guidance</t>
+          <t>Taxonomy, Evaluation and Exploitation of IPI-Centric LLM Agent Defense Frameworks</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -12276,17 +12264,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Guidance Injection</t>
+          <t>Semantic-Masquerading IPI; Cascading IPI; Isolation-Breach IPI</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>tool-output</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>persistence-backdoor</t>
+          <t>goal-hijack</t>
         </is>
       </c>
       <c r="G2" s="5" t="n"/>
@@ -12295,7 +12283,7 @@
       <c r="J2" s="5" t="n"/>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>77bd60b2f06f814a3f6ef85ec0c11b0176b0ceb1</t>
+          <t>66c8e83ed0fc215dc8be0e44715a692ef27f005b</t>
         </is>
       </c>
     </row>
@@ -12305,27 +12293,27 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Human-Interpretable Adversarial Prompt Attack on Large Language Models with Situational Context</t>
+          <t>FlashMem: Distilling Intrinsic Latent Memory via Computation Reuse</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>attack / failure mechanism</t>
+          <t>defense / fix</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>situation-driven contextual adversarial prompt attack</t>
+          <t>FlashMem</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>memory</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>reasoning-corruption</t>
         </is>
       </c>
       <c r="G3" s="5" t="n"/>
@@ -12334,7 +12322,7 @@
       <c r="J3" s="5" t="n"/>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>7cf2dd505b53e690ce0ff1fd15cc55f127841819</t>
+          <t>4e368119b5b8e809062d9da09b24941c705f9236</t>
         </is>
       </c>
     </row>
@@ -12344,27 +12332,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Caution for the Environment: Multimodal Agents are Susceptible to Environmental Distractions</t>
+          <t>Poisoning Retrieval Corpora by Injecting Adversarial Passages</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>defense / fix</t>
+          <t>attack / failure mechanism</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>UNNAMED: DPO-based faithfulness-improvement training for GUI agents against environmental distraction</t>
+          <t>UNNAMED: gradient-based corpus poisoning (adversarial passage injection)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>cross-modal</t>
+          <t>RAG</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>silent-corruption</t>
         </is>
       </c>
       <c r="G4" s="5" t="n"/>
@@ -12373,7 +12361,7 @@
       <c r="J4" s="5" t="n"/>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>ee745d4c5e9ff890731866f54b6b333bb3a4eb57</t>
+          <t>e3a49a110801fd961db887f8af1239cc79b55a5b</t>
         </is>
       </c>
     </row>
@@ -12383,27 +12371,27 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Enterprise Secure AI Execution Engine: A Zero-Trust Security Gateway for Enterprise LLM Systems</t>
+          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>defense / fix</t>
+          <t>attack / failure mechanism</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Enterprise Secure AI Execution Engine (Zero-Trust AI Security Gateway)</t>
+          <t>context poisoning (self-induced, non-adversarial)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>tool-output</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>data-exfiltration</t>
+          <t>silent-corruption</t>
         </is>
       </c>
       <c r="G5" s="5" t="n"/>
@@ -12412,7 +12400,7 @@
       <c r="J5" s="5" t="n"/>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>1ce4b21dda6721f1c94b63ab1b93144a87a9b0ad</t>
+          <t>arxiv:2606.25514</t>
         </is>
       </c>
     </row>
@@ -12422,22 +12410,22 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Tug-of-War between Knowledge: Exploring and Resolving Knowledge Conflicts in Retrieval-Augmented Language Models</t>
+          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>attack / failure mechanism</t>
+          <t>defense / fix</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>UNNAMED: over-trust bias toward conflicting external evidence over correct parametric memory in RALMs</t>
+          <t>icat-agent (decentralized event-based multi-agent scaffold)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>RAG</t>
+          <t>tool-output</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -12451,7 +12439,7 @@
       <c r="J6" s="5" t="n"/>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>812b87876b22260fe046af447c5f40a4ce2906ea</t>
+          <t>arxiv:2606.25514</t>
         </is>
       </c>
     </row>
@@ -12461,7 +12449,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Tug-of-War between Knowledge: Exploring and Resolving Knowledge Conflicts in Retrieval-Augmented Language Models</t>
+          <t>Tug-of-War within A Decade: Conflict Resolution in Vulnerability Analysis via Teacher-Guided Retrieval-Augmented Generations</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -12471,7 +12459,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>CD2 (Conflict-Disentangle Contrastive Decoding)</t>
+          <t>CRVA-TGRAG (Conflict Resolution in Vulnerability Analysis via Teacher-Guided RAG)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -12490,7 +12478,7 @@
       <c r="J7" s="5" t="n"/>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>812b87876b22260fe046af447c5f40a4ce2906ea</t>
+          <t>a2de6faaa98252c163c088613a04ad2dceb284a4</t>
         </is>
       </c>
     </row>
@@ -12500,7 +12488,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>CodeDelegator: Mitigating Context Pollution via Role Separation in Code-as-Action Agents</t>
+          <t>Context-Aware RL for Agentic and Multimodal LLMs</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -12510,12 +12498,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>context pollution (role conflation in single-agent code-as-action agents)</t>
+          <t>context unawareness (failure to identify a small decisive piece of evidence within long/complex context)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>cross-modal</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -12529,7 +12517,7 @@
       <c r="J8" s="5" t="n"/>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>894af73fb679f95ea1a36eb6bad300bfb80566fa</t>
+          <t>72b5e6023db3b5af8e8f27f8b4a52bc5f1f32ba7</t>
         </is>
       </c>
     </row>
@@ -12539,7 +12527,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>CodeDelegator: Mitigating Context Pollution via Role Separation in Code-as-Action Agents</t>
+          <t>Context-Aware RL for Agentic and Multimodal LLMs</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -12549,12 +12537,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>CodeDelegator (role separation via Delegator/Coder agents + EPSS)</t>
+          <t>ContextRL</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>cross-modal</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -12568,7 +12556,7 @@
       <c r="J9" s="5" t="n"/>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>894af73fb679f95ea1a36eb6bad300bfb80566fa</t>
+          <t>72b5e6023db3b5af8e8f27f8b4a52bc5f1f32ba7</t>
         </is>
       </c>
     </row>
@@ -12578,7 +12566,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Compile, Then Page: Executable SOP Programs and a Capability-Gated Runtime for Procedural LLM Agents</t>
+          <t>Hybrid Real-time Framework for Detecting Adaptive Prompt Injection Attacks in Large Language Models</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -12588,7 +12576,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Program-Guided (PG) Runtime / Compile-then-Page SOP compiler</t>
+          <t>UNNAMED: Hybrid multi-layered real-time PI detection framework</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -12598,7 +12586,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>goal-hijack</t>
         </is>
       </c>
       <c r="G10" s="5" t="n"/>
@@ -12607,7 +12595,7 @@
       <c r="J10" s="5" t="n"/>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>62e953c40357cfb93027ef8e55b60eacd76bc963</t>
+          <t>dd8e3ff740ecd615b37dfb219d98e73a782f71d1</t>
         </is>
       </c>
     </row>
@@ -12617,22 +12605,22 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Breaking ReAct Agents: Foot-in-the-Door Attack Will Get You In</t>
+          <t>DRIP: Defending Prompt Injection via Token-wise Representation Editing and Residual Instruction Fusion</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>attack / failure mechanism</t>
+          <t>defense / fix</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Foot-in-the-Door (FITD) attack</t>
+          <t>DRIP</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -12646,7 +12634,7 @@
       <c r="J11" s="5" t="n"/>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>6424243734d098460777049e1f11705d1b5d85c8</t>
+          <t>65d9d85b86ce1b8c3dd01a446ebf28d99fd26bdd</t>
         </is>
       </c>
     </row>
@@ -12656,27 +12644,27 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Breaking ReAct Agents: Foot-in-the-Door Attack Will Get You In</t>
+          <t>Corpus Poisoning via Approximate Greedy Gradient Descent</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>defense / fix</t>
+          <t>attack / failure mechanism</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>UNNAMED: Reflection-based defenses against Foot-in-the-Door IPI (Self-Reflection / Hesitation Reflection / Safe Reflection)</t>
+          <t>AGGD (Approximate Greedy Gradient Descent)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>RAG</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>silent-corruption</t>
         </is>
       </c>
       <c r="G12" s="5" t="n"/>
@@ -12685,7 +12673,7 @@
       <c r="J12" s="5" t="n"/>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>6424243734d098460777049e1f11705d1b5d85c8</t>
+          <t>19afd7b97061fdf0dd4a4726bef4ed8acd31a0a8</t>
         </is>
       </c>
     </row>
@@ -12695,7 +12683,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Defending Against Prompt Injection with DataFilter</t>
+          <t>The Task Shield: Enforcing Task Alignment to Defend Against Indirect Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -12705,7 +12693,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>DataFilter</t>
+          <t>Task Shield</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -12724,7 +12712,7 @@
       <c r="J13" s="5" t="n"/>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>7222e1b74675ebfd85d5f261ef8ab5010111e737</t>
+          <t>8af6009a8d55d456213f6819567eb3ace39dd176</t>
         </is>
       </c>
     </row>
@@ -12734,7 +12722,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>HAGE: Harnessing Agentic Memory via RL-Driven Weighted Graph Evolution</t>
+          <t>PIShield: Detecting Prompt Injection Attacks via Intrinsic LLM Features</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -12744,17 +12732,17 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>HAGE (RL-driven weighted graph evolution)</t>
+          <t>PIShield</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>memory</t>
+          <t>tool-output</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>goal-hijack</t>
         </is>
       </c>
       <c r="G14" s="5" t="n"/>
@@ -12763,7 +12751,7 @@
       <c r="J14" s="5" t="n"/>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>95bb7a742af788471295bb3bd6f12d4f6886dfa1</t>
+          <t>1db392d42f020925561c0686ec24831fcd78bcae</t>
         </is>
       </c>
     </row>
@@ -12773,7 +12761,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>AgentProg: Empowering Long-Horizon GUI Agents with Program-guided Context Management</t>
+          <t>Rethinking All Evidence: Enhancing Trustworthy Retrieval-Augmented Generation via Conflict-Driven Summarization</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -12783,17 +12771,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>AgentProg (program-guided context management with Execution Tree and global belief state)</t>
+          <t>CARE-RAG (Conflict-Aware and Reliable Evidence for RAG)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>RAG</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>silent-corruption</t>
         </is>
       </c>
       <c r="G15" s="5" t="n"/>
@@ -12802,7 +12790,7 @@
       <c r="J15" s="5" t="n"/>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>420c63cc0480a1990a348b741612cbde516b3f30</t>
+          <t>0a06adbce02a4f5db3b3f08f23394e3acfc9a573</t>
         </is>
       </c>
     </row>
@@ -12812,7 +12800,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>ICON: Indirect Prompt Injection Defense for Agents based on Inference-Time Correction</t>
+          <t>PISanitizer: Preventing Prompt Injection to Long-Context LLMs via Prompt Sanitization</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -12822,7 +12810,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>ICON (Inference-Time Correction)</t>
+          <t>PISanitizer</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -12841,7 +12829,7 @@
       <c r="J16" s="5" t="n"/>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>9a559291c36be0ac35a9db4682d18acc6ccff2d3</t>
+          <t>177137fd3d07855a6fa2e0bdcee3606d0159fa3d</t>
         </is>
       </c>
     </row>
@@ -12851,7 +12839,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Research on Security Enhancement Methods for Adversarial Robust Large Language Model Intelligent Agents for Medical Decision-Making Tasks</t>
+          <t>CASCADE: A Cascaded Hybrid Defense Architecture for Prompt Injection Detection in MCP-Based Systems</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -12861,12 +12849,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>ARSM-Agent</t>
+          <t>CASCADE</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>tool-metadata</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -12880,58 +12868,19 @@
       <c r="J17" s="5" t="n"/>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>59f623857e6d89dc1d0f2ca4cb433f0017b768db</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>ESLD (External Surrogate Latent Defense): A Latent-Space Architecture for Faster, Stronger Prompt-Injection Defense</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>defense / fix</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>ESLD (External Surrogate Latent Defense)</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>tool-output</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>goal-hijack</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>bd1a5abc01ecfeb7a4723c4cf46b0b37c27273fb</t>
+          <t>b874b9a07cc89ff9501f87daddb54c9fff48bfa8</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation sqref="G2:G18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"yes,no,unclear"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"yes,no,unclear"</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"yes,no,unclear"</formula1>
     </dataValidation>
   </dataValidations>
